--- a/1_lecturas/inputs/registro_operario_mes.xlsx
+++ b/1_lecturas/inputs/registro_operario_mes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\1_lecturas\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158B7AEA-82E1-47BA-9AFB-70B4392F984F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557E1A81-ED3D-4BF3-A0A9-6AFC5E303A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Lecturas!$A$7:$H$582</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -2481,13 +2490,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H582"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="34.54296875" customWidth="1"/>
+    <col min="3" max="3" width="40.81640625" customWidth="1"/>
     <col min="4" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -2593,7 +2601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2617,7 +2625,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -2641,7 +2649,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
@@ -2665,7 +2673,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -2689,7 +2697,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -2713,7 +2721,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
@@ -2737,7 +2745,7 @@
       </c>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -2757,7 +2765,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2781,7 +2789,7 @@
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
@@ -2805,7 +2813,7 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
@@ -2829,7 +2837,7 @@
       </c>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2853,7 +2861,7 @@
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
@@ -2877,7 +2885,7 @@
       </c>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -2897,7 +2905,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -2921,7 +2929,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
@@ -2945,7 +2953,7 @@
       </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
@@ -2969,7 +2977,7 @@
       </c>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>50</v>
       </c>
@@ -2993,7 +3001,7 @@
       </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
@@ -3017,7 +3025,7 @@
       </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
@@ -3041,7 +3049,7 @@
       </c>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
@@ -3065,7 +3073,7 @@
       </c>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>50</v>
       </c>
@@ -3089,7 +3097,7 @@
       </c>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>50</v>
       </c>
@@ -3113,7 +3121,7 @@
       </c>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>50</v>
       </c>
@@ -3137,7 +3145,7 @@
       </c>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>50</v>
       </c>
@@ -3161,7 +3169,7 @@
       </c>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>50</v>
       </c>
@@ -3185,7 +3193,7 @@
       </c>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>50</v>
       </c>
@@ -3209,7 +3217,7 @@
       </c>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>50</v>
       </c>
@@ -3233,7 +3241,7 @@
       </c>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>50</v>
       </c>
@@ -3257,7 +3265,7 @@
       </c>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>50</v>
       </c>
@@ -3281,7 +3289,7 @@
       </c>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>50</v>
       </c>
@@ -3301,7 +3309,7 @@
       <c r="G37" s="5"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>50</v>
       </c>
@@ -3325,7 +3333,7 @@
       </c>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>50</v>
       </c>
@@ -3349,7 +3357,7 @@
       </c>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>50</v>
       </c>
@@ -3373,7 +3381,7 @@
       </c>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>50</v>
       </c>
@@ -3397,7 +3405,7 @@
       </c>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>50</v>
       </c>
@@ -3673,8 +3681,12 @@
       <c r="E53" s="3">
         <v>2160</v>
       </c>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="F53" s="5">
+        <v>2160</v>
+      </c>
+      <c r="G53" s="5">
+        <v>5</v>
+      </c>
       <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3693,8 +3705,12 @@
       <c r="E54" s="3">
         <v>539</v>
       </c>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="F54" s="5">
+        <v>547</v>
+      </c>
+      <c r="G54" s="5">
+        <v>8</v>
+      </c>
       <c r="H54" s="6"/>
     </row>
     <row r="55" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3733,8 +3749,12 @@
       <c r="E56" s="3">
         <v>884</v>
       </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="5">
+        <v>899</v>
+      </c>
+      <c r="G56" s="5">
+        <v>15</v>
+      </c>
       <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3753,8 +3773,12 @@
       <c r="E57" s="3">
         <v>1712</v>
       </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="5">
+        <v>1731</v>
+      </c>
+      <c r="G57" s="5">
+        <v>19</v>
+      </c>
       <c r="H57" s="6"/>
     </row>
     <row r="58" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3773,8 +3797,12 @@
       <c r="E58" s="3">
         <v>24</v>
       </c>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="5">
+        <v>29</v>
+      </c>
+      <c r="G58" s="5">
+        <v>6</v>
+      </c>
       <c r="H58" s="6"/>
     </row>
     <row r="59" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3793,8 +3821,12 @@
       <c r="E59" s="3">
         <v>26</v>
       </c>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="5">
+        <v>32</v>
+      </c>
+      <c r="G59" s="5">
+        <v>6</v>
+      </c>
       <c r="H59" s="6"/>
     </row>
     <row r="60" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3813,8 +3845,12 @@
       <c r="E60" s="3">
         <v>156</v>
       </c>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="5">
+        <v>166</v>
+      </c>
+      <c r="G60" s="5">
+        <v>10</v>
+      </c>
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3833,8 +3869,12 @@
       <c r="E61" s="3">
         <v>59</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="5">
+        <v>64</v>
+      </c>
+      <c r="G61" s="5">
+        <v>6</v>
+      </c>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3873,8 +3913,12 @@
       <c r="E63" s="3">
         <v>29</v>
       </c>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="5">
+        <v>35</v>
+      </c>
+      <c r="G63" s="5">
+        <v>6</v>
+      </c>
       <c r="H63" s="6"/>
     </row>
     <row r="64" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3893,8 +3937,12 @@
       <c r="E64" s="3">
         <v>90</v>
       </c>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="5">
+        <v>119</v>
+      </c>
+      <c r="G64" s="5">
+        <v>29</v>
+      </c>
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3913,8 +3961,12 @@
       <c r="E65" s="3">
         <v>60</v>
       </c>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="F65" s="5">
+        <v>74</v>
+      </c>
+      <c r="G65" s="5">
+        <v>14</v>
+      </c>
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3933,8 +3985,12 @@
       <c r="E66" s="3">
         <v>1739</v>
       </c>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="F66" s="5">
+        <v>1788</v>
+      </c>
+      <c r="G66" s="5">
+        <v>49</v>
+      </c>
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3953,8 +4009,12 @@
       <c r="E67" s="3">
         <v>148</v>
       </c>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="F67" s="5">
+        <v>154</v>
+      </c>
+      <c r="G67" s="5">
+        <v>6</v>
+      </c>
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3973,8 +4033,12 @@
       <c r="E68" s="3">
         <v>328</v>
       </c>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="F68" s="5">
+        <v>356</v>
+      </c>
+      <c r="G68" s="5">
+        <v>28</v>
+      </c>
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3993,8 +4057,12 @@
       <c r="E69" s="3">
         <v>549</v>
       </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="F69" s="5">
+        <v>552</v>
+      </c>
+      <c r="G69" s="5">
+        <v>5</v>
+      </c>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4013,8 +4081,12 @@
       <c r="E70" s="3">
         <v>53</v>
       </c>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="F70" s="5">
+        <v>72</v>
+      </c>
+      <c r="G70" s="5">
+        <v>19</v>
+      </c>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4033,8 +4105,12 @@
       <c r="E71" s="3">
         <v>1514</v>
       </c>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="F71" s="5">
+        <v>1515</v>
+      </c>
+      <c r="G71" s="5">
+        <v>5</v>
+      </c>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4053,8 +4129,12 @@
       <c r="E72" s="3">
         <v>291</v>
       </c>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="F72" s="5">
+        <v>306</v>
+      </c>
+      <c r="G72" s="5">
+        <v>15</v>
+      </c>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4093,8 +4173,12 @@
       <c r="E74" s="3">
         <v>140</v>
       </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
+      <c r="F74" s="5">
+        <v>145</v>
+      </c>
+      <c r="G74" s="5">
+        <v>6</v>
+      </c>
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4153,8 +4237,12 @@
       <c r="E77" s="3">
         <v>3635</v>
       </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
+      <c r="F77" s="5">
+        <v>3655</v>
+      </c>
+      <c r="G77" s="5">
+        <v>20</v>
+      </c>
       <c r="H77" s="6"/>
     </row>
     <row r="78" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4173,8 +4261,12 @@
       <c r="E78" s="3">
         <v>14</v>
       </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="F78" s="5">
+        <v>17</v>
+      </c>
+      <c r="G78" s="5">
+        <v>5</v>
+      </c>
       <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4193,8 +4285,12 @@
       <c r="E79" s="3">
         <v>377</v>
       </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="F79" s="5">
+        <v>391</v>
+      </c>
+      <c r="G79" s="5">
+        <v>14</v>
+      </c>
       <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4213,8 +4309,12 @@
       <c r="E80" s="3">
         <v>32</v>
       </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
+      <c r="F80" s="5">
+        <v>35</v>
+      </c>
+      <c r="G80" s="5">
+        <v>5</v>
+      </c>
       <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4233,8 +4333,12 @@
       <c r="E81" s="3">
         <v>671</v>
       </c>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
+      <c r="F81" s="5">
+        <v>687</v>
+      </c>
+      <c r="G81" s="5">
+        <v>16</v>
+      </c>
       <c r="H81" s="6"/>
     </row>
     <row r="82" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4253,8 +4357,12 @@
       <c r="E82" s="3">
         <v>28</v>
       </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
+      <c r="F82" s="5">
+        <v>284</v>
+      </c>
+      <c r="G82" s="5">
+        <v>6</v>
+      </c>
       <c r="H82" s="6"/>
     </row>
     <row r="83" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4273,8 +4381,12 @@
       <c r="E83" s="3">
         <v>310</v>
       </c>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
+      <c r="F83" s="5">
+        <v>316</v>
+      </c>
+      <c r="G83" s="5">
+        <v>6</v>
+      </c>
       <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4313,8 +4425,12 @@
       <c r="E85" s="3">
         <v>351</v>
       </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
+      <c r="F85" s="5">
+        <v>363</v>
+      </c>
+      <c r="G85" s="5">
+        <v>12</v>
+      </c>
       <c r="H85" s="6"/>
     </row>
     <row r="86" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4333,8 +4449,12 @@
       <c r="E86" s="3">
         <v>0</v>
       </c>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
+      <c r="F86" s="5">
+        <v>4</v>
+      </c>
+      <c r="G86" s="5">
+        <v>5</v>
+      </c>
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -4357,7 +4477,7 @@
       <c r="G87" s="5"/>
       <c r="H87" s="6"/>
     </row>
-    <row r="88" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>153</v>
       </c>
@@ -4373,11 +4493,15 @@
       <c r="E88" s="3">
         <v>30</v>
       </c>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
+      <c r="F88" s="5">
+        <v>36</v>
+      </c>
+      <c r="G88" s="5">
+        <v>6</v>
+      </c>
       <c r="H88" s="6"/>
     </row>
-    <row r="89" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>153</v>
       </c>
@@ -4393,11 +4517,15 @@
       <c r="E89" s="3">
         <v>2332</v>
       </c>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
+      <c r="F89" s="5">
+        <v>2338</v>
+      </c>
+      <c r="G89" s="5">
+        <v>6</v>
+      </c>
       <c r="H89" s="6"/>
     </row>
-    <row r="90" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>153</v>
       </c>
@@ -4413,11 +4541,15 @@
       <c r="E90" s="3">
         <v>40</v>
       </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="F90" s="5">
+        <v>50</v>
+      </c>
+      <c r="G90" s="5">
+        <v>10</v>
+      </c>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>153</v>
       </c>
@@ -4433,11 +4565,15 @@
       <c r="E91" s="3">
         <v>406</v>
       </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="F91" s="5">
+        <v>428</v>
+      </c>
+      <c r="G91" s="5">
+        <v>22</v>
+      </c>
       <c r="H91" s="6"/>
     </row>
-    <row r="92" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>153</v>
       </c>
@@ -4453,11 +4589,15 @@
       <c r="E92" s="3">
         <v>659</v>
       </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="F92" s="5">
+        <v>676</v>
+      </c>
+      <c r="G92" s="5">
+        <v>17</v>
+      </c>
       <c r="H92" s="6"/>
     </row>
-    <row r="93" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>153</v>
       </c>
@@ -4473,11 +4613,15 @@
       <c r="E93" s="3">
         <v>258</v>
       </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="F93" s="5">
+        <v>327</v>
+      </c>
+      <c r="G93" s="5">
+        <v>69</v>
+      </c>
       <c r="H93" s="6"/>
     </row>
-    <row r="94" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>153</v>
       </c>
@@ -4493,11 +4637,15 @@
       <c r="E94" s="3">
         <v>5965</v>
       </c>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
+      <c r="F94" s="5">
+        <v>6082</v>
+      </c>
+      <c r="G94" s="5">
+        <v>117</v>
+      </c>
       <c r="H94" s="6"/>
     </row>
-    <row r="95" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>153</v>
       </c>
@@ -4513,11 +4661,15 @@
       <c r="E95" s="3">
         <v>41</v>
       </c>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
+      <c r="F95" s="5">
+        <v>52</v>
+      </c>
+      <c r="G95" s="5">
+        <v>11</v>
+      </c>
       <c r="H95" s="6"/>
     </row>
-    <row r="96" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>153</v>
       </c>
@@ -4533,11 +4685,15 @@
       <c r="E96" s="3">
         <v>4139</v>
       </c>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="F96" s="5">
+        <v>4151</v>
+      </c>
+      <c r="G96" s="5">
+        <v>12</v>
+      </c>
       <c r="H96" s="6"/>
     </row>
-    <row r="97" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>153</v>
       </c>
@@ -4553,11 +4709,15 @@
       <c r="E97" s="3">
         <v>2921</v>
       </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
+      <c r="F97" s="5">
+        <v>2930</v>
+      </c>
+      <c r="G97" s="5">
+        <v>9</v>
+      </c>
       <c r="H97" s="6"/>
     </row>
-    <row r="98" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>153</v>
       </c>
@@ -4573,11 +4733,15 @@
       <c r="E98" s="3">
         <v>1132</v>
       </c>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
+      <c r="F98" s="5">
+        <v>1144</v>
+      </c>
+      <c r="G98" s="5">
+        <v>12</v>
+      </c>
       <c r="H98" s="6"/>
     </row>
-    <row r="99" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>153</v>
       </c>
@@ -4593,11 +4757,15 @@
       <c r="E99" s="3">
         <v>298</v>
       </c>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
+      <c r="F99" s="5">
+        <v>313</v>
+      </c>
+      <c r="G99" s="5">
+        <v>15</v>
+      </c>
       <c r="H99" s="6"/>
     </row>
-    <row r="100" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>153</v>
       </c>
@@ -4613,11 +4781,15 @@
       <c r="E100" s="3">
         <v>581</v>
       </c>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
+      <c r="F100" s="5">
+        <v>602</v>
+      </c>
+      <c r="G100" s="5">
+        <v>21</v>
+      </c>
       <c r="H100" s="6"/>
     </row>
-    <row r="101" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>153</v>
       </c>
@@ -4637,7 +4809,7 @@
       <c r="G101" s="5"/>
       <c r="H101" s="6"/>
     </row>
-    <row r="102" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>153</v>
       </c>
@@ -4653,11 +4825,15 @@
       <c r="E102" s="3">
         <v>25</v>
       </c>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
+      <c r="F102" s="5">
+        <v>31</v>
+      </c>
+      <c r="G102" s="5">
+        <v>6</v>
+      </c>
       <c r="H102" s="6"/>
     </row>
-    <row r="103" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>153</v>
       </c>
@@ -4673,11 +4849,15 @@
       <c r="E103" s="3">
         <v>3209</v>
       </c>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
+      <c r="F103" s="5">
+        <v>3230</v>
+      </c>
+      <c r="G103" s="5">
+        <v>21</v>
+      </c>
       <c r="H103" s="6"/>
     </row>
-    <row r="104" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>153</v>
       </c>
@@ -4693,11 +4873,15 @@
       <c r="E104" s="3">
         <v>1105</v>
       </c>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
+      <c r="F104" s="5">
+        <v>1140</v>
+      </c>
+      <c r="G104" s="5">
+        <v>35</v>
+      </c>
       <c r="H104" s="6"/>
     </row>
-    <row r="105" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>153</v>
       </c>
@@ -4713,11 +4897,15 @@
       <c r="E105" s="3">
         <v>65</v>
       </c>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
+      <c r="F105" s="5">
+        <v>76</v>
+      </c>
+      <c r="G105" s="5">
+        <v>11</v>
+      </c>
       <c r="H105" s="6"/>
     </row>
-    <row r="106" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>172</v>
       </c>
@@ -4733,11 +4921,15 @@
       <c r="E106" s="3">
         <v>307</v>
       </c>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
+      <c r="F106" s="5">
+        <v>312</v>
+      </c>
+      <c r="G106" s="5">
+        <v>5</v>
+      </c>
       <c r="H106" s="6"/>
     </row>
-    <row r="107" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>172</v>
       </c>
@@ -4753,11 +4945,15 @@
       <c r="E107" s="3">
         <v>76</v>
       </c>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
+      <c r="F107" s="5">
+        <v>97</v>
+      </c>
+      <c r="G107" s="5">
+        <v>21</v>
+      </c>
       <c r="H107" s="6"/>
     </row>
-    <row r="108" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>172</v>
       </c>
@@ -4777,7 +4973,7 @@
       <c r="G108" s="5"/>
       <c r="H108" s="6"/>
     </row>
-    <row r="109" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>172</v>
       </c>
@@ -4793,11 +4989,15 @@
       <c r="E109" s="3">
         <v>3015</v>
       </c>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
+      <c r="F109" s="5">
+        <v>3027</v>
+      </c>
+      <c r="G109" s="5">
+        <v>12</v>
+      </c>
       <c r="H109" s="6"/>
     </row>
-    <row r="110" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>172</v>
       </c>
@@ -4813,11 +5013,15 @@
       <c r="E110" s="3">
         <v>232</v>
       </c>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
+      <c r="F110" s="5">
+        <v>245</v>
+      </c>
+      <c r="G110" s="5">
+        <v>13</v>
+      </c>
       <c r="H110" s="6"/>
     </row>
-    <row r="111" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>172</v>
       </c>
@@ -4837,7 +5041,7 @@
       <c r="G111" s="5"/>
       <c r="H111" s="6"/>
     </row>
-    <row r="112" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>172</v>
       </c>
@@ -4853,11 +5057,15 @@
       <c r="E112" s="3">
         <v>980</v>
       </c>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
+      <c r="F112" s="5">
+        <v>989</v>
+      </c>
+      <c r="G112" s="5">
+        <v>9</v>
+      </c>
       <c r="H112" s="6"/>
     </row>
-    <row r="113" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>172</v>
       </c>
@@ -4873,11 +5081,15 @@
       <c r="E113" s="3">
         <v>77</v>
       </c>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
+      <c r="F113" s="5">
+        <v>80</v>
+      </c>
+      <c r="G113" s="5">
+        <v>5</v>
+      </c>
       <c r="H113" s="6"/>
     </row>
-    <row r="114" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>172</v>
       </c>
@@ -4893,11 +5105,15 @@
       <c r="E114" s="3">
         <v>1013</v>
       </c>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
+      <c r="F114" s="5">
+        <v>1017</v>
+      </c>
+      <c r="G114" s="5">
+        <v>5</v>
+      </c>
       <c r="H114" s="6"/>
     </row>
-    <row r="115" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>172</v>
       </c>
@@ -4913,11 +5129,15 @@
       <c r="E115" s="3">
         <v>38</v>
       </c>
-      <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
+      <c r="F115" s="5">
+        <v>64</v>
+      </c>
+      <c r="G115" s="5">
+        <v>26</v>
+      </c>
       <c r="H115" s="6"/>
     </row>
-    <row r="116" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>172</v>
       </c>
@@ -4933,11 +5153,15 @@
       <c r="E116" s="3">
         <v>1084</v>
       </c>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
+      <c r="F116" s="5">
+        <v>1102</v>
+      </c>
+      <c r="G116" s="5">
+        <v>18</v>
+      </c>
       <c r="H116" s="6"/>
     </row>
-    <row r="117" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>172</v>
       </c>
@@ -4953,11 +5177,15 @@
       <c r="E117" s="3">
         <v>4303</v>
       </c>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
+      <c r="F117" s="5">
+        <v>4331</v>
+      </c>
+      <c r="G117" s="5">
+        <v>28</v>
+      </c>
       <c r="H117" s="6"/>
     </row>
-    <row r="118" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>172</v>
       </c>
@@ -4973,11 +5201,15 @@
       <c r="E118" s="3">
         <v>63</v>
       </c>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
+      <c r="F118" s="5">
+        <v>66</v>
+      </c>
+      <c r="G118" s="5">
+        <v>5</v>
+      </c>
       <c r="H118" s="6"/>
     </row>
-    <row r="119" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>172</v>
       </c>
@@ -4993,11 +5225,15 @@
       <c r="E119" s="3">
         <v>3127</v>
       </c>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
+      <c r="F119" s="5">
+        <v>3134</v>
+      </c>
+      <c r="G119" s="5">
+        <v>7</v>
+      </c>
       <c r="H119" s="6"/>
     </row>
-    <row r="120" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>172</v>
       </c>
@@ -5013,11 +5249,15 @@
       <c r="E120" s="3">
         <v>97</v>
       </c>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
+      <c r="F120" s="5">
+        <v>106</v>
+      </c>
+      <c r="G120" s="5">
+        <v>9</v>
+      </c>
       <c r="H120" s="6"/>
     </row>
-    <row r="121" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>172</v>
       </c>
@@ -5033,11 +5273,15 @@
       <c r="E121" s="3">
         <v>351</v>
       </c>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
+      <c r="F121" s="5">
+        <v>360</v>
+      </c>
+      <c r="G121" s="5">
+        <v>9</v>
+      </c>
       <c r="H121" s="6"/>
     </row>
-    <row r="122" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>172</v>
       </c>
@@ -5053,11 +5297,15 @@
       <c r="E122" s="3">
         <v>24</v>
       </c>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
+      <c r="F122" s="5">
+        <v>26</v>
+      </c>
+      <c r="G122" s="5">
+        <v>5</v>
+      </c>
       <c r="H122" s="6"/>
     </row>
-    <row r="123" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>4</v>
       </c>
@@ -5073,11 +5321,15 @@
       <c r="E123" s="3">
         <v>865</v>
       </c>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
+      <c r="F123" s="5">
+        <v>882</v>
+      </c>
+      <c r="G123" s="5">
+        <v>17</v>
+      </c>
       <c r="H123" s="6"/>
     </row>
-    <row r="124" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>4</v>
       </c>
@@ -5097,7 +5349,7 @@
       <c r="G124" s="5"/>
       <c r="H124" s="6"/>
     </row>
-    <row r="125" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>4</v>
       </c>
@@ -5113,11 +5365,15 @@
       <c r="E125" s="3">
         <v>4</v>
       </c>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
+      <c r="F125" s="5">
+        <v>4</v>
+      </c>
+      <c r="G125" s="5">
+        <v>5</v>
+      </c>
       <c r="H125" s="6"/>
     </row>
-    <row r="126" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>4</v>
       </c>
@@ -5133,11 +5389,15 @@
       <c r="E126" s="3">
         <v>0</v>
       </c>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
+      <c r="F126" s="5">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5">
+        <v>5</v>
+      </c>
       <c r="H126" s="6"/>
     </row>
-    <row r="127" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>4</v>
       </c>
@@ -5153,11 +5413,15 @@
       <c r="E127" s="3">
         <v>755</v>
       </c>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
+      <c r="F127" s="5">
+        <v>772</v>
+      </c>
+      <c r="G127" s="5">
+        <v>17</v>
+      </c>
       <c r="H127" s="6"/>
     </row>
-    <row r="128" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>4</v>
       </c>
@@ -5173,11 +5437,15 @@
       <c r="E128" s="3">
         <v>2305</v>
       </c>
-      <c r="F128" s="5"/>
-      <c r="G128" s="5"/>
+      <c r="F128" s="5">
+        <v>2339</v>
+      </c>
+      <c r="G128" s="5">
+        <v>34</v>
+      </c>
       <c r="H128" s="6"/>
     </row>
-    <row r="129" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>4</v>
       </c>
@@ -5193,11 +5461,15 @@
       <c r="E129" s="3">
         <v>41</v>
       </c>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
+      <c r="F129" s="5">
+        <v>47</v>
+      </c>
+      <c r="G129" s="5">
+        <v>6</v>
+      </c>
       <c r="H129" s="6"/>
     </row>
-    <row r="130" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>4</v>
       </c>
@@ -5213,11 +5485,15 @@
       <c r="E130" s="3">
         <v>258</v>
       </c>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
+      <c r="F130" s="5">
+        <v>321</v>
+      </c>
+      <c r="G130" s="5">
+        <v>63</v>
+      </c>
       <c r="H130" s="6"/>
     </row>
-    <row r="131" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>4</v>
       </c>
@@ -5233,11 +5509,15 @@
       <c r="E131" s="3">
         <v>35</v>
       </c>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
+      <c r="F131" s="5">
+        <v>46</v>
+      </c>
+      <c r="G131" s="5">
+        <v>11</v>
+      </c>
       <c r="H131" s="6"/>
     </row>
-    <row r="132" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>4</v>
       </c>
@@ -5253,11 +5533,15 @@
       <c r="E132" s="3">
         <v>87</v>
       </c>
-      <c r="F132" s="5"/>
-      <c r="G132" s="5"/>
+      <c r="F132" s="5">
+        <v>112</v>
+      </c>
+      <c r="G132" s="5">
+        <v>25</v>
+      </c>
       <c r="H132" s="6"/>
     </row>
-    <row r="133" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>4</v>
       </c>
@@ -5273,11 +5557,15 @@
       <c r="E133" s="3">
         <v>320</v>
       </c>
-      <c r="F133" s="5"/>
-      <c r="G133" s="5"/>
+      <c r="F133" s="5">
+        <v>344</v>
+      </c>
+      <c r="G133" s="5">
+        <v>24</v>
+      </c>
       <c r="H133" s="6"/>
     </row>
-    <row r="134" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>4</v>
       </c>
@@ -5293,11 +5581,15 @@
       <c r="E134" s="3">
         <v>242</v>
       </c>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
+      <c r="F134" s="5">
+        <v>275</v>
+      </c>
+      <c r="G134" s="5">
+        <v>33</v>
+      </c>
       <c r="H134" s="6"/>
     </row>
-    <row r="135" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>4</v>
       </c>
@@ -5313,11 +5605,15 @@
       <c r="E135" s="3">
         <v>6</v>
       </c>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
+      <c r="F135" s="5">
+        <v>10</v>
+      </c>
+      <c r="G135" s="5">
+        <v>5</v>
+      </c>
       <c r="H135" s="6"/>
     </row>
-    <row r="136" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>4</v>
       </c>
@@ -5333,11 +5629,15 @@
       <c r="E136" s="3">
         <v>751</v>
       </c>
-      <c r="F136" s="5"/>
-      <c r="G136" s="5"/>
+      <c r="F136" s="5">
+        <v>761</v>
+      </c>
+      <c r="G136" s="5">
+        <v>10</v>
+      </c>
       <c r="H136" s="6"/>
     </row>
-    <row r="137" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>4</v>
       </c>
@@ -5353,11 +5653,15 @@
       <c r="E137" s="3">
         <v>69</v>
       </c>
-      <c r="F137" s="5"/>
-      <c r="G137" s="5"/>
+      <c r="F137" s="5">
+        <v>86</v>
+      </c>
+      <c r="G137" s="5">
+        <v>34</v>
+      </c>
       <c r="H137" s="6"/>
     </row>
-    <row r="138" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>207</v>
       </c>
@@ -5373,11 +5677,15 @@
       <c r="E138" s="3">
         <v>887</v>
       </c>
-      <c r="F138" s="5"/>
-      <c r="G138" s="5"/>
+      <c r="F138" s="5">
+        <v>909</v>
+      </c>
+      <c r="G138" s="5">
+        <v>22</v>
+      </c>
       <c r="H138" s="6"/>
     </row>
-    <row r="139" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>207</v>
       </c>
@@ -5393,11 +5701,15 @@
       <c r="E139" s="3">
         <v>87</v>
       </c>
-      <c r="F139" s="5"/>
-      <c r="G139" s="5"/>
+      <c r="F139" s="5">
+        <v>111</v>
+      </c>
+      <c r="G139" s="5">
+        <v>24</v>
+      </c>
       <c r="H139" s="6"/>
     </row>
-    <row r="140" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>207</v>
       </c>
@@ -5413,11 +5725,15 @@
       <c r="E140" s="3">
         <v>34</v>
       </c>
-      <c r="F140" s="5"/>
-      <c r="G140" s="5"/>
+      <c r="F140" s="5">
+        <v>43</v>
+      </c>
+      <c r="G140" s="5">
+        <v>9</v>
+      </c>
       <c r="H140" s="6"/>
     </row>
-    <row r="141" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>207</v>
       </c>
@@ -5433,11 +5749,15 @@
       <c r="E141" s="3">
         <v>34</v>
       </c>
-      <c r="F141" s="5"/>
-      <c r="G141" s="5"/>
+      <c r="F141" s="5">
+        <v>41</v>
+      </c>
+      <c r="G141" s="5">
+        <v>7</v>
+      </c>
       <c r="H141" s="6"/>
     </row>
-    <row r="142" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>207</v>
       </c>
@@ -5453,11 +5773,15 @@
       <c r="E142" s="3">
         <v>523</v>
       </c>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
+      <c r="F142" s="5">
+        <v>543</v>
+      </c>
+      <c r="G142" s="5">
+        <v>20</v>
+      </c>
       <c r="H142" s="6"/>
     </row>
-    <row r="143" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>207</v>
       </c>
@@ -5473,11 +5797,15 @@
       <c r="E143" s="3">
         <v>92</v>
       </c>
-      <c r="F143" s="5"/>
-      <c r="G143" s="5"/>
+      <c r="F143" s="5">
+        <v>118</v>
+      </c>
+      <c r="G143" s="5">
+        <v>26</v>
+      </c>
       <c r="H143" s="6"/>
     </row>
-    <row r="144" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>207</v>
       </c>
@@ -5493,11 +5821,15 @@
       <c r="E144" s="3">
         <v>1803</v>
       </c>
-      <c r="F144" s="5"/>
-      <c r="G144" s="5"/>
+      <c r="F144" s="5">
+        <v>1826</v>
+      </c>
+      <c r="G144" s="5">
+        <v>23</v>
+      </c>
       <c r="H144" s="6"/>
     </row>
-    <row r="145" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>207</v>
       </c>
@@ -5513,11 +5845,15 @@
       <c r="E145" s="3">
         <v>5311</v>
       </c>
-      <c r="F145" s="5"/>
-      <c r="G145" s="5"/>
+      <c r="F145" s="5">
+        <v>5334</v>
+      </c>
+      <c r="G145" s="5">
+        <v>23</v>
+      </c>
       <c r="H145" s="6"/>
     </row>
-    <row r="146" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>207</v>
       </c>
@@ -5533,11 +5869,15 @@
       <c r="E146" s="3">
         <v>1105</v>
       </c>
-      <c r="F146" s="5"/>
-      <c r="G146" s="5"/>
+      <c r="F146" s="5">
+        <v>1123</v>
+      </c>
+      <c r="G146" s="5">
+        <v>18</v>
+      </c>
       <c r="H146" s="6"/>
     </row>
-    <row r="147" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>207</v>
       </c>
@@ -5557,7 +5897,7 @@
       <c r="G147" s="5"/>
       <c r="H147" s="6"/>
     </row>
-    <row r="148" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>207</v>
       </c>
@@ -5573,11 +5913,15 @@
       <c r="E148" s="3">
         <v>54</v>
       </c>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
+      <c r="F148" s="5">
+        <v>69</v>
+      </c>
+      <c r="G148" s="5">
+        <v>15</v>
+      </c>
       <c r="H148" s="6"/>
     </row>
-    <row r="149" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>207</v>
       </c>
@@ -5593,11 +5937,15 @@
       <c r="E149" s="3">
         <v>37</v>
       </c>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
+      <c r="F149" s="5">
+        <v>43</v>
+      </c>
+      <c r="G149" s="5">
+        <v>6</v>
+      </c>
       <c r="H149" s="6"/>
     </row>
-    <row r="150" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>207</v>
       </c>
@@ -5613,11 +5961,15 @@
       <c r="E150" s="3">
         <v>101</v>
       </c>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
+      <c r="F150" s="5">
+        <v>132</v>
+      </c>
+      <c r="G150" s="5">
+        <v>31</v>
+      </c>
       <c r="H150" s="6"/>
     </row>
-    <row r="151" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>207</v>
       </c>
@@ -5633,11 +5985,15 @@
       <c r="E151" s="3">
         <v>71</v>
       </c>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
+      <c r="F151" s="5">
+        <v>89</v>
+      </c>
+      <c r="G151" s="5">
+        <v>18</v>
+      </c>
       <c r="H151" s="6"/>
     </row>
-    <row r="152" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>207</v>
       </c>
@@ -5653,11 +6009,15 @@
       <c r="E152" s="3">
         <v>2235</v>
       </c>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
+      <c r="F152" s="5">
+        <v>2241</v>
+      </c>
+      <c r="G152" s="5">
+        <v>6</v>
+      </c>
       <c r="H152" s="6"/>
     </row>
-    <row r="153" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>207</v>
       </c>
@@ -5673,11 +6033,15 @@
       <c r="E153" s="3">
         <v>20</v>
       </c>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
+      <c r="F153" s="5">
+        <v>26</v>
+      </c>
+      <c r="G153" s="5">
+        <v>6</v>
+      </c>
       <c r="H153" s="6"/>
     </row>
-    <row r="154" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>207</v>
       </c>
@@ -5693,11 +6057,15 @@
       <c r="E154" s="3">
         <v>491</v>
       </c>
-      <c r="F154" s="5"/>
-      <c r="G154" s="5"/>
+      <c r="F154" s="5">
+        <v>502</v>
+      </c>
+      <c r="G154" s="5">
+        <v>11</v>
+      </c>
       <c r="H154" s="6"/>
     </row>
-    <row r="155" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>207</v>
       </c>
@@ -5717,7 +6085,7 @@
       <c r="G155" s="5"/>
       <c r="H155" s="6"/>
     </row>
-    <row r="156" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>207</v>
       </c>
@@ -5737,7 +6105,7 @@
       <c r="G156" s="5"/>
       <c r="H156" s="6"/>
     </row>
-    <row r="157" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>207</v>
       </c>
@@ -5753,11 +6121,15 @@
       <c r="E157" s="3">
         <v>109</v>
       </c>
-      <c r="F157" s="5"/>
-      <c r="G157" s="5"/>
+      <c r="F157" s="5">
+        <v>144</v>
+      </c>
+      <c r="G157" s="5">
+        <v>35</v>
+      </c>
       <c r="H157" s="6"/>
     </row>
-    <row r="158" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
         <v>207</v>
       </c>
@@ -5773,11 +6145,15 @@
       <c r="E158" s="3">
         <v>29</v>
       </c>
-      <c r="F158" s="5"/>
-      <c r="G158" s="5"/>
+      <c r="F158" s="5">
+        <v>32</v>
+      </c>
+      <c r="G158" s="5">
+        <v>5</v>
+      </c>
       <c r="H158" s="6"/>
     </row>
-    <row r="159" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>207</v>
       </c>
@@ -5793,11 +6169,15 @@
       <c r="E159" s="3">
         <v>71</v>
       </c>
-      <c r="F159" s="5"/>
-      <c r="G159" s="5"/>
+      <c r="F159" s="5">
+        <v>90</v>
+      </c>
+      <c r="G159" s="5">
+        <v>19</v>
+      </c>
       <c r="H159" s="6"/>
     </row>
-    <row r="160" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
         <v>207</v>
       </c>
@@ -5813,11 +6193,15 @@
       <c r="E160" s="3">
         <v>68</v>
       </c>
-      <c r="F160" s="5"/>
-      <c r="G160" s="5"/>
+      <c r="F160" s="5">
+        <v>90</v>
+      </c>
+      <c r="G160" s="5">
+        <v>22</v>
+      </c>
       <c r="H160" s="6"/>
     </row>
-    <row r="161" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>207</v>
       </c>
@@ -5833,11 +6217,15 @@
       <c r="E161" s="3">
         <v>1761</v>
       </c>
-      <c r="F161" s="5"/>
-      <c r="G161" s="5"/>
+      <c r="F161" s="5">
+        <v>1790</v>
+      </c>
+      <c r="G161" s="5">
+        <v>29</v>
+      </c>
       <c r="H161" s="6"/>
     </row>
-    <row r="162" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
         <v>207</v>
       </c>
@@ -5853,11 +6241,15 @@
       <c r="E162" s="3">
         <v>804</v>
       </c>
-      <c r="F162" s="5"/>
-      <c r="G162" s="5"/>
+      <c r="F162" s="5">
+        <v>818</v>
+      </c>
+      <c r="G162" s="5">
+        <v>14</v>
+      </c>
       <c r="H162" s="6"/>
     </row>
-    <row r="163" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>207</v>
       </c>
@@ -5873,11 +6265,15 @@
       <c r="E163" s="3">
         <v>315</v>
       </c>
-      <c r="F163" s="5"/>
-      <c r="G163" s="5"/>
+      <c r="F163" s="5">
+        <v>337</v>
+      </c>
+      <c r="G163" s="5">
+        <v>22</v>
+      </c>
       <c r="H163" s="6"/>
     </row>
-    <row r="164" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
         <v>207</v>
       </c>
@@ -5893,11 +6289,15 @@
       <c r="E164" s="3">
         <v>344</v>
       </c>
-      <c r="F164" s="5"/>
-      <c r="G164" s="5"/>
+      <c r="F164" s="5">
+        <v>351</v>
+      </c>
+      <c r="G164" s="5">
+        <v>7</v>
+      </c>
       <c r="H164" s="6"/>
     </row>
-    <row r="165" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>207</v>
       </c>
@@ -5913,11 +6313,15 @@
       <c r="E165" s="3">
         <v>519</v>
       </c>
-      <c r="F165" s="5"/>
-      <c r="G165" s="5"/>
+      <c r="F165" s="5">
+        <v>544</v>
+      </c>
+      <c r="G165" s="5">
+        <v>25</v>
+      </c>
       <c r="H165" s="6"/>
     </row>
-    <row r="166" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>240</v>
       </c>
@@ -5933,11 +6337,15 @@
       <c r="E166" s="3">
         <v>54</v>
       </c>
-      <c r="F166" s="5"/>
-      <c r="G166" s="5"/>
+      <c r="F166" s="5">
+        <v>76</v>
+      </c>
+      <c r="G166" s="5">
+        <v>22</v>
+      </c>
       <c r="H166" s="6"/>
     </row>
-    <row r="167" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>240</v>
       </c>
@@ -5953,11 +6361,15 @@
       <c r="E167" s="3">
         <v>2264</v>
       </c>
-      <c r="F167" s="5"/>
-      <c r="G167" s="5"/>
+      <c r="F167" s="5">
+        <v>2280</v>
+      </c>
+      <c r="G167" s="5">
+        <v>16</v>
+      </c>
       <c r="H167" s="6"/>
     </row>
-    <row r="168" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>240</v>
       </c>
@@ -5973,11 +6385,15 @@
       <c r="E168" s="3">
         <v>3370</v>
       </c>
-      <c r="F168" s="5"/>
-      <c r="G168" s="5"/>
+      <c r="F168" s="5">
+        <v>3396</v>
+      </c>
+      <c r="G168" s="5">
+        <v>26</v>
+      </c>
       <c r="H168" s="6"/>
     </row>
-    <row r="169" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>240</v>
       </c>
@@ -5993,11 +6409,15 @@
       <c r="E169" s="3">
         <v>2474</v>
       </c>
-      <c r="F169" s="5"/>
-      <c r="G169" s="5"/>
+      <c r="F169" s="5">
+        <v>2488</v>
+      </c>
+      <c r="G169" s="5">
+        <v>14</v>
+      </c>
       <c r="H169" s="6"/>
     </row>
-    <row r="170" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
         <v>240</v>
       </c>
@@ -6013,11 +6433,15 @@
       <c r="E170" s="3">
         <v>27</v>
       </c>
-      <c r="F170" s="5"/>
-      <c r="G170" s="5"/>
+      <c r="F170" s="5">
+        <v>39</v>
+      </c>
+      <c r="G170" s="5">
+        <v>12</v>
+      </c>
       <c r="H170" s="6"/>
     </row>
-    <row r="171" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>240</v>
       </c>
@@ -6037,7 +6461,7 @@
       <c r="G171" s="5"/>
       <c r="H171" s="6"/>
     </row>
-    <row r="172" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
         <v>240</v>
       </c>
@@ -6053,11 +6477,15 @@
       <c r="E172" s="3">
         <v>134</v>
       </c>
-      <c r="F172" s="5"/>
-      <c r="G172" s="5"/>
+      <c r="F172" s="5">
+        <v>165</v>
+      </c>
+      <c r="G172" s="5">
+        <v>31</v>
+      </c>
       <c r="H172" s="6"/>
     </row>
-    <row r="173" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>240</v>
       </c>
@@ -6073,11 +6501,15 @@
       <c r="E173" s="3">
         <v>60</v>
       </c>
-      <c r="F173" s="5"/>
-      <c r="G173" s="5"/>
+      <c r="F173" s="5">
+        <v>74</v>
+      </c>
+      <c r="G173" s="5">
+        <v>14</v>
+      </c>
       <c r="H173" s="6"/>
     </row>
-    <row r="174" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>240</v>
       </c>
@@ -6093,11 +6525,15 @@
       <c r="E174" s="3">
         <v>43</v>
       </c>
-      <c r="F174" s="5"/>
-      <c r="G174" s="5"/>
+      <c r="F174" s="5">
+        <v>52</v>
+      </c>
+      <c r="G174" s="5">
+        <v>9</v>
+      </c>
       <c r="H174" s="6"/>
     </row>
-    <row r="175" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>240</v>
       </c>
@@ -6113,11 +6549,15 @@
       <c r="E175" s="3">
         <v>19</v>
       </c>
-      <c r="F175" s="5"/>
-      <c r="G175" s="5"/>
+      <c r="F175" s="5">
+        <v>20</v>
+      </c>
+      <c r="G175" s="5">
+        <v>5</v>
+      </c>
       <c r="H175" s="6"/>
     </row>
-    <row r="176" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>240</v>
       </c>
@@ -6133,11 +6573,15 @@
       <c r="E176" s="3">
         <v>19</v>
       </c>
-      <c r="F176" s="5"/>
-      <c r="G176" s="5"/>
+      <c r="F176" s="5">
+        <v>22</v>
+      </c>
+      <c r="G176" s="5">
+        <v>5</v>
+      </c>
       <c r="H176" s="6"/>
     </row>
-    <row r="177" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>240</v>
       </c>
@@ -6153,11 +6597,15 @@
       <c r="E177" s="3">
         <v>43</v>
       </c>
-      <c r="F177" s="5"/>
-      <c r="G177" s="5"/>
+      <c r="F177" s="5">
+        <v>54</v>
+      </c>
+      <c r="G177" s="5">
+        <v>11</v>
+      </c>
       <c r="H177" s="6"/>
     </row>
-    <row r="178" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
         <v>240</v>
       </c>
@@ -6173,11 +6621,15 @@
       <c r="E178" s="3">
         <v>345</v>
       </c>
-      <c r="F178" s="5"/>
-      <c r="G178" s="5"/>
+      <c r="F178" s="5">
+        <v>374</v>
+      </c>
+      <c r="G178" s="5">
+        <v>25</v>
+      </c>
       <c r="H178" s="6"/>
     </row>
-    <row r="179" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>240</v>
       </c>
@@ -6193,11 +6645,15 @@
       <c r="E179" s="3">
         <v>41</v>
       </c>
-      <c r="F179" s="5"/>
-      <c r="G179" s="5"/>
+      <c r="F179" s="5">
+        <v>46</v>
+      </c>
+      <c r="G179" s="5">
+        <v>6</v>
+      </c>
       <c r="H179" s="6"/>
     </row>
-    <row r="180" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>240</v>
       </c>
@@ -6213,11 +6669,15 @@
       <c r="E180" s="3">
         <v>1205</v>
       </c>
-      <c r="F180" s="5"/>
-      <c r="G180" s="5"/>
+      <c r="F180" s="5">
+        <v>1217</v>
+      </c>
+      <c r="G180" s="5">
+        <v>12</v>
+      </c>
       <c r="H180" s="6"/>
     </row>
-    <row r="181" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>240</v>
       </c>
@@ -6233,11 +6693,15 @@
       <c r="E181" s="3">
         <v>33</v>
       </c>
-      <c r="F181" s="5"/>
-      <c r="G181" s="5"/>
+      <c r="F181" s="5">
+        <v>41</v>
+      </c>
+      <c r="G181" s="5">
+        <v>8</v>
+      </c>
       <c r="H181" s="6"/>
     </row>
-    <row r="182" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
         <v>240</v>
       </c>
@@ -6253,11 +6717,15 @@
       <c r="E182" s="3">
         <v>66</v>
       </c>
-      <c r="F182" s="5"/>
-      <c r="G182" s="5"/>
+      <c r="F182" s="5">
+        <v>83</v>
+      </c>
+      <c r="G182" s="5">
+        <v>17</v>
+      </c>
       <c r="H182" s="6"/>
     </row>
-    <row r="183" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>240</v>
       </c>
@@ -6273,11 +6741,15 @@
       <c r="E183" s="3">
         <v>32</v>
       </c>
-      <c r="F183" s="5"/>
-      <c r="G183" s="5"/>
+      <c r="F183" s="5">
+        <v>40</v>
+      </c>
+      <c r="G183" s="5">
+        <v>8</v>
+      </c>
       <c r="H183" s="6"/>
     </row>
-    <row r="184" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>240</v>
       </c>
@@ -6293,11 +6765,15 @@
       <c r="E184" s="3">
         <v>19</v>
       </c>
-      <c r="F184" s="5"/>
-      <c r="G184" s="5"/>
+      <c r="F184" s="5">
+        <v>27</v>
+      </c>
+      <c r="G184" s="5">
+        <v>8</v>
+      </c>
       <c r="H184" s="6"/>
     </row>
-    <row r="185" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>240</v>
       </c>
@@ -6313,11 +6789,15 @@
       <c r="E185" s="3">
         <v>0</v>
       </c>
-      <c r="F185" s="5"/>
-      <c r="G185" s="5"/>
+      <c r="F185" s="5">
+        <v>0</v>
+      </c>
+      <c r="G185" s="5">
+        <v>5</v>
+      </c>
       <c r="H185" s="6"/>
     </row>
-    <row r="186" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>240</v>
       </c>
@@ -6333,11 +6813,15 @@
       <c r="E186" s="3">
         <v>55</v>
       </c>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
+      <c r="F186" s="5">
+        <v>69</v>
+      </c>
+      <c r="G186" s="5">
+        <v>14</v>
+      </c>
       <c r="H186" s="6"/>
     </row>
-    <row r="187" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>240</v>
       </c>
@@ -6353,11 +6837,15 @@
       <c r="E187" s="3">
         <v>2577</v>
       </c>
-      <c r="F187" s="5"/>
-      <c r="G187" s="5"/>
+      <c r="F187" s="5">
+        <v>2595</v>
+      </c>
+      <c r="G187" s="5">
+        <v>18</v>
+      </c>
       <c r="H187" s="6"/>
     </row>
-    <row r="188" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
         <v>263</v>
       </c>
@@ -6373,11 +6861,15 @@
       <c r="E188" s="3">
         <v>72</v>
       </c>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
+      <c r="F188" s="5">
+        <v>98</v>
+      </c>
+      <c r="G188" s="5">
+        <v>26</v>
+      </c>
       <c r="H188" s="6"/>
     </row>
-    <row r="189" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>263</v>
       </c>
@@ -6393,11 +6885,15 @@
       <c r="E189" s="3">
         <v>582</v>
       </c>
-      <c r="F189" s="5"/>
-      <c r="G189" s="5"/>
+      <c r="F189" s="5">
+        <v>591</v>
+      </c>
+      <c r="G189" s="5">
+        <v>9</v>
+      </c>
       <c r="H189" s="6"/>
     </row>
-    <row r="190" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
         <v>263</v>
       </c>
@@ -6413,11 +6909,15 @@
       <c r="E190" s="3">
         <v>117</v>
       </c>
-      <c r="F190" s="5"/>
-      <c r="G190" s="5"/>
+      <c r="F190" s="5">
+        <v>120</v>
+      </c>
+      <c r="G190" s="5">
+        <v>5</v>
+      </c>
       <c r="H190" s="6"/>
     </row>
-    <row r="191" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>263</v>
       </c>
@@ -6433,11 +6933,15 @@
       <c r="E191" s="3">
         <v>2042</v>
       </c>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
+      <c r="F191" s="5">
+        <v>2060</v>
+      </c>
+      <c r="G191" s="5">
+        <v>18</v>
+      </c>
       <c r="H191" s="6"/>
     </row>
-    <row r="192" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
         <v>263</v>
       </c>
@@ -6453,11 +6957,15 @@
       <c r="E192" s="3">
         <v>691</v>
       </c>
-      <c r="F192" s="5"/>
-      <c r="G192" s="5"/>
+      <c r="F192" s="5">
+        <v>694</v>
+      </c>
+      <c r="G192" s="5">
+        <v>5</v>
+      </c>
       <c r="H192" s="6"/>
     </row>
-    <row r="193" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>263</v>
       </c>
@@ -6473,11 +6981,15 @@
       <c r="E193" s="3">
         <v>3433</v>
       </c>
-      <c r="F193" s="5"/>
-      <c r="G193" s="5"/>
+      <c r="F193" s="5">
+        <v>3460</v>
+      </c>
+      <c r="G193" s="5">
+        <v>27</v>
+      </c>
       <c r="H193" s="6"/>
     </row>
-    <row r="194" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
         <v>263</v>
       </c>
@@ -6493,11 +7005,15 @@
       <c r="E194" s="3">
         <v>498</v>
       </c>
-      <c r="F194" s="5"/>
-      <c r="G194" s="5"/>
+      <c r="F194" s="5">
+        <v>514</v>
+      </c>
+      <c r="G194" s="5">
+        <v>16</v>
+      </c>
       <c r="H194" s="6"/>
     </row>
-    <row r="195" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>263</v>
       </c>
@@ -6513,11 +7029,15 @@
       <c r="E195" s="3">
         <v>603</v>
       </c>
-      <c r="F195" s="5"/>
-      <c r="G195" s="5"/>
+      <c r="F195" s="5">
+        <v>617</v>
+      </c>
+      <c r="G195" s="5">
+        <v>14</v>
+      </c>
       <c r="H195" s="6"/>
     </row>
-    <row r="196" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>263</v>
       </c>
@@ -6533,11 +7053,15 @@
       <c r="E196" s="3">
         <v>2</v>
       </c>
-      <c r="F196" s="5"/>
-      <c r="G196" s="5"/>
+      <c r="F196" s="5">
+        <v>2</v>
+      </c>
+      <c r="G196" s="5">
+        <v>5</v>
+      </c>
       <c r="H196" s="6"/>
     </row>
-    <row r="197" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>263</v>
       </c>
@@ -6553,11 +7077,15 @@
       <c r="E197" s="3">
         <v>508</v>
       </c>
-      <c r="F197" s="5"/>
-      <c r="G197" s="5"/>
+      <c r="F197" s="5">
+        <v>513</v>
+      </c>
+      <c r="G197" s="5">
+        <v>6</v>
+      </c>
       <c r="H197" s="6"/>
     </row>
-    <row r="198" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
         <v>263</v>
       </c>
@@ -6573,11 +7101,15 @@
       <c r="E198" s="3">
         <v>79</v>
       </c>
-      <c r="F198" s="5"/>
-      <c r="G198" s="5"/>
+      <c r="F198" s="5">
+        <v>82</v>
+      </c>
+      <c r="G198" s="5">
+        <v>5</v>
+      </c>
       <c r="H198" s="6"/>
     </row>
-    <row r="199" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>263</v>
       </c>
@@ -6593,11 +7125,15 @@
       <c r="E199" s="3">
         <v>45</v>
       </c>
-      <c r="F199" s="5"/>
-      <c r="G199" s="5"/>
+      <c r="F199" s="5">
+        <v>55</v>
+      </c>
+      <c r="G199" s="5">
+        <v>10</v>
+      </c>
       <c r="H199" s="6"/>
     </row>
-    <row r="200" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>263</v>
       </c>
@@ -6613,11 +7149,15 @@
       <c r="E200" s="3">
         <v>26</v>
       </c>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
+      <c r="F200" s="5">
+        <v>33</v>
+      </c>
+      <c r="G200" s="5">
+        <v>7</v>
+      </c>
       <c r="H200" s="6"/>
     </row>
-    <row r="201" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>263</v>
       </c>
@@ -6633,11 +7173,15 @@
       <c r="E201" s="3">
         <v>53</v>
       </c>
-      <c r="F201" s="5"/>
-      <c r="G201" s="5"/>
+      <c r="F201" s="5">
+        <v>70</v>
+      </c>
+      <c r="G201" s="5">
+        <v>17</v>
+      </c>
       <c r="H201" s="6"/>
     </row>
-    <row r="202" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>263</v>
       </c>
@@ -6653,11 +7197,15 @@
       <c r="E202" s="3">
         <v>21</v>
       </c>
-      <c r="F202" s="5"/>
-      <c r="G202" s="5"/>
+      <c r="F202" s="5">
+        <v>26</v>
+      </c>
+      <c r="G202" s="5">
+        <v>6</v>
+      </c>
       <c r="H202" s="6"/>
     </row>
-    <row r="203" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>263</v>
       </c>
@@ -6673,11 +7221,15 @@
       <c r="E203" s="3">
         <v>58</v>
       </c>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
+      <c r="F203" s="5">
+        <v>73</v>
+      </c>
+      <c r="G203" s="5">
+        <v>15</v>
+      </c>
       <c r="H203" s="6"/>
     </row>
-    <row r="204" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>263</v>
       </c>
@@ -6693,11 +7245,15 @@
       <c r="E204" s="3">
         <v>7</v>
       </c>
-      <c r="F204" s="5"/>
-      <c r="G204" s="5"/>
+      <c r="F204" s="5">
+        <v>9</v>
+      </c>
+      <c r="G204" s="5">
+        <v>5</v>
+      </c>
       <c r="H204" s="6"/>
     </row>
-    <row r="205" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>263</v>
       </c>
@@ -6713,11 +7269,15 @@
       <c r="E205" s="3">
         <v>26</v>
       </c>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
+      <c r="F205" s="5">
+        <v>61</v>
+      </c>
+      <c r="G205" s="5">
+        <v>35</v>
+      </c>
       <c r="H205" s="6"/>
     </row>
-    <row r="206" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>263</v>
       </c>
@@ -6733,11 +7293,15 @@
       <c r="E206" s="3">
         <v>593</v>
       </c>
-      <c r="F206" s="5"/>
-      <c r="G206" s="5"/>
+      <c r="F206" s="5">
+        <v>610</v>
+      </c>
+      <c r="G206" s="5">
+        <v>17</v>
+      </c>
       <c r="H206" s="6"/>
     </row>
-    <row r="207" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>284</v>
       </c>
@@ -6753,11 +7317,15 @@
       <c r="E207" s="3">
         <v>107</v>
       </c>
-      <c r="F207" s="5"/>
-      <c r="G207" s="5"/>
+      <c r="F207" s="5">
+        <v>114</v>
+      </c>
+      <c r="G207" s="5">
+        <v>7</v>
+      </c>
       <c r="H207" s="6"/>
     </row>
-    <row r="208" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>284</v>
       </c>
@@ -6773,11 +7341,15 @@
       <c r="E208" s="3">
         <v>535</v>
       </c>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
+      <c r="F208" s="5">
+        <v>547</v>
+      </c>
+      <c r="G208" s="5">
+        <v>12</v>
+      </c>
       <c r="H208" s="6"/>
     </row>
-    <row r="209" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
         <v>284</v>
       </c>
@@ -6793,11 +7365,15 @@
       <c r="E209" s="3">
         <v>0</v>
       </c>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
+      <c r="F209" s="5">
+        <v>0</v>
+      </c>
+      <c r="G209" s="5">
+        <v>5</v>
+      </c>
       <c r="H209" s="6"/>
     </row>
-    <row r="210" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>284</v>
       </c>
@@ -6813,11 +7389,15 @@
       <c r="E210" s="3">
         <v>28</v>
       </c>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
+      <c r="F210" s="5">
+        <v>33</v>
+      </c>
+      <c r="G210" s="5">
+        <v>6</v>
+      </c>
       <c r="H210" s="6"/>
     </row>
-    <row r="211" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>284</v>
       </c>
@@ -6833,11 +7413,15 @@
       <c r="E211" s="3">
         <v>71</v>
       </c>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
+      <c r="F211" s="5">
+        <v>91</v>
+      </c>
+      <c r="G211" s="5">
+        <v>20</v>
+      </c>
       <c r="H211" s="6"/>
     </row>
-    <row r="212" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>284</v>
       </c>
@@ -6857,7 +7441,7 @@
       <c r="G212" s="5"/>
       <c r="H212" s="6"/>
     </row>
-    <row r="213" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>284</v>
       </c>
@@ -6873,11 +7457,15 @@
       <c r="E213" s="3">
         <v>63</v>
       </c>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
+      <c r="F213" s="5">
+        <v>73</v>
+      </c>
+      <c r="G213" s="5">
+        <v>10</v>
+      </c>
       <c r="H213" s="6"/>
     </row>
-    <row r="214" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>284</v>
       </c>
@@ -6893,11 +7481,15 @@
       <c r="E214" s="3">
         <v>48</v>
       </c>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
+      <c r="F214" s="5">
+        <v>61</v>
+      </c>
+      <c r="G214" s="5">
+        <v>13</v>
+      </c>
       <c r="H214" s="6"/>
     </row>
-    <row r="215" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>284</v>
       </c>
@@ -6913,11 +7505,15 @@
       <c r="E215" s="3">
         <v>49</v>
       </c>
-      <c r="F215" s="5"/>
-      <c r="G215" s="5"/>
+      <c r="F215" s="5">
+        <v>62</v>
+      </c>
+      <c r="G215" s="5">
+        <v>13</v>
+      </c>
       <c r="H215" s="6"/>
     </row>
-    <row r="216" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>284</v>
       </c>
@@ -6933,11 +7529,15 @@
       <c r="E216" s="3">
         <v>172</v>
       </c>
-      <c r="F216" s="5"/>
-      <c r="G216" s="5"/>
+      <c r="F216" s="5">
+        <v>176</v>
+      </c>
+      <c r="G216" s="5">
+        <v>5</v>
+      </c>
       <c r="H216" s="6"/>
     </row>
-    <row r="217" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>284</v>
       </c>
@@ -6953,11 +7553,15 @@
       <c r="E217" s="3">
         <v>686</v>
       </c>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
+      <c r="F217" s="5">
+        <v>697</v>
+      </c>
+      <c r="G217" s="5">
+        <v>11</v>
+      </c>
       <c r="H217" s="6"/>
     </row>
-    <row r="218" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>284</v>
       </c>
@@ -6977,7 +7581,7 @@
       <c r="G218" s="5"/>
       <c r="H218" s="6"/>
     </row>
-    <row r="219" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
         <v>284</v>
       </c>
@@ -6993,11 +7597,15 @@
       <c r="E219" s="3">
         <v>1487</v>
       </c>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
+      <c r="F219" s="5">
+        <v>1499</v>
+      </c>
+      <c r="G219" s="5">
+        <v>14</v>
+      </c>
       <c r="H219" s="6"/>
     </row>
-    <row r="220" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>284</v>
       </c>
@@ -7013,11 +7621,15 @@
       <c r="E220" s="3">
         <v>13931</v>
       </c>
-      <c r="F220" s="5"/>
-      <c r="G220" s="5"/>
+      <c r="F220" s="5">
+        <v>14062</v>
+      </c>
+      <c r="G220" s="5">
+        <v>327</v>
+      </c>
       <c r="H220" s="6"/>
     </row>
-    <row r="221" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>299</v>
       </c>
@@ -7033,11 +7645,15 @@
       <c r="E221" s="3">
         <v>44</v>
       </c>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
+      <c r="F221" s="5">
+        <v>55</v>
+      </c>
+      <c r="G221" s="5">
+        <v>11</v>
+      </c>
       <c r="H221" s="6"/>
     </row>
-    <row r="222" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
         <v>299</v>
       </c>
@@ -7053,11 +7669,15 @@
       <c r="E222" s="3">
         <v>29</v>
       </c>
-      <c r="F222" s="5"/>
-      <c r="G222" s="5"/>
+      <c r="F222" s="5">
+        <v>41</v>
+      </c>
+      <c r="G222" s="5">
+        <v>12</v>
+      </c>
       <c r="H222" s="6"/>
     </row>
-    <row r="223" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
         <v>299</v>
       </c>
@@ -7073,11 +7693,15 @@
       <c r="E223" s="3">
         <v>127</v>
       </c>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
+      <c r="F223" s="5">
+        <v>129</v>
+      </c>
+      <c r="G223" s="5">
+        <v>5</v>
+      </c>
       <c r="H223" s="6"/>
     </row>
-    <row r="224" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>299</v>
       </c>
@@ -7093,11 +7717,15 @@
       <c r="E224" s="3">
         <v>84</v>
       </c>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
+      <c r="F224" s="5">
+        <v>108</v>
+      </c>
+      <c r="G224" s="5">
+        <v>24</v>
+      </c>
       <c r="H224" s="6"/>
     </row>
-    <row r="225" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>299</v>
       </c>
@@ -7117,7 +7745,7 @@
       <c r="G225" s="5"/>
       <c r="H225" s="6"/>
     </row>
-    <row r="226" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>299</v>
       </c>
@@ -7133,11 +7761,15 @@
       <c r="E226" s="3">
         <v>138</v>
       </c>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
+      <c r="F226" s="5">
+        <v>183</v>
+      </c>
+      <c r="G226" s="5">
+        <v>45</v>
+      </c>
       <c r="H226" s="6"/>
     </row>
-    <row r="227" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
         <v>299</v>
       </c>
@@ -7153,11 +7785,15 @@
       <c r="E227" s="3">
         <v>258</v>
       </c>
-      <c r="F227" s="5"/>
-      <c r="G227" s="5"/>
+      <c r="F227" s="5">
+        <v>278</v>
+      </c>
+      <c r="G227" s="5">
+        <v>20</v>
+      </c>
       <c r="H227" s="6"/>
     </row>
-    <row r="228" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>299</v>
       </c>
@@ -7173,11 +7809,15 @@
       <c r="E228" s="3">
         <v>8</v>
       </c>
-      <c r="F228" s="5"/>
-      <c r="G228" s="5"/>
+      <c r="F228" s="5">
+        <v>16</v>
+      </c>
+      <c r="G228" s="5">
+        <v>8</v>
+      </c>
       <c r="H228" s="6"/>
     </row>
-    <row r="229" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>299</v>
       </c>
@@ -7193,11 +7833,15 @@
       <c r="E229" s="3">
         <v>8</v>
       </c>
-      <c r="F229" s="5"/>
-      <c r="G229" s="5"/>
+      <c r="F229" s="5">
+        <v>17</v>
+      </c>
+      <c r="G229" s="5">
+        <v>9</v>
+      </c>
       <c r="H229" s="6"/>
     </row>
-    <row r="230" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>299</v>
       </c>
@@ -7213,11 +7857,15 @@
       <c r="E230" s="3">
         <v>94</v>
       </c>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
+      <c r="F230" s="5">
+        <v>99</v>
+      </c>
+      <c r="G230" s="5">
+        <v>6</v>
+      </c>
       <c r="H230" s="6"/>
     </row>
-    <row r="231" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>299</v>
       </c>
@@ -7233,11 +7881,15 @@
       <c r="E231" s="3">
         <v>1086</v>
       </c>
-      <c r="F231" s="5"/>
-      <c r="G231" s="5"/>
+      <c r="F231" s="5">
+        <v>1098</v>
+      </c>
+      <c r="G231" s="5">
+        <v>12</v>
+      </c>
       <c r="H231" s="6"/>
     </row>
-    <row r="232" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>299</v>
       </c>
@@ -7253,11 +7905,15 @@
       <c r="E232" s="3">
         <v>1005</v>
       </c>
-      <c r="F232" s="5"/>
-      <c r="G232" s="5"/>
+      <c r="F232" s="5">
+        <v>1049</v>
+      </c>
+      <c r="G232" s="5">
+        <v>44</v>
+      </c>
       <c r="H232" s="6"/>
     </row>
-    <row r="233" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>299</v>
       </c>
@@ -7273,11 +7929,15 @@
       <c r="E233" s="3">
         <v>1326</v>
       </c>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
+      <c r="F233" s="5">
+        <v>1333</v>
+      </c>
+      <c r="G233" s="5">
+        <v>7</v>
+      </c>
       <c r="H233" s="6"/>
     </row>
-    <row r="234" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>299</v>
       </c>
@@ -7293,11 +7953,15 @@
       <c r="E234" s="3">
         <v>325</v>
       </c>
-      <c r="F234" s="5"/>
-      <c r="G234" s="5"/>
+      <c r="F234" s="5">
+        <v>334</v>
+      </c>
+      <c r="G234" s="5">
+        <v>9</v>
+      </c>
       <c r="H234" s="6"/>
     </row>
-    <row r="235" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
         <v>299</v>
       </c>
@@ -7313,11 +7977,15 @@
       <c r="E235" s="3">
         <v>542</v>
       </c>
-      <c r="F235" s="5"/>
-      <c r="G235" s="5"/>
+      <c r="F235" s="5">
+        <v>570</v>
+      </c>
+      <c r="G235" s="5">
+        <v>28</v>
+      </c>
       <c r="H235" s="6"/>
     </row>
-    <row r="236" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>299</v>
       </c>
@@ -7337,7 +8005,7 @@
       <c r="G236" s="5"/>
       <c r="H236" s="6"/>
     </row>
-    <row r="237" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>299</v>
       </c>
@@ -7353,11 +8021,15 @@
       <c r="E237" s="3">
         <v>54</v>
       </c>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
+      <c r="F237" s="5">
+        <v>67</v>
+      </c>
+      <c r="G237" s="5">
+        <v>13</v>
+      </c>
       <c r="H237" s="6"/>
     </row>
-    <row r="238" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>299</v>
       </c>
@@ -7377,7 +8049,7 @@
       <c r="G238" s="5"/>
       <c r="H238" s="6"/>
     </row>
-    <row r="239" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
         <v>318</v>
       </c>
@@ -7393,11 +8065,15 @@
       <c r="E239" s="3">
         <v>32</v>
       </c>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
+      <c r="F239" s="5">
+        <v>37</v>
+      </c>
+      <c r="G239" s="5">
+        <v>6</v>
+      </c>
       <c r="H239" s="6"/>
     </row>
-    <row r="240" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>318</v>
       </c>
@@ -7413,11 +8089,15 @@
       <c r="E240" s="3">
         <v>75</v>
       </c>
-      <c r="F240" s="5"/>
-      <c r="G240" s="5"/>
+      <c r="F240" s="5">
+        <v>95</v>
+      </c>
+      <c r="G240" s="5">
+        <v>20</v>
+      </c>
       <c r="H240" s="6"/>
     </row>
-    <row r="241" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>318</v>
       </c>
@@ -7433,11 +8113,15 @@
       <c r="E241" s="3">
         <v>88</v>
       </c>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
+      <c r="F241" s="5">
+        <v>101</v>
+      </c>
+      <c r="G241" s="5">
+        <v>13</v>
+      </c>
       <c r="H241" s="6"/>
     </row>
-    <row r="242" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>318</v>
       </c>
@@ -7453,11 +8137,15 @@
       <c r="E242" s="3">
         <v>38</v>
       </c>
-      <c r="F242" s="5"/>
-      <c r="G242" s="5"/>
+      <c r="F242" s="5">
+        <v>46</v>
+      </c>
+      <c r="G242" s="5">
+        <v>8</v>
+      </c>
       <c r="H242" s="6"/>
     </row>
-    <row r="243" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
         <v>318</v>
       </c>
@@ -7473,11 +8161,15 @@
       <c r="E243" s="3">
         <v>13</v>
       </c>
-      <c r="F243" s="5"/>
-      <c r="G243" s="5"/>
+      <c r="F243" s="5">
+        <v>13</v>
+      </c>
+      <c r="G243" s="5">
+        <v>5</v>
+      </c>
       <c r="H243" s="6"/>
     </row>
-    <row r="244" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>318</v>
       </c>
@@ -7493,11 +8185,15 @@
       <c r="E244" s="3">
         <v>47</v>
       </c>
-      <c r="F244" s="5"/>
-      <c r="G244" s="5"/>
+      <c r="F244" s="5">
+        <v>61</v>
+      </c>
+      <c r="G244" s="5">
+        <v>14</v>
+      </c>
       <c r="H244" s="6"/>
     </row>
-    <row r="245" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>318</v>
       </c>
@@ -7513,11 +8209,15 @@
       <c r="E245" s="3">
         <v>61</v>
       </c>
-      <c r="F245" s="5"/>
-      <c r="G245" s="5"/>
+      <c r="F245" s="5">
+        <v>71</v>
+      </c>
+      <c r="G245" s="5">
+        <v>10</v>
+      </c>
       <c r="H245" s="6"/>
     </row>
-    <row r="246" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>318</v>
       </c>
@@ -7533,11 +8233,15 @@
       <c r="E246" s="3">
         <v>79</v>
       </c>
-      <c r="F246" s="5"/>
-      <c r="G246" s="5"/>
+      <c r="F246" s="5">
+        <v>101</v>
+      </c>
+      <c r="G246" s="5">
+        <v>22</v>
+      </c>
       <c r="H246" s="6"/>
     </row>
-    <row r="247" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
         <v>318</v>
       </c>
@@ -7557,7 +8261,7 @@
       <c r="G247" s="5"/>
       <c r="H247" s="6"/>
     </row>
-    <row r="248" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>318</v>
       </c>
@@ -7573,11 +8277,15 @@
       <c r="E248" s="3">
         <v>65</v>
       </c>
-      <c r="F248" s="5"/>
-      <c r="G248" s="5"/>
+      <c r="F248" s="5">
+        <v>83</v>
+      </c>
+      <c r="G248" s="5">
+        <v>18</v>
+      </c>
       <c r="H248" s="6"/>
     </row>
-    <row r="249" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
         <v>318</v>
       </c>
@@ -7593,11 +8301,15 @@
       <c r="E249" s="3">
         <v>26</v>
       </c>
-      <c r="F249" s="5"/>
-      <c r="G249" s="5"/>
+      <c r="F249" s="5">
+        <v>35</v>
+      </c>
+      <c r="G249" s="5">
+        <v>9</v>
+      </c>
       <c r="H249" s="6"/>
     </row>
-    <row r="250" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>318</v>
       </c>
@@ -7613,11 +8325,15 @@
       <c r="E250" s="3">
         <v>39</v>
       </c>
-      <c r="F250" s="5"/>
-      <c r="G250" s="5"/>
+      <c r="F250" s="5">
+        <v>50</v>
+      </c>
+      <c r="G250" s="5">
+        <v>11</v>
+      </c>
       <c r="H250" s="6"/>
     </row>
-    <row r="251" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>318</v>
       </c>
@@ -7633,11 +8349,15 @@
       <c r="E251" s="3">
         <v>1450</v>
       </c>
-      <c r="F251" s="5"/>
-      <c r="G251" s="5"/>
+      <c r="F251" s="5">
+        <v>1455</v>
+      </c>
+      <c r="G251" s="5">
+        <v>6</v>
+      </c>
       <c r="H251" s="6"/>
     </row>
-    <row r="252" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>318</v>
       </c>
@@ -7653,11 +8373,15 @@
       <c r="E252" s="3">
         <v>62</v>
       </c>
-      <c r="F252" s="5"/>
-      <c r="G252" s="5"/>
+      <c r="F252" s="5">
+        <v>80</v>
+      </c>
+      <c r="G252" s="5">
+        <v>18</v>
+      </c>
       <c r="H252" s="6"/>
     </row>
-    <row r="253" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
         <v>318</v>
       </c>
@@ -7673,11 +8397,15 @@
       <c r="E253" s="3">
         <v>2451</v>
       </c>
-      <c r="F253" s="5"/>
-      <c r="G253" s="5"/>
+      <c r="F253" s="5">
+        <v>2459</v>
+      </c>
+      <c r="G253" s="5">
+        <v>8</v>
+      </c>
       <c r="H253" s="6"/>
     </row>
-    <row r="254" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>318</v>
       </c>
@@ -7697,7 +8425,7 @@
       <c r="G254" s="5"/>
       <c r="H254" s="6"/>
     </row>
-    <row r="255" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3" t="s">
         <v>1</v>
       </c>
@@ -7713,11 +8441,15 @@
       <c r="E255" s="3">
         <v>3251</v>
       </c>
-      <c r="F255" s="5"/>
-      <c r="G255" s="5"/>
+      <c r="F255" s="5">
+        <v>3273</v>
+      </c>
+      <c r="G255" s="5">
+        <v>22</v>
+      </c>
       <c r="H255" s="6"/>
     </row>
-    <row r="256" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>1</v>
       </c>
@@ -7733,11 +8465,15 @@
       <c r="E256" s="3">
         <v>3151</v>
       </c>
-      <c r="F256" s="5"/>
-      <c r="G256" s="5"/>
+      <c r="F256" s="5">
+        <v>3163</v>
+      </c>
+      <c r="G256" s="5">
+        <v>12</v>
+      </c>
       <c r="H256" s="6"/>
     </row>
-    <row r="257" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
         <v>1</v>
       </c>
@@ -7753,11 +8489,15 @@
       <c r="E257" s="3">
         <v>1185</v>
       </c>
-      <c r="F257" s="5"/>
-      <c r="G257" s="5"/>
+      <c r="F257" s="5">
+        <v>1188</v>
+      </c>
+      <c r="G257" s="5">
+        <v>5</v>
+      </c>
       <c r="H257" s="6"/>
     </row>
-    <row r="258" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>1</v>
       </c>
@@ -7773,11 +8513,15 @@
       <c r="E258" s="3">
         <v>30</v>
       </c>
-      <c r="F258" s="5"/>
-      <c r="G258" s="5"/>
+      <c r="F258" s="5">
+        <v>33</v>
+      </c>
+      <c r="G258" s="5">
+        <v>5</v>
+      </c>
       <c r="H258" s="6"/>
     </row>
-    <row r="259" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>1</v>
       </c>
@@ -7793,11 +8537,15 @@
       <c r="E259" s="3">
         <v>291</v>
       </c>
-      <c r="F259" s="5"/>
-      <c r="G259" s="5"/>
+      <c r="F259" s="5">
+        <v>302</v>
+      </c>
+      <c r="G259" s="5">
+        <v>11</v>
+      </c>
       <c r="H259" s="6"/>
     </row>
-    <row r="260" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>1</v>
       </c>
@@ -7813,11 +8561,15 @@
       <c r="E260" s="3">
         <v>3985</v>
       </c>
-      <c r="F260" s="5"/>
-      <c r="G260" s="5"/>
+      <c r="F260" s="5">
+        <v>3998</v>
+      </c>
+      <c r="G260" s="5">
+        <v>13</v>
+      </c>
       <c r="H260" s="6"/>
     </row>
-    <row r="261" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
         <v>1</v>
       </c>
@@ -7833,11 +8585,15 @@
       <c r="E261" s="3">
         <v>742</v>
       </c>
-      <c r="F261" s="5"/>
-      <c r="G261" s="5"/>
+      <c r="F261" s="5">
+        <v>757</v>
+      </c>
+      <c r="G261" s="5">
+        <v>15</v>
+      </c>
       <c r="H261" s="6"/>
     </row>
-    <row r="262" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>1</v>
       </c>
@@ -7853,11 +8609,15 @@
       <c r="E262" s="3">
         <v>158</v>
       </c>
-      <c r="F262" s="5"/>
-      <c r="G262" s="5"/>
+      <c r="F262" s="5">
+        <v>168</v>
+      </c>
+      <c r="G262" s="5">
+        <v>10</v>
+      </c>
       <c r="H262" s="6"/>
     </row>
-    <row r="263" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
         <v>1</v>
       </c>
@@ -7873,11 +8633,15 @@
       <c r="E263" s="3">
         <v>0</v>
       </c>
-      <c r="F263" s="5"/>
-      <c r="G263" s="5"/>
+      <c r="F263" s="5">
+        <v>0</v>
+      </c>
+      <c r="G263" s="5">
+        <v>5</v>
+      </c>
       <c r="H263" s="6"/>
     </row>
-    <row r="264" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>1</v>
       </c>
@@ -7893,11 +8657,15 @@
       <c r="E264" s="3">
         <v>1154</v>
       </c>
-      <c r="F264" s="5"/>
-      <c r="G264" s="5"/>
+      <c r="F264" s="5">
+        <v>1163</v>
+      </c>
+      <c r="G264" s="5">
+        <v>9</v>
+      </c>
       <c r="H264" s="6"/>
     </row>
-    <row r="265" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
         <v>1</v>
       </c>
@@ -7913,11 +8681,15 @@
       <c r="E265" s="3">
         <v>7</v>
       </c>
-      <c r="F265" s="5"/>
-      <c r="G265" s="5"/>
+      <c r="F265" s="5">
+        <v>8</v>
+      </c>
+      <c r="G265" s="5">
+        <v>5</v>
+      </c>
       <c r="H265" s="6"/>
     </row>
-    <row r="266" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>1</v>
       </c>
@@ -7937,7 +8709,7 @@
       <c r="G266" s="5"/>
       <c r="H266" s="6"/>
     </row>
-    <row r="267" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>1</v>
       </c>
@@ -7953,11 +8725,15 @@
       <c r="E267" s="3">
         <v>99993</v>
       </c>
-      <c r="F267" s="5"/>
-      <c r="G267" s="5"/>
+      <c r="F267" s="5">
+        <v>3</v>
+      </c>
+      <c r="G267" s="5">
+        <v>5</v>
+      </c>
       <c r="H267" s="6"/>
     </row>
-    <row r="268" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>1</v>
       </c>
@@ -7973,11 +8749,15 @@
       <c r="E268" s="3">
         <v>23</v>
       </c>
-      <c r="F268" s="5"/>
-      <c r="G268" s="5"/>
+      <c r="F268" s="5">
+        <v>29</v>
+      </c>
+      <c r="G268" s="5">
+        <v>6</v>
+      </c>
       <c r="H268" s="6"/>
     </row>
-    <row r="269" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>1</v>
       </c>
@@ -7993,11 +8773,15 @@
       <c r="E269" s="3">
         <v>101</v>
       </c>
-      <c r="F269" s="5"/>
-      <c r="G269" s="5"/>
+      <c r="F269" s="5">
+        <v>103</v>
+      </c>
+      <c r="G269" s="5">
+        <v>5</v>
+      </c>
       <c r="H269" s="6"/>
     </row>
-    <row r="270" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>1</v>
       </c>
@@ -8013,11 +8797,15 @@
       <c r="E270" s="3">
         <v>96</v>
       </c>
-      <c r="F270" s="5"/>
-      <c r="G270" s="5"/>
+      <c r="F270" s="5">
+        <v>102</v>
+      </c>
+      <c r="G270" s="5">
+        <v>6</v>
+      </c>
       <c r="H270" s="6"/>
     </row>
-    <row r="271" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
         <v>1</v>
       </c>
@@ -8033,11 +8821,15 @@
       <c r="E271" s="3">
         <v>19</v>
       </c>
-      <c r="F271" s="5"/>
-      <c r="G271" s="5"/>
+      <c r="F271" s="5">
+        <v>21</v>
+      </c>
+      <c r="G271" s="5">
+        <v>5</v>
+      </c>
       <c r="H271" s="6"/>
     </row>
-    <row r="272" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>1</v>
       </c>
@@ -8053,11 +8845,15 @@
       <c r="E272" s="3">
         <v>19</v>
       </c>
-      <c r="F272" s="5"/>
-      <c r="G272" s="5"/>
+      <c r="F272" s="5">
+        <v>19</v>
+      </c>
+      <c r="G272" s="5">
+        <v>5</v>
+      </c>
       <c r="H272" s="6"/>
     </row>
-    <row r="273" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
         <v>1</v>
       </c>
@@ -8073,11 +8869,15 @@
       <c r="E273" s="3">
         <v>71</v>
       </c>
-      <c r="F273" s="5"/>
-      <c r="G273" s="5"/>
+      <c r="F273" s="5">
+        <v>88</v>
+      </c>
+      <c r="G273" s="5">
+        <v>17</v>
+      </c>
       <c r="H273" s="6"/>
     </row>
-    <row r="274" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>1</v>
       </c>
@@ -8093,11 +8893,15 @@
       <c r="E274" s="3">
         <v>77</v>
       </c>
-      <c r="F274" s="5"/>
-      <c r="G274" s="5"/>
+      <c r="F274" s="5">
+        <v>97</v>
+      </c>
+      <c r="G274" s="5">
+        <v>20</v>
+      </c>
       <c r="H274" s="6"/>
     </row>
-    <row r="275" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
         <v>1</v>
       </c>
@@ -8113,11 +8917,15 @@
       <c r="E275" s="3">
         <v>89</v>
       </c>
-      <c r="F275" s="5"/>
-      <c r="G275" s="5"/>
+      <c r="F275" s="5">
+        <v>104</v>
+      </c>
+      <c r="G275" s="5">
+        <v>15</v>
+      </c>
       <c r="H275" s="6"/>
     </row>
-    <row r="276" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>1</v>
       </c>
@@ -8133,11 +8941,15 @@
       <c r="E276" s="3">
         <v>86</v>
       </c>
-      <c r="F276" s="5"/>
-      <c r="G276" s="5"/>
+      <c r="F276" s="5">
+        <v>105</v>
+      </c>
+      <c r="G276" s="5">
+        <v>19</v>
+      </c>
       <c r="H276" s="6"/>
     </row>
-    <row r="277" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
         <v>357</v>
       </c>
@@ -8153,11 +8965,15 @@
       <c r="E277" s="3">
         <v>67</v>
       </c>
-      <c r="F277" s="5"/>
-      <c r="G277" s="5"/>
+      <c r="F277" s="5">
+        <v>88</v>
+      </c>
+      <c r="G277" s="5">
+        <v>21</v>
+      </c>
       <c r="H277" s="6"/>
     </row>
-    <row r="278" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>357</v>
       </c>
@@ -8173,11 +8989,15 @@
       <c r="E278" s="3">
         <v>82</v>
       </c>
-      <c r="F278" s="5"/>
-      <c r="G278" s="5"/>
+      <c r="F278" s="5">
+        <v>99</v>
+      </c>
+      <c r="G278" s="5">
+        <v>17</v>
+      </c>
       <c r="H278" s="6"/>
     </row>
-    <row r="279" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
         <v>357</v>
       </c>
@@ -8193,11 +9013,15 @@
       <c r="E279" s="3">
         <v>23</v>
       </c>
-      <c r="F279" s="5"/>
-      <c r="G279" s="5"/>
+      <c r="F279" s="5">
+        <v>32</v>
+      </c>
+      <c r="G279" s="5">
+        <v>9</v>
+      </c>
       <c r="H279" s="6"/>
     </row>
-    <row r="280" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>357</v>
       </c>
@@ -8213,11 +9037,15 @@
       <c r="E280" s="3">
         <v>174</v>
       </c>
-      <c r="F280" s="5"/>
-      <c r="G280" s="5"/>
+      <c r="F280" s="5">
+        <v>178</v>
+      </c>
+      <c r="G280" s="5">
+        <v>5</v>
+      </c>
       <c r="H280" s="6"/>
     </row>
-    <row r="281" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
         <v>357</v>
       </c>
@@ -8237,7 +9065,7 @@
       <c r="G281" s="5"/>
       <c r="H281" s="6"/>
     </row>
-    <row r="282" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>357</v>
       </c>
@@ -8253,11 +9081,15 @@
       <c r="E282" s="3">
         <v>832</v>
       </c>
-      <c r="F282" s="5"/>
-      <c r="G282" s="5"/>
+      <c r="F282" s="5">
+        <v>854</v>
+      </c>
+      <c r="G282" s="5">
+        <v>22</v>
+      </c>
       <c r="H282" s="6"/>
     </row>
-    <row r="283" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
         <v>364</v>
       </c>
@@ -8273,11 +9105,15 @@
       <c r="E283" s="3">
         <v>33</v>
       </c>
-      <c r="F283" s="5"/>
-      <c r="G283" s="5"/>
+      <c r="F283" s="5">
+        <v>40</v>
+      </c>
+      <c r="G283" s="5">
+        <v>7</v>
+      </c>
       <c r="H283" s="6"/>
     </row>
-    <row r="284" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>364</v>
       </c>
@@ -8293,11 +9129,15 @@
       <c r="E284" s="3">
         <v>51</v>
       </c>
-      <c r="F284" s="5"/>
-      <c r="G284" s="5"/>
+      <c r="F284" s="5">
+        <v>59</v>
+      </c>
+      <c r="G284" s="5">
+        <v>8</v>
+      </c>
       <c r="H284" s="6"/>
     </row>
-    <row r="285" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
         <v>364</v>
       </c>
@@ -8313,11 +9153,15 @@
       <c r="E285" s="3">
         <v>29</v>
       </c>
-      <c r="F285" s="5"/>
-      <c r="G285" s="5"/>
+      <c r="F285" s="5">
+        <v>38</v>
+      </c>
+      <c r="G285" s="5">
+        <v>9</v>
+      </c>
       <c r="H285" s="6"/>
     </row>
-    <row r="286" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>364</v>
       </c>
@@ -8333,11 +9177,15 @@
       <c r="E286" s="3">
         <v>10</v>
       </c>
-      <c r="F286" s="5"/>
-      <c r="G286" s="5"/>
+      <c r="F286" s="5">
+        <v>13</v>
+      </c>
+      <c r="G286" s="5">
+        <v>5</v>
+      </c>
       <c r="H286" s="6"/>
     </row>
-    <row r="287" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
         <v>364</v>
       </c>
@@ -8353,11 +9201,15 @@
       <c r="E287" s="3">
         <v>676</v>
       </c>
-      <c r="F287" s="5"/>
-      <c r="G287" s="5"/>
+      <c r="F287" s="5">
+        <v>679</v>
+      </c>
+      <c r="G287" s="5">
+        <v>5</v>
+      </c>
       <c r="H287" s="6"/>
     </row>
-    <row r="288" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>364</v>
       </c>
@@ -8373,11 +9225,15 @@
       <c r="E288" s="3">
         <v>25</v>
       </c>
-      <c r="F288" s="5"/>
-      <c r="G288" s="5"/>
+      <c r="F288" s="5">
+        <v>33</v>
+      </c>
+      <c r="G288" s="5">
+        <v>8</v>
+      </c>
       <c r="H288" s="6"/>
     </row>
-    <row r="289" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>364</v>
       </c>
@@ -8393,11 +9249,15 @@
       <c r="E289" s="3">
         <v>251</v>
       </c>
-      <c r="F289" s="5"/>
-      <c r="G289" s="5"/>
+      <c r="F289" s="5">
+        <v>254</v>
+      </c>
+      <c r="G289" s="5">
+        <v>5</v>
+      </c>
       <c r="H289" s="6"/>
     </row>
-    <row r="290" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>364</v>
       </c>
@@ -8413,11 +9273,15 @@
       <c r="E290" s="3">
         <v>40</v>
       </c>
-      <c r="F290" s="5"/>
-      <c r="G290" s="5"/>
+      <c r="F290" s="5">
+        <v>49</v>
+      </c>
+      <c r="G290" s="5">
+        <v>9</v>
+      </c>
       <c r="H290" s="6"/>
     </row>
-    <row r="291" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>364</v>
       </c>
@@ -8433,11 +9297,15 @@
       <c r="E291" s="3">
         <v>67</v>
       </c>
-      <c r="F291" s="5"/>
-      <c r="G291" s="5"/>
+      <c r="F291" s="5">
+        <v>82</v>
+      </c>
+      <c r="G291" s="5">
+        <v>15</v>
+      </c>
       <c r="H291" s="6"/>
     </row>
-    <row r="292" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>364</v>
       </c>
@@ -8453,11 +9321,15 @@
       <c r="E292" s="3">
         <v>1320</v>
       </c>
-      <c r="F292" s="5"/>
-      <c r="G292" s="5"/>
+      <c r="F292" s="5">
+        <v>1333</v>
+      </c>
+      <c r="G292" s="5">
+        <v>13</v>
+      </c>
       <c r="H292" s="6"/>
     </row>
-    <row r="293" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
         <v>364</v>
       </c>
@@ -8473,11 +9345,15 @@
       <c r="E293" s="3">
         <v>247</v>
       </c>
-      <c r="F293" s="5"/>
-      <c r="G293" s="5"/>
+      <c r="F293" s="5">
+        <v>250</v>
+      </c>
+      <c r="G293" s="5">
+        <v>5</v>
+      </c>
       <c r="H293" s="6"/>
     </row>
-    <row r="294" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>364</v>
       </c>
@@ -8493,11 +9369,15 @@
       <c r="E294" s="3">
         <v>17</v>
       </c>
-      <c r="F294" s="5"/>
-      <c r="G294" s="5"/>
+      <c r="F294" s="5">
+        <v>21</v>
+      </c>
+      <c r="G294" s="5">
+        <v>5</v>
+      </c>
       <c r="H294" s="6"/>
     </row>
-    <row r="295" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
         <v>364</v>
       </c>
@@ -8513,11 +9393,15 @@
       <c r="E295" s="3">
         <v>56</v>
       </c>
-      <c r="F295" s="5"/>
-      <c r="G295" s="5"/>
+      <c r="F295" s="5">
+        <v>73</v>
+      </c>
+      <c r="G295" s="5">
+        <v>17</v>
+      </c>
       <c r="H295" s="6"/>
     </row>
-    <row r="296" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>364</v>
       </c>
@@ -8533,11 +9417,15 @@
       <c r="E296" s="3">
         <v>658</v>
       </c>
-      <c r="F296" s="5"/>
-      <c r="G296" s="5"/>
+      <c r="F296" s="5">
+        <v>664</v>
+      </c>
+      <c r="G296" s="5">
+        <v>6</v>
+      </c>
       <c r="H296" s="6"/>
     </row>
-    <row r="297" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
         <v>364</v>
       </c>
@@ -8553,11 +9441,15 @@
       <c r="E297" s="3">
         <v>1050</v>
       </c>
-      <c r="F297" s="5"/>
-      <c r="G297" s="5"/>
+      <c r="F297" s="5">
+        <v>1067</v>
+      </c>
+      <c r="G297" s="5">
+        <v>17</v>
+      </c>
       <c r="H297" s="6"/>
     </row>
-    <row r="298" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>364</v>
       </c>
@@ -8573,11 +9465,15 @@
       <c r="E298" s="3">
         <v>29</v>
       </c>
-      <c r="F298" s="5"/>
-      <c r="G298" s="5"/>
+      <c r="F298" s="5">
+        <v>32</v>
+      </c>
+      <c r="G298" s="5">
+        <v>5</v>
+      </c>
       <c r="H298" s="6"/>
     </row>
-    <row r="299" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
         <v>364</v>
       </c>
@@ -8593,11 +9489,15 @@
       <c r="E299" s="3">
         <v>11</v>
       </c>
-      <c r="F299" s="5"/>
-      <c r="G299" s="5"/>
+      <c r="F299" s="5">
+        <v>13</v>
+      </c>
+      <c r="G299" s="5">
+        <v>5</v>
+      </c>
       <c r="H299" s="6"/>
     </row>
-    <row r="300" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>364</v>
       </c>
@@ -8613,11 +9513,15 @@
       <c r="E300" s="3">
         <v>390</v>
       </c>
-      <c r="F300" s="5"/>
-      <c r="G300" s="5"/>
+      <c r="F300" s="5">
+        <v>400</v>
+      </c>
+      <c r="G300" s="5">
+        <v>10</v>
+      </c>
       <c r="H300" s="6"/>
     </row>
-    <row r="301" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
         <v>364</v>
       </c>
@@ -8633,11 +9537,15 @@
       <c r="E301" s="3">
         <v>23</v>
       </c>
-      <c r="F301" s="5"/>
-      <c r="G301" s="5"/>
+      <c r="F301" s="5">
+        <v>29</v>
+      </c>
+      <c r="G301" s="5">
+        <v>6</v>
+      </c>
       <c r="H301" s="6"/>
     </row>
-    <row r="302" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>364</v>
       </c>
@@ -8653,11 +9561,15 @@
       <c r="E302" s="3">
         <v>229</v>
       </c>
-      <c r="F302" s="5"/>
-      <c r="G302" s="5"/>
+      <c r="F302" s="5">
+        <v>253</v>
+      </c>
+      <c r="G302" s="5">
+        <v>24</v>
+      </c>
       <c r="H302" s="6"/>
     </row>
-    <row r="303" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>364</v>
       </c>
@@ -8673,11 +9585,15 @@
       <c r="E303" s="3">
         <v>1199</v>
       </c>
-      <c r="F303" s="5"/>
-      <c r="G303" s="5"/>
+      <c r="F303" s="5">
+        <v>1212</v>
+      </c>
+      <c r="G303" s="5">
+        <v>13</v>
+      </c>
       <c r="H303" s="6"/>
     </row>
-    <row r="304" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>364</v>
       </c>
@@ -8693,11 +9609,15 @@
       <c r="E304" s="3">
         <v>70</v>
       </c>
-      <c r="F304" s="5"/>
-      <c r="G304" s="5"/>
+      <c r="F304" s="5">
+        <v>75</v>
+      </c>
+      <c r="G304" s="5">
+        <v>6</v>
+      </c>
       <c r="H304" s="6"/>
     </row>
-    <row r="305" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
         <v>364</v>
       </c>
@@ -8713,11 +9633,15 @@
       <c r="E305" s="3">
         <v>97</v>
       </c>
-      <c r="F305" s="5"/>
-      <c r="G305" s="5"/>
+      <c r="F305" s="5">
+        <v>99</v>
+      </c>
+      <c r="G305" s="5">
+        <v>5</v>
+      </c>
       <c r="H305" s="6"/>
     </row>
-    <row r="306" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>364</v>
       </c>
@@ -8733,11 +9657,15 @@
       <c r="E306" s="3">
         <v>4</v>
       </c>
-      <c r="F306" s="5"/>
-      <c r="G306" s="5"/>
+      <c r="F306" s="5">
+        <v>5</v>
+      </c>
+      <c r="G306" s="5">
+        <v>5</v>
+      </c>
       <c r="H306" s="6"/>
     </row>
-    <row r="307" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
         <v>364</v>
       </c>
@@ -8753,11 +9681,15 @@
       <c r="E307" s="3">
         <v>23</v>
       </c>
-      <c r="F307" s="5"/>
-      <c r="G307" s="5"/>
+      <c r="F307" s="5">
+        <v>35</v>
+      </c>
+      <c r="G307" s="5">
+        <v>12</v>
+      </c>
       <c r="H307" s="6"/>
     </row>
-    <row r="308" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>364</v>
       </c>
@@ -8773,11 +9705,15 @@
       <c r="E308" s="3">
         <v>1</v>
       </c>
-      <c r="F308" s="5"/>
-      <c r="G308" s="5"/>
+      <c r="F308" s="5">
+        <v>1</v>
+      </c>
+      <c r="G308" s="5">
+        <v>5</v>
+      </c>
       <c r="H308" s="6"/>
     </row>
-    <row r="309" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>364</v>
       </c>
@@ -8793,11 +9729,15 @@
       <c r="E309" s="3">
         <v>1196</v>
       </c>
-      <c r="F309" s="5"/>
-      <c r="G309" s="5"/>
+      <c r="F309" s="5">
+        <v>1206</v>
+      </c>
+      <c r="G309" s="5">
+        <v>10</v>
+      </c>
       <c r="H309" s="6"/>
     </row>
-    <row r="310" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>364</v>
       </c>
@@ -8813,11 +9753,15 @@
       <c r="E310" s="3">
         <v>193</v>
       </c>
-      <c r="F310" s="5"/>
-      <c r="G310" s="5"/>
+      <c r="F310" s="5">
+        <v>197</v>
+      </c>
+      <c r="G310" s="5">
+        <v>5</v>
+      </c>
       <c r="H310" s="6"/>
     </row>
-    <row r="311" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
         <v>364</v>
       </c>
@@ -8833,11 +9777,15 @@
       <c r="E311" s="3">
         <v>9</v>
       </c>
-      <c r="F311" s="5"/>
-      <c r="G311" s="5"/>
+      <c r="F311" s="5">
+        <v>11</v>
+      </c>
+      <c r="G311" s="5">
+        <v>5</v>
+      </c>
       <c r="H311" s="6"/>
     </row>
-    <row r="312" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>7</v>
       </c>
@@ -8853,11 +9801,15 @@
       <c r="E312" s="3">
         <v>115</v>
       </c>
-      <c r="F312" s="5"/>
-      <c r="G312" s="5"/>
+      <c r="F312" s="5">
+        <v>127</v>
+      </c>
+      <c r="G312" s="5">
+        <v>12</v>
+      </c>
       <c r="H312" s="6"/>
     </row>
-    <row r="313" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
         <v>7</v>
       </c>
@@ -8873,11 +9825,15 @@
       <c r="E313" s="3">
         <v>629</v>
       </c>
-      <c r="F313" s="5"/>
-      <c r="G313" s="5"/>
+      <c r="F313" s="5">
+        <v>643</v>
+      </c>
+      <c r="G313" s="5">
+        <v>14</v>
+      </c>
       <c r="H313" s="6"/>
     </row>
-    <row r="314" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>7</v>
       </c>
@@ -8893,11 +9849,15 @@
       <c r="E314" s="3">
         <v>50</v>
       </c>
-      <c r="F314" s="5"/>
-      <c r="G314" s="5"/>
+      <c r="F314" s="5">
+        <v>80</v>
+      </c>
+      <c r="G314" s="5">
+        <v>30</v>
+      </c>
       <c r="H314" s="6"/>
     </row>
-    <row r="315" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3" t="s">
         <v>7</v>
       </c>
@@ -8913,11 +9873,15 @@
       <c r="E315" s="3">
         <v>421</v>
       </c>
-      <c r="F315" s="5"/>
-      <c r="G315" s="5"/>
+      <c r="F315" s="5">
+        <v>474</v>
+      </c>
+      <c r="G315" s="5">
+        <v>53</v>
+      </c>
       <c r="H315" s="6"/>
     </row>
-    <row r="316" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>7</v>
       </c>
@@ -8933,11 +9897,15 @@
       <c r="E316" s="3">
         <v>185</v>
       </c>
-      <c r="F316" s="5"/>
-      <c r="G316" s="5"/>
+      <c r="F316" s="5">
+        <v>192</v>
+      </c>
+      <c r="G316" s="5">
+        <v>7</v>
+      </c>
       <c r="H316" s="6"/>
     </row>
-    <row r="317" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>7</v>
       </c>
@@ -8953,11 +9921,15 @@
       <c r="E317" s="3">
         <v>1</v>
       </c>
-      <c r="F317" s="5"/>
-      <c r="G317" s="5"/>
+      <c r="F317" s="5">
+        <v>1</v>
+      </c>
+      <c r="G317" s="5">
+        <v>5</v>
+      </c>
       <c r="H317" s="6"/>
     </row>
-    <row r="318" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>7</v>
       </c>
@@ -8973,11 +9945,15 @@
       <c r="E318" s="3">
         <v>1361</v>
       </c>
-      <c r="F318" s="5"/>
-      <c r="G318" s="5"/>
+      <c r="F318" s="5">
+        <v>1377</v>
+      </c>
+      <c r="G318" s="5">
+        <v>16</v>
+      </c>
       <c r="H318" s="6"/>
     </row>
-    <row r="319" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
         <v>7</v>
       </c>
@@ -8993,11 +9969,15 @@
       <c r="E319" s="3">
         <v>47</v>
       </c>
-      <c r="F319" s="5"/>
-      <c r="G319" s="5"/>
+      <c r="F319" s="5">
+        <v>58</v>
+      </c>
+      <c r="G319" s="5">
+        <v>11</v>
+      </c>
       <c r="H319" s="6"/>
     </row>
-    <row r="320" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>7</v>
       </c>
@@ -9013,11 +9993,15 @@
       <c r="E320" s="3">
         <v>8</v>
       </c>
-      <c r="F320" s="5"/>
-      <c r="G320" s="5"/>
+      <c r="F320" s="5">
+        <v>20</v>
+      </c>
+      <c r="G320" s="5">
+        <v>12</v>
+      </c>
       <c r="H320" s="6"/>
     </row>
-    <row r="321" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
         <v>7</v>
       </c>
@@ -9033,11 +10017,15 @@
       <c r="E321" s="3">
         <v>745</v>
       </c>
-      <c r="F321" s="5"/>
-      <c r="G321" s="5"/>
+      <c r="F321" s="5">
+        <v>750</v>
+      </c>
+      <c r="G321" s="5">
+        <v>6</v>
+      </c>
       <c r="H321" s="6"/>
     </row>
-    <row r="322" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>7</v>
       </c>
@@ -9053,11 +10041,15 @@
       <c r="E322" s="3">
         <v>26</v>
       </c>
-      <c r="F322" s="5"/>
-      <c r="G322" s="5"/>
+      <c r="F322" s="5">
+        <v>32</v>
+      </c>
+      <c r="G322" s="5">
+        <v>6</v>
+      </c>
       <c r="H322" s="6"/>
     </row>
-    <row r="323" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
         <v>7</v>
       </c>
@@ -9073,11 +10065,15 @@
       <c r="E323" s="3">
         <v>286</v>
       </c>
-      <c r="F323" s="5"/>
-      <c r="G323" s="5"/>
+      <c r="F323" s="5">
+        <v>297</v>
+      </c>
+      <c r="G323" s="5">
+        <v>11</v>
+      </c>
       <c r="H323" s="6"/>
     </row>
-    <row r="324" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>7</v>
       </c>
@@ -9097,7 +10093,7 @@
       <c r="G324" s="5"/>
       <c r="H324" s="6"/>
     </row>
-    <row r="325" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
         <v>7</v>
       </c>
@@ -9113,11 +10109,15 @@
       <c r="E325" s="3">
         <v>60</v>
       </c>
-      <c r="F325" s="5"/>
-      <c r="G325" s="5"/>
+      <c r="F325" s="5">
+        <v>76</v>
+      </c>
+      <c r="G325" s="5">
+        <v>16</v>
+      </c>
       <c r="H325" s="6"/>
     </row>
-    <row r="326" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>7</v>
       </c>
@@ -9133,11 +10133,15 @@
       <c r="E326" s="3">
         <v>25</v>
       </c>
-      <c r="F326" s="5"/>
-      <c r="G326" s="5"/>
+      <c r="F326" s="5">
+        <v>30</v>
+      </c>
+      <c r="G326" s="5">
+        <v>5</v>
+      </c>
       <c r="H326" s="6"/>
     </row>
-    <row r="327" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
         <v>7</v>
       </c>
@@ -9153,11 +10157,15 @@
       <c r="E327" s="3">
         <v>167</v>
       </c>
-      <c r="F327" s="5"/>
-      <c r="G327" s="5"/>
+      <c r="F327" s="5">
+        <v>171</v>
+      </c>
+      <c r="G327" s="5">
+        <v>5</v>
+      </c>
       <c r="H327" s="6"/>
     </row>
-    <row r="328" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>7</v>
       </c>
@@ -9173,11 +10181,15 @@
       <c r="E328" s="3">
         <v>1345</v>
       </c>
-      <c r="F328" s="5"/>
-      <c r="G328" s="5"/>
+      <c r="F328" s="5">
+        <v>1352</v>
+      </c>
+      <c r="G328" s="5">
+        <v>7</v>
+      </c>
       <c r="H328" s="6"/>
     </row>
-    <row r="329" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
         <v>7</v>
       </c>
@@ -9197,7 +10209,7 @@
       <c r="G329" s="5"/>
       <c r="H329" s="6"/>
     </row>
-    <row r="330" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>7</v>
       </c>
@@ -9213,11 +10225,15 @@
       <c r="E330" s="3">
         <v>125</v>
       </c>
-      <c r="F330" s="5"/>
-      <c r="G330" s="5"/>
+      <c r="F330" s="5">
+        <v>132</v>
+      </c>
+      <c r="G330" s="5">
+        <v>7</v>
+      </c>
       <c r="H330" s="6"/>
     </row>
-    <row r="331" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
         <v>7</v>
       </c>
@@ -9233,11 +10249,15 @@
       <c r="E331" s="3">
         <v>104</v>
       </c>
-      <c r="F331" s="5"/>
-      <c r="G331" s="5"/>
+      <c r="F331" s="5">
+        <v>109</v>
+      </c>
+      <c r="G331" s="5">
+        <v>6</v>
+      </c>
       <c r="H331" s="6"/>
     </row>
-    <row r="332" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>7</v>
       </c>
@@ -9253,11 +10273,15 @@
       <c r="E332" s="3">
         <v>38</v>
       </c>
-      <c r="F332" s="5"/>
-      <c r="G332" s="5"/>
+      <c r="F332" s="5">
+        <v>47</v>
+      </c>
+      <c r="G332" s="5">
+        <v>9</v>
+      </c>
       <c r="H332" s="6"/>
     </row>
-    <row r="333" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
         <v>7</v>
       </c>
@@ -9277,7 +10301,7 @@
       <c r="G333" s="5"/>
       <c r="H333" s="6"/>
     </row>
-    <row r="334" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>416</v>
       </c>
@@ -9293,11 +10317,15 @@
       <c r="E334" s="3">
         <v>357</v>
       </c>
-      <c r="F334" s="5"/>
-      <c r="G334" s="5"/>
+      <c r="F334" s="5">
+        <v>360</v>
+      </c>
+      <c r="G334" s="5">
+        <v>5</v>
+      </c>
       <c r="H334" s="6"/>
     </row>
-    <row r="335" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
         <v>416</v>
       </c>
@@ -9313,11 +10341,15 @@
       <c r="E335" s="3">
         <v>855</v>
       </c>
-      <c r="F335" s="5"/>
-      <c r="G335" s="5"/>
+      <c r="F335" s="5">
+        <v>873</v>
+      </c>
+      <c r="G335" s="5">
+        <v>18</v>
+      </c>
       <c r="H335" s="6"/>
     </row>
-    <row r="336" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>416</v>
       </c>
@@ -9333,11 +10365,15 @@
       <c r="E336" s="3">
         <v>2448</v>
       </c>
-      <c r="F336" s="5"/>
-      <c r="G336" s="5"/>
+      <c r="F336" s="5">
+        <v>2455</v>
+      </c>
+      <c r="G336" s="5">
+        <v>7</v>
+      </c>
       <c r="H336" s="6"/>
     </row>
-    <row r="337" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>416</v>
       </c>
@@ -9357,7 +10393,7 @@
       <c r="G337" s="5"/>
       <c r="H337" s="6"/>
     </row>
-    <row r="338" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
         <v>416</v>
       </c>
@@ -9373,11 +10409,15 @@
       <c r="E338" s="3">
         <v>55</v>
       </c>
-      <c r="F338" s="5"/>
-      <c r="G338" s="5"/>
+      <c r="F338" s="5">
+        <v>72</v>
+      </c>
+      <c r="G338" s="5">
+        <v>17</v>
+      </c>
       <c r="H338" s="6"/>
     </row>
-    <row r="339" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>416</v>
       </c>
@@ -9393,11 +10433,15 @@
       <c r="E339" s="3">
         <v>2102</v>
       </c>
-      <c r="F339" s="5"/>
-      <c r="G339" s="5"/>
+      <c r="F339" s="5">
+        <v>2127</v>
+      </c>
+      <c r="G339" s="5">
+        <v>25</v>
+      </c>
       <c r="H339" s="6"/>
     </row>
-    <row r="340" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
         <v>416</v>
       </c>
@@ -9413,11 +10457,15 @@
       <c r="E340" s="3">
         <v>1674</v>
       </c>
-      <c r="F340" s="5"/>
-      <c r="G340" s="5"/>
+      <c r="F340" s="5">
+        <v>1686</v>
+      </c>
+      <c r="G340" s="5">
+        <v>12</v>
+      </c>
       <c r="H340" s="6"/>
     </row>
-    <row r="341" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>416</v>
       </c>
@@ -9433,11 +10481,15 @@
       <c r="E341" s="3">
         <v>54</v>
       </c>
-      <c r="F341" s="5"/>
-      <c r="G341" s="5"/>
+      <c r="F341" s="5">
+        <v>69</v>
+      </c>
+      <c r="G341" s="5">
+        <v>15</v>
+      </c>
       <c r="H341" s="6"/>
     </row>
-    <row r="342" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
         <v>416</v>
       </c>
@@ -9453,11 +10505,15 @@
       <c r="E342" s="3">
         <v>277</v>
       </c>
-      <c r="F342" s="5"/>
-      <c r="G342" s="5"/>
+      <c r="F342" s="5">
+        <v>294</v>
+      </c>
+      <c r="G342" s="5">
+        <v>17</v>
+      </c>
       <c r="H342" s="6"/>
     </row>
-    <row r="343" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
         <v>416</v>
       </c>
@@ -9477,7 +10533,7 @@
       <c r="G343" s="5"/>
       <c r="H343" s="6"/>
     </row>
-    <row r="344" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
         <v>416</v>
       </c>
@@ -9493,11 +10549,15 @@
       <c r="E344" s="3">
         <v>1073</v>
       </c>
-      <c r="F344" s="5"/>
-      <c r="G344" s="5"/>
+      <c r="F344" s="5">
+        <v>1087</v>
+      </c>
+      <c r="G344" s="5">
+        <v>14</v>
+      </c>
       <c r="H344" s="6"/>
     </row>
-    <row r="345" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>416</v>
       </c>
@@ -9513,11 +10573,15 @@
       <c r="E345" s="3">
         <v>857</v>
       </c>
-      <c r="F345" s="5"/>
-      <c r="G345" s="5"/>
+      <c r="F345" s="5">
+        <v>869</v>
+      </c>
+      <c r="G345" s="5">
+        <v>12</v>
+      </c>
       <c r="H345" s="6"/>
     </row>
-    <row r="346" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
         <v>416</v>
       </c>
@@ -9537,7 +10601,7 @@
       <c r="G346" s="5"/>
       <c r="H346" s="6"/>
     </row>
-    <row r="347" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>416</v>
       </c>
@@ -9553,11 +10617,15 @@
       <c r="E347" s="3">
         <v>1112</v>
       </c>
-      <c r="F347" s="5"/>
-      <c r="G347" s="5"/>
+      <c r="F347" s="5">
+        <v>1118</v>
+      </c>
+      <c r="G347" s="5">
+        <v>6</v>
+      </c>
       <c r="H347" s="6"/>
     </row>
-    <row r="348" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
         <v>416</v>
       </c>
@@ -9573,11 +10641,15 @@
       <c r="E348" s="3">
         <v>336</v>
       </c>
-      <c r="F348" s="5"/>
-      <c r="G348" s="5"/>
+      <c r="F348" s="5">
+        <v>339</v>
+      </c>
+      <c r="G348" s="5">
+        <v>5</v>
+      </c>
       <c r="H348" s="6"/>
     </row>
-    <row r="349" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
         <v>416</v>
       </c>
@@ -9593,11 +10665,15 @@
       <c r="E349" s="3">
         <v>172</v>
       </c>
-      <c r="F349" s="5"/>
-      <c r="G349" s="5"/>
+      <c r="F349" s="5">
+        <v>178</v>
+      </c>
+      <c r="G349" s="5">
+        <v>6</v>
+      </c>
       <c r="H349" s="6"/>
     </row>
-    <row r="350" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
         <v>433</v>
       </c>
@@ -9613,11 +10689,15 @@
       <c r="E350" s="3">
         <v>251</v>
       </c>
-      <c r="F350" s="5"/>
-      <c r="G350" s="5"/>
+      <c r="F350" s="5">
+        <v>262</v>
+      </c>
+      <c r="G350" s="5">
+        <v>12</v>
+      </c>
       <c r="H350" s="6"/>
     </row>
-    <row r="351" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
         <v>433</v>
       </c>
@@ -9633,11 +10713,15 @@
       <c r="E351" s="3">
         <v>40</v>
       </c>
-      <c r="F351" s="5"/>
-      <c r="G351" s="5"/>
+      <c r="F351" s="5">
+        <v>50</v>
+      </c>
+      <c r="G351" s="5">
+        <v>10</v>
+      </c>
       <c r="H351" s="6"/>
     </row>
-    <row r="352" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
         <v>433</v>
       </c>
@@ -9653,11 +10737,15 @@
       <c r="E352" s="3">
         <v>151</v>
       </c>
-      <c r="F352" s="5"/>
-      <c r="G352" s="5"/>
+      <c r="F352" s="5">
+        <v>155</v>
+      </c>
+      <c r="G352" s="5">
+        <v>5</v>
+      </c>
       <c r="H352" s="6"/>
     </row>
-    <row r="353" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
         <v>433</v>
       </c>
@@ -9673,11 +10761,15 @@
       <c r="E353" s="3">
         <v>784</v>
       </c>
-      <c r="F353" s="5"/>
-      <c r="G353" s="5"/>
+      <c r="F353" s="5">
+        <v>786</v>
+      </c>
+      <c r="G353" s="5">
+        <v>5</v>
+      </c>
       <c r="H353" s="6"/>
     </row>
-    <row r="354" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
         <v>433</v>
       </c>
@@ -9693,11 +10785,15 @@
       <c r="E354" s="3">
         <v>465</v>
       </c>
-      <c r="F354" s="5"/>
-      <c r="G354" s="5"/>
+      <c r="F354" s="5">
+        <v>467</v>
+      </c>
+      <c r="G354" s="5">
+        <v>5</v>
+      </c>
       <c r="H354" s="6"/>
     </row>
-    <row r="355" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>433</v>
       </c>
@@ -9713,11 +10809,15 @@
       <c r="E355" s="3">
         <v>293</v>
       </c>
-      <c r="F355" s="5"/>
-      <c r="G355" s="5"/>
+      <c r="F355" s="5">
+        <v>306</v>
+      </c>
+      <c r="G355" s="5">
+        <v>13</v>
+      </c>
       <c r="H355" s="6"/>
     </row>
-    <row r="356" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
         <v>433</v>
       </c>
@@ -9733,11 +10833,15 @@
       <c r="E356" s="3">
         <v>2118</v>
       </c>
-      <c r="F356" s="5"/>
-      <c r="G356" s="5"/>
+      <c r="F356" s="5">
+        <v>2136</v>
+      </c>
+      <c r="G356" s="5">
+        <v>18</v>
+      </c>
       <c r="H356" s="6"/>
     </row>
-    <row r="357" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
         <v>441</v>
       </c>
@@ -9753,11 +10857,15 @@
       <c r="E357" s="3">
         <v>676</v>
       </c>
-      <c r="F357" s="5"/>
-      <c r="G357" s="5"/>
+      <c r="F357" s="5">
+        <v>694</v>
+      </c>
+      <c r="G357" s="5">
+        <v>18</v>
+      </c>
       <c r="H357" s="6"/>
     </row>
-    <row r="358" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
         <v>441</v>
       </c>
@@ -9773,11 +10881,15 @@
       <c r="E358" s="3">
         <v>2183</v>
       </c>
-      <c r="F358" s="5"/>
-      <c r="G358" s="5"/>
+      <c r="F358" s="5">
+        <v>2210</v>
+      </c>
+      <c r="G358" s="5">
+        <v>27</v>
+      </c>
       <c r="H358" s="6"/>
     </row>
-    <row r="359" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
         <v>441</v>
       </c>
@@ -9793,11 +10905,15 @@
       <c r="E359" s="3">
         <v>34</v>
       </c>
-      <c r="F359" s="5"/>
-      <c r="G359" s="5"/>
+      <c r="F359" s="5">
+        <v>45</v>
+      </c>
+      <c r="G359" s="5">
+        <v>11</v>
+      </c>
       <c r="H359" s="6"/>
     </row>
-    <row r="360" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
         <v>441</v>
       </c>
@@ -9813,11 +10929,15 @@
       <c r="E360" s="3">
         <v>67</v>
       </c>
-      <c r="F360" s="5"/>
-      <c r="G360" s="5"/>
+      <c r="F360" s="5">
+        <v>84</v>
+      </c>
+      <c r="G360" s="5">
+        <v>17</v>
+      </c>
       <c r="H360" s="6"/>
     </row>
-    <row r="361" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
         <v>441</v>
       </c>
@@ -9833,11 +10953,15 @@
       <c r="E361" s="3">
         <v>2292</v>
       </c>
-      <c r="F361" s="5"/>
-      <c r="G361" s="5"/>
+      <c r="F361" s="5">
+        <v>2313</v>
+      </c>
+      <c r="G361" s="5">
+        <v>21</v>
+      </c>
       <c r="H361" s="6"/>
     </row>
-    <row r="362" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
         <v>441</v>
       </c>
@@ -9857,7 +10981,7 @@
       <c r="G362" s="5"/>
       <c r="H362" s="6"/>
     </row>
-    <row r="363" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
         <v>441</v>
       </c>
@@ -9873,11 +10997,15 @@
       <c r="E363" s="3">
         <v>195</v>
       </c>
-      <c r="F363" s="5"/>
-      <c r="G363" s="5"/>
+      <c r="F363" s="5">
+        <v>195</v>
+      </c>
+      <c r="G363" s="5">
+        <v>5</v>
+      </c>
       <c r="H363" s="6"/>
     </row>
-    <row r="364" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
         <v>441</v>
       </c>
@@ -9893,11 +11021,15 @@
       <c r="E364" s="3">
         <v>349</v>
       </c>
-      <c r="F364" s="5"/>
-      <c r="G364" s="5"/>
+      <c r="F364" s="5">
+        <v>349</v>
+      </c>
+      <c r="G364" s="5">
+        <v>5</v>
+      </c>
       <c r="H364" s="6"/>
     </row>
-    <row r="365" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
         <v>441</v>
       </c>
@@ -9913,11 +11045,15 @@
       <c r="E365" s="3">
         <v>831</v>
       </c>
-      <c r="F365" s="5"/>
-      <c r="G365" s="5"/>
+      <c r="F365" s="5">
+        <v>842</v>
+      </c>
+      <c r="G365" s="5">
+        <v>11</v>
+      </c>
       <c r="H365" s="6"/>
     </row>
-    <row r="366" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
         <v>441</v>
       </c>
@@ -9933,11 +11069,15 @@
       <c r="E366" s="3">
         <v>1825</v>
       </c>
-      <c r="F366" s="5"/>
-      <c r="G366" s="5"/>
+      <c r="F366" s="5">
+        <v>1030</v>
+      </c>
+      <c r="G366" s="5">
+        <v>6</v>
+      </c>
       <c r="H366" s="6"/>
     </row>
-    <row r="367" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
         <v>441</v>
       </c>
@@ -9953,11 +11093,15 @@
       <c r="E367" s="3">
         <v>1399</v>
       </c>
-      <c r="F367" s="5"/>
-      <c r="G367" s="5"/>
+      <c r="F367" s="5">
+        <v>1406</v>
+      </c>
+      <c r="G367" s="5">
+        <v>7</v>
+      </c>
       <c r="H367" s="6"/>
     </row>
-    <row r="368" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
         <v>441</v>
       </c>
@@ -9973,11 +11117,15 @@
       <c r="E368" s="3">
         <v>66</v>
       </c>
-      <c r="F368" s="5"/>
-      <c r="G368" s="5"/>
+      <c r="F368" s="5">
+        <v>66</v>
+      </c>
+      <c r="G368" s="5">
+        <v>5</v>
+      </c>
       <c r="H368" s="6"/>
     </row>
-    <row r="369" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
         <v>441</v>
       </c>
@@ -9993,11 +11141,15 @@
       <c r="E369" s="3">
         <v>4534</v>
       </c>
-      <c r="F369" s="5"/>
-      <c r="G369" s="5"/>
+      <c r="F369" s="5">
+        <v>4546</v>
+      </c>
+      <c r="G369" s="5">
+        <v>12</v>
+      </c>
       <c r="H369" s="6"/>
     </row>
-    <row r="370" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
         <v>441</v>
       </c>
@@ -10017,7 +11169,7 @@
       <c r="G370" s="5"/>
       <c r="H370" s="6"/>
     </row>
-    <row r="371" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>441</v>
       </c>
@@ -10033,11 +11185,15 @@
       <c r="E371" s="3">
         <v>1588</v>
       </c>
-      <c r="F371" s="5"/>
-      <c r="G371" s="5"/>
+      <c r="F371" s="5">
+        <v>1600</v>
+      </c>
+      <c r="G371" s="5">
+        <v>12</v>
+      </c>
       <c r="H371" s="6"/>
     </row>
-    <row r="372" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
         <v>457</v>
       </c>
@@ -10053,11 +11209,15 @@
       <c r="E372" s="3">
         <v>2712</v>
       </c>
-      <c r="F372" s="5"/>
-      <c r="G372" s="5"/>
+      <c r="F372" s="5">
+        <v>2725</v>
+      </c>
+      <c r="G372" s="5">
+        <v>13</v>
+      </c>
       <c r="H372" s="6"/>
     </row>
-    <row r="373" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
         <v>457</v>
       </c>
@@ -10077,7 +11237,7 @@
       <c r="G373" s="5"/>
       <c r="H373" s="6"/>
     </row>
-    <row r="374" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
         <v>457</v>
       </c>
@@ -10093,11 +11253,15 @@
       <c r="E374" s="3">
         <v>191</v>
       </c>
-      <c r="F374" s="5"/>
-      <c r="G374" s="5"/>
+      <c r="F374" s="5">
+        <v>198</v>
+      </c>
+      <c r="G374" s="5">
+        <v>7</v>
+      </c>
       <c r="H374" s="6"/>
     </row>
-    <row r="375" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>457</v>
       </c>
@@ -10113,11 +11277,15 @@
       <c r="E375" s="3">
         <v>1438</v>
       </c>
-      <c r="F375" s="5"/>
-      <c r="G375" s="5"/>
+      <c r="F375" s="5">
+        <v>1443</v>
+      </c>
+      <c r="G375" s="5">
+        <v>6</v>
+      </c>
       <c r="H375" s="6"/>
     </row>
-    <row r="376" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
         <v>457</v>
       </c>
@@ -10133,11 +11301,15 @@
       <c r="E376" s="3">
         <v>372</v>
       </c>
-      <c r="F376" s="5"/>
-      <c r="G376" s="5"/>
+      <c r="F376" s="5">
+        <v>372</v>
+      </c>
+      <c r="G376" s="5">
+        <v>5</v>
+      </c>
       <c r="H376" s="6"/>
     </row>
-    <row r="377" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
         <v>457</v>
       </c>
@@ -10153,11 +11325,15 @@
       <c r="E377" s="3">
         <v>230</v>
       </c>
-      <c r="F377" s="5"/>
-      <c r="G377" s="5"/>
+      <c r="F377" s="5">
+        <v>278</v>
+      </c>
+      <c r="G377" s="5">
+        <v>48</v>
+      </c>
       <c r="H377" s="6"/>
     </row>
-    <row r="378" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
         <v>457</v>
       </c>
@@ -10173,11 +11349,15 @@
       <c r="E378" s="3">
         <v>52</v>
       </c>
-      <c r="F378" s="5"/>
-      <c r="G378" s="5"/>
+      <c r="F378" s="5">
+        <v>70</v>
+      </c>
+      <c r="G378" s="5">
+        <v>18</v>
+      </c>
       <c r="H378" s="6"/>
     </row>
-    <row r="379" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>457</v>
       </c>
@@ -10193,11 +11373,15 @@
       <c r="E379" s="3">
         <v>39</v>
       </c>
-      <c r="F379" s="5"/>
-      <c r="G379" s="5"/>
+      <c r="F379" s="5">
+        <v>51</v>
+      </c>
+      <c r="G379" s="5">
+        <v>12</v>
+      </c>
       <c r="H379" s="6"/>
     </row>
-    <row r="380" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
         <v>457</v>
       </c>
@@ -10213,11 +11397,15 @@
       <c r="E380" s="3">
         <v>601</v>
       </c>
-      <c r="F380" s="5"/>
-      <c r="G380" s="5"/>
+      <c r="F380" s="5">
+        <v>601</v>
+      </c>
+      <c r="G380" s="5">
+        <v>5</v>
+      </c>
       <c r="H380" s="6"/>
     </row>
-    <row r="381" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
         <v>457</v>
       </c>
@@ -10233,11 +11421,15 @@
       <c r="E381" s="3">
         <v>263</v>
       </c>
-      <c r="F381" s="5"/>
-      <c r="G381" s="5"/>
+      <c r="F381" s="5">
+        <v>281</v>
+      </c>
+      <c r="G381" s="5">
+        <v>18</v>
+      </c>
       <c r="H381" s="6"/>
     </row>
-    <row r="382" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
         <v>457</v>
       </c>
@@ -10253,11 +11445,15 @@
       <c r="E382" s="3">
         <v>510</v>
       </c>
-      <c r="F382" s="5"/>
-      <c r="G382" s="5"/>
+      <c r="F382" s="5">
+        <v>513</v>
+      </c>
+      <c r="G382" s="5">
+        <v>5</v>
+      </c>
       <c r="H382" s="6"/>
     </row>
-    <row r="383" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
         <v>457</v>
       </c>
@@ -10277,7 +11473,7 @@
       <c r="G383" s="5"/>
       <c r="H383" s="6"/>
     </row>
-    <row r="384" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
         <v>457</v>
       </c>
@@ -10293,11 +11489,15 @@
       <c r="E384" s="3">
         <v>67</v>
       </c>
-      <c r="F384" s="5"/>
-      <c r="G384" s="5"/>
+      <c r="F384" s="5">
+        <v>75</v>
+      </c>
+      <c r="G384" s="5">
+        <v>8</v>
+      </c>
       <c r="H384" s="6"/>
     </row>
-    <row r="385" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
         <v>457</v>
       </c>
@@ -10313,11 +11513,15 @@
       <c r="E385" s="3">
         <v>33</v>
       </c>
-      <c r="F385" s="5"/>
-      <c r="G385" s="5"/>
+      <c r="F385" s="5">
+        <v>42</v>
+      </c>
+      <c r="G385" s="5">
+        <v>9</v>
+      </c>
       <c r="H385" s="6"/>
     </row>
-    <row r="386" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
         <v>457</v>
       </c>
@@ -10333,11 +11537,15 @@
       <c r="E386" s="3">
         <v>371</v>
       </c>
-      <c r="F386" s="5"/>
-      <c r="G386" s="5"/>
+      <c r="F386" s="5">
+        <v>372</v>
+      </c>
+      <c r="G386" s="5">
+        <v>5</v>
+      </c>
       <c r="H386" s="6"/>
     </row>
-    <row r="387" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
         <v>457</v>
       </c>
@@ -10353,11 +11561,15 @@
       <c r="E387" s="3">
         <v>156</v>
       </c>
-      <c r="F387" s="5"/>
-      <c r="G387" s="5"/>
+      <c r="F387" s="5">
+        <v>167</v>
+      </c>
+      <c r="G387" s="5">
+        <v>11</v>
+      </c>
       <c r="H387" s="6"/>
     </row>
-    <row r="388" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
         <v>457</v>
       </c>
@@ -10373,11 +11585,15 @@
       <c r="E388" s="3">
         <v>2403</v>
       </c>
-      <c r="F388" s="5"/>
-      <c r="G388" s="5"/>
+      <c r="F388" s="5">
+        <v>2403</v>
+      </c>
+      <c r="G388" s="5">
+        <v>5</v>
+      </c>
       <c r="H388" s="6"/>
     </row>
-    <row r="389" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
         <v>457</v>
       </c>
@@ -10393,11 +11609,15 @@
       <c r="E389" s="3">
         <v>1801</v>
       </c>
-      <c r="F389" s="5"/>
-      <c r="G389" s="5"/>
+      <c r="F389" s="5">
+        <v>1812</v>
+      </c>
+      <c r="G389" s="5">
+        <v>11</v>
+      </c>
       <c r="H389" s="6"/>
     </row>
-    <row r="390" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3" t="s">
         <v>457</v>
       </c>
@@ -10413,11 +11633,15 @@
       <c r="E390" s="3">
         <v>446</v>
       </c>
-      <c r="F390" s="5"/>
-      <c r="G390" s="5"/>
+      <c r="F390" s="5">
+        <v>460</v>
+      </c>
+      <c r="G390" s="5">
+        <v>14</v>
+      </c>
       <c r="H390" s="6"/>
     </row>
-    <row r="391" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>457</v>
       </c>
@@ -10433,11 +11657,15 @@
       <c r="E391" s="3">
         <v>449</v>
       </c>
-      <c r="F391" s="5"/>
-      <c r="G391" s="5"/>
+      <c r="F391" s="5">
+        <v>508</v>
+      </c>
+      <c r="G391" s="5">
+        <v>59</v>
+      </c>
       <c r="H391" s="6"/>
     </row>
-    <row r="392" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
         <v>478</v>
       </c>
@@ -10453,11 +11681,15 @@
       <c r="E392" s="3">
         <v>2192</v>
       </c>
-      <c r="F392" s="5"/>
-      <c r="G392" s="5"/>
+      <c r="F392" s="5">
+        <v>2198</v>
+      </c>
+      <c r="G392" s="5">
+        <v>6</v>
+      </c>
       <c r="H392" s="6"/>
     </row>
-    <row r="393" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
         <v>478</v>
       </c>
@@ -10473,11 +11705,15 @@
       <c r="E393" s="3">
         <v>393</v>
       </c>
-      <c r="F393" s="5"/>
-      <c r="G393" s="5"/>
+      <c r="F393" s="5">
+        <v>396</v>
+      </c>
+      <c r="G393" s="5">
+        <v>5</v>
+      </c>
       <c r="H393" s="6"/>
     </row>
-    <row r="394" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3" t="s">
         <v>478</v>
       </c>
@@ -10493,11 +11729,15 @@
       <c r="E394" s="3">
         <v>1048</v>
       </c>
-      <c r="F394" s="5"/>
-      <c r="G394" s="5"/>
+      <c r="F394" s="5">
+        <v>1054</v>
+      </c>
+      <c r="G394" s="5">
+        <v>6</v>
+      </c>
       <c r="H394" s="6"/>
     </row>
-    <row r="395" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
         <v>478</v>
       </c>
@@ -10513,11 +11753,15 @@
       <c r="E395" s="3">
         <v>7</v>
       </c>
-      <c r="F395" s="5"/>
-      <c r="G395" s="5"/>
+      <c r="F395" s="5">
+        <v>8</v>
+      </c>
+      <c r="G395" s="5">
+        <v>5</v>
+      </c>
       <c r="H395" s="6"/>
     </row>
-    <row r="396" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
         <v>478</v>
       </c>
@@ -10533,11 +11777,15 @@
       <c r="E396" s="3">
         <v>7201</v>
       </c>
-      <c r="F396" s="5"/>
-      <c r="G396" s="5"/>
+      <c r="F396" s="5">
+        <v>7205</v>
+      </c>
+      <c r="G396" s="5">
+        <v>5</v>
+      </c>
       <c r="H396" s="6"/>
     </row>
-    <row r="397" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
         <v>478</v>
       </c>
@@ -10553,11 +11801,15 @@
       <c r="E397" s="3">
         <v>1555</v>
       </c>
-      <c r="F397" s="5"/>
-      <c r="G397" s="5"/>
+      <c r="F397" s="5">
+        <v>1561</v>
+      </c>
+      <c r="G397" s="5">
+        <v>6</v>
+      </c>
       <c r="H397" s="6"/>
     </row>
-    <row r="398" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
         <v>485</v>
       </c>
@@ -10573,11 +11825,15 @@
       <c r="E398" s="3">
         <v>1157</v>
       </c>
-      <c r="F398" s="5"/>
-      <c r="G398" s="5"/>
+      <c r="F398" s="5">
+        <v>1176</v>
+      </c>
+      <c r="G398" s="5">
+        <v>19</v>
+      </c>
       <c r="H398" s="6"/>
     </row>
-    <row r="399" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
         <v>485</v>
       </c>
@@ -10593,11 +11849,15 @@
       <c r="E399" s="3">
         <v>33</v>
       </c>
-      <c r="F399" s="5"/>
-      <c r="G399" s="5"/>
+      <c r="F399" s="5">
+        <v>34</v>
+      </c>
+      <c r="G399" s="5">
+        <v>5</v>
+      </c>
       <c r="H399" s="6"/>
     </row>
-    <row r="400" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
         <v>485</v>
       </c>
@@ -10613,11 +11873,15 @@
       <c r="E400" s="3">
         <v>23</v>
       </c>
-      <c r="F400" s="5"/>
-      <c r="G400" s="5"/>
+      <c r="F400" s="5">
+        <v>24</v>
+      </c>
+      <c r="G400" s="5">
+        <v>5</v>
+      </c>
       <c r="H400" s="6"/>
     </row>
-    <row r="401" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
         <v>485</v>
       </c>
@@ -10633,11 +11897,15 @@
       <c r="E401" s="3">
         <v>295</v>
       </c>
-      <c r="F401" s="5"/>
-      <c r="G401" s="5"/>
+      <c r="F401" s="5">
+        <v>295</v>
+      </c>
+      <c r="G401" s="5">
+        <v>5</v>
+      </c>
       <c r="H401" s="6"/>
     </row>
-    <row r="402" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
         <v>485</v>
       </c>
@@ -10653,11 +11921,15 @@
       <c r="E402" s="3">
         <v>1095</v>
       </c>
-      <c r="F402" s="5"/>
-      <c r="G402" s="5"/>
+      <c r="F402" s="5">
+        <v>1111</v>
+      </c>
+      <c r="G402" s="5">
+        <v>16</v>
+      </c>
       <c r="H402" s="6"/>
     </row>
-    <row r="403" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
         <v>485</v>
       </c>
@@ -10673,11 +11945,15 @@
       <c r="E403" s="3">
         <v>2084</v>
       </c>
-      <c r="F403" s="5"/>
-      <c r="G403" s="5"/>
+      <c r="F403" s="5">
+        <v>2097</v>
+      </c>
+      <c r="G403" s="5">
+        <v>13</v>
+      </c>
       <c r="H403" s="6"/>
     </row>
-    <row r="404" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3" t="s">
         <v>485</v>
       </c>
@@ -10693,11 +11969,15 @@
       <c r="E404" s="3">
         <v>1085</v>
       </c>
-      <c r="F404" s="5"/>
-      <c r="G404" s="5"/>
+      <c r="F404" s="5">
+        <v>1088</v>
+      </c>
+      <c r="G404" s="5">
+        <v>5</v>
+      </c>
       <c r="H404" s="6"/>
     </row>
-    <row r="405" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>485</v>
       </c>
@@ -10713,11 +11993,15 @@
       <c r="E405" s="3">
         <v>557</v>
       </c>
-      <c r="F405" s="5"/>
-      <c r="G405" s="5"/>
+      <c r="F405" s="5">
+        <v>558</v>
+      </c>
+      <c r="G405" s="5">
+        <v>5</v>
+      </c>
       <c r="H405" s="6"/>
     </row>
-    <row r="406" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3" t="s">
         <v>485</v>
       </c>
@@ -10733,11 +12017,15 @@
       <c r="E406" s="3">
         <v>997</v>
       </c>
-      <c r="F406" s="5"/>
-      <c r="G406" s="5"/>
+      <c r="F406" s="5">
+        <v>1005</v>
+      </c>
+      <c r="G406" s="5">
+        <v>8</v>
+      </c>
       <c r="H406" s="6"/>
     </row>
-    <row r="407" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
         <v>485</v>
       </c>
@@ -10753,11 +12041,15 @@
       <c r="E407" s="3">
         <v>2502</v>
       </c>
-      <c r="F407" s="5"/>
-      <c r="G407" s="5"/>
+      <c r="F407" s="5">
+        <v>2518</v>
+      </c>
+      <c r="G407" s="5">
+        <v>16</v>
+      </c>
       <c r="H407" s="6"/>
     </row>
-    <row r="408" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3" t="s">
         <v>485</v>
       </c>
@@ -10773,11 +12065,15 @@
       <c r="E408" s="3">
         <v>1521</v>
       </c>
-      <c r="F408" s="5"/>
-      <c r="G408" s="5"/>
+      <c r="F408" s="5">
+        <v>1538</v>
+      </c>
+      <c r="G408" s="5">
+        <v>17</v>
+      </c>
       <c r="H408" s="6"/>
     </row>
-    <row r="409" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
         <v>485</v>
       </c>
@@ -10793,11 +12089,15 @@
       <c r="E409" s="3">
         <v>2479</v>
       </c>
-      <c r="F409" s="5"/>
-      <c r="G409" s="5"/>
+      <c r="F409" s="5">
+        <v>2492</v>
+      </c>
+      <c r="G409" s="5">
+        <v>13</v>
+      </c>
       <c r="H409" s="6"/>
     </row>
-    <row r="410" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3" t="s">
         <v>485</v>
       </c>
@@ -10813,11 +12113,15 @@
       <c r="E410" s="3">
         <v>121</v>
       </c>
-      <c r="F410" s="5"/>
-      <c r="G410" s="5"/>
+      <c r="F410" s="5">
+        <v>134</v>
+      </c>
+      <c r="G410" s="5">
+        <v>13</v>
+      </c>
       <c r="H410" s="6"/>
     </row>
-    <row r="411" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
         <v>485</v>
       </c>
@@ -10833,11 +12137,15 @@
       <c r="E411" s="3">
         <v>224</v>
       </c>
-      <c r="F411" s="5"/>
-      <c r="G411" s="5"/>
+      <c r="F411" s="5">
+        <v>225</v>
+      </c>
+      <c r="G411" s="5">
+        <v>5</v>
+      </c>
       <c r="H411" s="6"/>
     </row>
-    <row r="412" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3" t="s">
         <v>485</v>
       </c>
@@ -10853,11 +12161,15 @@
       <c r="E412" s="3">
         <v>1001</v>
       </c>
-      <c r="F412" s="5"/>
-      <c r="G412" s="5"/>
+      <c r="F412" s="5">
+        <v>1008</v>
+      </c>
+      <c r="G412" s="5">
+        <v>8</v>
+      </c>
       <c r="H412" s="6"/>
     </row>
-    <row r="413" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
         <v>485</v>
       </c>
@@ -10873,11 +12185,15 @@
       <c r="E413" s="3">
         <v>113</v>
       </c>
-      <c r="F413" s="5"/>
-      <c r="G413" s="5"/>
+      <c r="F413" s="5">
+        <v>120</v>
+      </c>
+      <c r="G413" s="5">
+        <v>7</v>
+      </c>
       <c r="H413" s="6"/>
     </row>
-    <row r="414" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
         <v>502</v>
       </c>
@@ -10893,11 +12209,15 @@
       <c r="E414" s="3">
         <v>29</v>
       </c>
-      <c r="F414" s="5"/>
-      <c r="G414" s="5"/>
+      <c r="F414" s="5">
+        <v>29</v>
+      </c>
+      <c r="G414" s="5">
+        <v>5</v>
+      </c>
       <c r="H414" s="6"/>
     </row>
-    <row r="415" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
         <v>502</v>
       </c>
@@ -10913,11 +12233,15 @@
       <c r="E415" s="3">
         <v>5</v>
       </c>
-      <c r="F415" s="5"/>
-      <c r="G415" s="5"/>
+      <c r="F415" s="5">
+        <v>5</v>
+      </c>
+      <c r="G415" s="5">
+        <v>5</v>
+      </c>
       <c r="H415" s="6"/>
     </row>
-    <row r="416" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3" t="s">
         <v>502</v>
       </c>
@@ -10933,11 +12257,15 @@
       <c r="E416" s="3">
         <v>26</v>
       </c>
-      <c r="F416" s="5"/>
-      <c r="G416" s="5"/>
+      <c r="F416" s="5">
+        <v>32</v>
+      </c>
+      <c r="G416" s="5">
+        <v>6</v>
+      </c>
       <c r="H416" s="6"/>
     </row>
-    <row r="417" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
         <v>502</v>
       </c>
@@ -10953,11 +12281,15 @@
       <c r="E417" s="3">
         <v>63</v>
       </c>
-      <c r="F417" s="5"/>
-      <c r="G417" s="5"/>
+      <c r="F417" s="5">
+        <v>77</v>
+      </c>
+      <c r="G417" s="5">
+        <v>14</v>
+      </c>
       <c r="H417" s="6"/>
     </row>
-    <row r="418" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3" t="s">
         <v>502</v>
       </c>
@@ -10973,11 +12305,15 @@
       <c r="E418" s="3">
         <v>49</v>
       </c>
-      <c r="F418" s="5"/>
-      <c r="G418" s="5"/>
+      <c r="F418" s="5">
+        <v>61</v>
+      </c>
+      <c r="G418" s="5">
+        <v>12</v>
+      </c>
       <c r="H418" s="6"/>
     </row>
-    <row r="419" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>502</v>
       </c>
@@ -10993,11 +12329,15 @@
       <c r="E419" s="3">
         <v>14</v>
       </c>
-      <c r="F419" s="5"/>
-      <c r="G419" s="5"/>
+      <c r="F419" s="5">
+        <v>16</v>
+      </c>
+      <c r="G419" s="5">
+        <v>5</v>
+      </c>
       <c r="H419" s="6"/>
     </row>
-    <row r="420" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3" t="s">
         <v>502</v>
       </c>
@@ -11013,11 +12353,15 @@
       <c r="E420" s="3">
         <v>362</v>
       </c>
-      <c r="F420" s="5"/>
-      <c r="G420" s="5"/>
+      <c r="F420" s="5">
+        <v>366</v>
+      </c>
+      <c r="G420" s="5">
+        <v>5</v>
+      </c>
       <c r="H420" s="6"/>
     </row>
-    <row r="421" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
         <v>502</v>
       </c>
@@ -11037,7 +12381,7 @@
       <c r="G421" s="5"/>
       <c r="H421" s="6"/>
     </row>
-    <row r="422" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3" t="s">
         <v>502</v>
       </c>
@@ -11053,11 +12397,15 @@
       <c r="E422" s="3">
         <v>0</v>
       </c>
-      <c r="F422" s="5"/>
-      <c r="G422" s="5"/>
+      <c r="F422" s="5">
+        <v>0</v>
+      </c>
+      <c r="G422" s="5">
+        <v>5</v>
+      </c>
       <c r="H422" s="6"/>
     </row>
-    <row r="423" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
         <v>502</v>
       </c>
@@ -11077,7 +12425,7 @@
       <c r="G423" s="5"/>
       <c r="H423" s="6"/>
     </row>
-    <row r="424" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3" t="s">
         <v>502</v>
       </c>
@@ -11097,7 +12445,7 @@
       <c r="G424" s="5"/>
       <c r="H424" s="6"/>
     </row>
-    <row r="425" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>502</v>
       </c>
@@ -11113,11 +12461,15 @@
       <c r="E425" s="3">
         <v>676</v>
       </c>
-      <c r="F425" s="5"/>
-      <c r="G425" s="5"/>
+      <c r="F425" s="5">
+        <v>679</v>
+      </c>
+      <c r="G425" s="5">
+        <v>5</v>
+      </c>
       <c r="H425" s="6"/>
     </row>
-    <row r="426" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
         <v>502</v>
       </c>
@@ -11133,11 +12485,15 @@
       <c r="E426" s="3">
         <v>42</v>
       </c>
-      <c r="F426" s="5"/>
-      <c r="G426" s="5"/>
+      <c r="F426" s="5">
+        <v>42</v>
+      </c>
+      <c r="G426" s="5">
+        <v>5</v>
+      </c>
       <c r="H426" s="6"/>
     </row>
-    <row r="427" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
         <v>502</v>
       </c>
@@ -11157,7 +12513,7 @@
       <c r="G427" s="5"/>
       <c r="H427" s="6"/>
     </row>
-    <row r="428" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3" t="s">
         <v>502</v>
       </c>
@@ -11173,11 +12529,15 @@
       <c r="E428" s="3">
         <v>3690</v>
       </c>
-      <c r="F428" s="5"/>
-      <c r="G428" s="5"/>
+      <c r="F428" s="5">
+        <v>3704</v>
+      </c>
+      <c r="G428" s="5">
+        <v>14</v>
+      </c>
       <c r="H428" s="6"/>
     </row>
-    <row r="429" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
         <v>502</v>
       </c>
@@ -11193,11 +12553,15 @@
       <c r="E429" s="3">
         <v>2274</v>
       </c>
-      <c r="F429" s="5"/>
-      <c r="G429" s="5"/>
+      <c r="F429" s="5">
+        <v>2283</v>
+      </c>
+      <c r="G429" s="5">
+        <v>9</v>
+      </c>
       <c r="H429" s="6"/>
     </row>
-    <row r="430" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3" t="s">
         <v>502</v>
       </c>
@@ -11217,7 +12581,7 @@
       <c r="G430" s="5"/>
       <c r="H430" s="6"/>
     </row>
-    <row r="431" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
         <v>502</v>
       </c>
@@ -11233,11 +12597,15 @@
       <c r="E431" s="3">
         <v>2354</v>
       </c>
-      <c r="F431" s="5"/>
-      <c r="G431" s="5"/>
+      <c r="F431" s="5">
+        <v>2366</v>
+      </c>
+      <c r="G431" s="5">
+        <v>12</v>
+      </c>
       <c r="H431" s="6"/>
     </row>
-    <row r="432" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3" t="s">
         <v>502</v>
       </c>
@@ -11253,11 +12621,15 @@
       <c r="E432" s="3">
         <v>1188</v>
       </c>
-      <c r="F432" s="5"/>
-      <c r="G432" s="5"/>
+      <c r="F432" s="5">
+        <v>1200</v>
+      </c>
+      <c r="G432" s="5">
+        <v>12</v>
+      </c>
       <c r="H432" s="6"/>
     </row>
-    <row r="433" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
         <v>520</v>
       </c>
@@ -11273,11 +12645,15 @@
       <c r="E433" s="3">
         <v>240</v>
       </c>
-      <c r="F433" s="5"/>
-      <c r="G433" s="5"/>
+      <c r="F433" s="5">
+        <v>250</v>
+      </c>
+      <c r="G433" s="5">
+        <v>10</v>
+      </c>
       <c r="H433" s="6"/>
     </row>
-    <row r="434" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3" t="s">
         <v>520</v>
       </c>
@@ -11293,11 +12669,15 @@
       <c r="E434" s="3">
         <v>1734</v>
       </c>
-      <c r="F434" s="5"/>
-      <c r="G434" s="5"/>
+      <c r="F434" s="5">
+        <v>1754</v>
+      </c>
+      <c r="G434" s="5">
+        <v>20</v>
+      </c>
       <c r="H434" s="6"/>
     </row>
-    <row r="435" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
         <v>520</v>
       </c>
@@ -11313,11 +12693,15 @@
       <c r="E435" s="3">
         <v>766</v>
       </c>
-      <c r="F435" s="5"/>
-      <c r="G435" s="5"/>
+      <c r="F435" s="5">
+        <v>777</v>
+      </c>
+      <c r="G435" s="5">
+        <v>11</v>
+      </c>
       <c r="H435" s="6"/>
     </row>
-    <row r="436" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3" t="s">
         <v>520</v>
       </c>
@@ -11333,11 +12717,15 @@
       <c r="E436" s="3">
         <v>3303</v>
       </c>
-      <c r="F436" s="5"/>
-      <c r="G436" s="5"/>
+      <c r="F436" s="5">
+        <v>3313</v>
+      </c>
+      <c r="G436" s="5">
+        <v>10</v>
+      </c>
       <c r="H436" s="6"/>
     </row>
-    <row r="437" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>520</v>
       </c>
@@ -11357,7 +12745,7 @@
       <c r="G437" s="5"/>
       <c r="H437" s="6"/>
     </row>
-    <row r="438" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3" t="s">
         <v>520</v>
       </c>
@@ -11373,11 +12761,15 @@
       <c r="E438" s="3">
         <v>2571</v>
       </c>
-      <c r="F438" s="5"/>
-      <c r="G438" s="5"/>
+      <c r="F438" s="5">
+        <v>2583</v>
+      </c>
+      <c r="G438" s="5">
+        <v>12</v>
+      </c>
       <c r="H438" s="6"/>
     </row>
-    <row r="439" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
         <v>520</v>
       </c>
@@ -11393,11 +12785,15 @@
       <c r="E439" s="3">
         <v>220</v>
       </c>
-      <c r="F439" s="5"/>
-      <c r="G439" s="5"/>
+      <c r="F439" s="5">
+        <v>223</v>
+      </c>
+      <c r="G439" s="5">
+        <v>5</v>
+      </c>
       <c r="H439" s="6"/>
     </row>
-    <row r="440" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3" t="s">
         <v>520</v>
       </c>
@@ -11417,7 +12813,7 @@
       <c r="G440" s="5"/>
       <c r="H440" s="6"/>
     </row>
-    <row r="441" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
         <v>520</v>
       </c>
@@ -11433,11 +12829,15 @@
       <c r="E441" s="3">
         <v>736</v>
       </c>
-      <c r="F441" s="5"/>
-      <c r="G441" s="5"/>
+      <c r="F441" s="5">
+        <v>749</v>
+      </c>
+      <c r="G441" s="5">
+        <v>13</v>
+      </c>
       <c r="H441" s="6"/>
     </row>
-    <row r="442" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3" t="s">
         <v>520</v>
       </c>
@@ -11453,11 +12853,15 @@
       <c r="E442" s="3">
         <v>590</v>
       </c>
-      <c r="F442" s="5"/>
-      <c r="G442" s="5"/>
+      <c r="F442" s="5">
+        <v>610</v>
+      </c>
+      <c r="G442" s="5">
+        <v>20</v>
+      </c>
       <c r="H442" s="6"/>
     </row>
-    <row r="443" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
         <v>520</v>
       </c>
@@ -11473,11 +12877,15 @@
       <c r="E443" s="3">
         <v>120</v>
       </c>
-      <c r="F443" s="5"/>
-      <c r="G443" s="5"/>
+      <c r="F443" s="5">
+        <v>125</v>
+      </c>
+      <c r="G443" s="5">
+        <v>6</v>
+      </c>
       <c r="H443" s="6"/>
     </row>
-    <row r="444" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3" t="s">
         <v>520</v>
       </c>
@@ -11493,11 +12901,15 @@
       <c r="E444" s="3">
         <v>1186</v>
       </c>
-      <c r="F444" s="5"/>
-      <c r="G444" s="5"/>
+      <c r="F444" s="5">
+        <v>1192</v>
+      </c>
+      <c r="G444" s="5">
+        <v>6</v>
+      </c>
       <c r="H444" s="6"/>
     </row>
-    <row r="445" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
         <v>520</v>
       </c>
@@ -11513,11 +12925,15 @@
       <c r="E445" s="3">
         <v>1012</v>
       </c>
-      <c r="F445" s="5"/>
-      <c r="G445" s="5"/>
+      <c r="F445" s="5">
+        <v>1016</v>
+      </c>
+      <c r="G445" s="5">
+        <v>5</v>
+      </c>
       <c r="H445" s="6"/>
     </row>
-    <row r="446" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3" t="s">
         <v>520</v>
       </c>
@@ -11533,11 +12949,15 @@
       <c r="E446" s="3">
         <v>204</v>
       </c>
-      <c r="F446" s="5"/>
-      <c r="G446" s="5"/>
+      <c r="F446" s="5">
+        <v>212</v>
+      </c>
+      <c r="G446" s="5">
+        <v>8</v>
+      </c>
       <c r="H446" s="6"/>
     </row>
-    <row r="447" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
         <v>520</v>
       </c>
@@ -11557,7 +12977,7 @@
       <c r="G447" s="5"/>
       <c r="H447" s="6"/>
     </row>
-    <row r="448" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
         <v>520</v>
       </c>
@@ -11577,7 +12997,7 @@
       <c r="G448" s="5"/>
       <c r="H448" s="6"/>
     </row>
-    <row r="449" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3" t="s">
         <v>520</v>
       </c>
@@ -11593,11 +13013,15 @@
       <c r="E449" s="3">
         <v>1356</v>
       </c>
-      <c r="F449" s="5"/>
-      <c r="G449" s="5"/>
+      <c r="F449" s="5">
+        <v>1363</v>
+      </c>
+      <c r="G449" s="5">
+        <v>7</v>
+      </c>
       <c r="H449" s="6"/>
     </row>
-    <row r="450" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
         <v>520</v>
       </c>
@@ -11613,11 +13037,15 @@
       <c r="E450" s="3">
         <v>88</v>
       </c>
-      <c r="F450" s="5"/>
-      <c r="G450" s="5"/>
+      <c r="F450" s="5">
+        <v>93</v>
+      </c>
+      <c r="G450" s="5">
+        <v>6</v>
+      </c>
       <c r="H450" s="6"/>
     </row>
-    <row r="451" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3" t="s">
         <v>520</v>
       </c>
@@ -11633,11 +13061,15 @@
       <c r="E451" s="3">
         <v>47</v>
       </c>
-      <c r="F451" s="5"/>
-      <c r="G451" s="5"/>
+      <c r="F451" s="5">
+        <v>47</v>
+      </c>
+      <c r="G451" s="5">
+        <v>5</v>
+      </c>
       <c r="H451" s="6"/>
     </row>
-    <row r="452" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
         <v>520</v>
       </c>
@@ -11653,11 +13085,15 @@
       <c r="E452" s="3">
         <v>298</v>
       </c>
-      <c r="F452" s="5"/>
-      <c r="G452" s="5"/>
+      <c r="F452" s="5">
+        <v>301</v>
+      </c>
+      <c r="G452" s="5">
+        <v>5</v>
+      </c>
       <c r="H452" s="6"/>
     </row>
-    <row r="453" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
         <v>520</v>
       </c>
@@ -11673,11 +13109,15 @@
       <c r="E453" s="3">
         <v>864</v>
       </c>
-      <c r="F453" s="5"/>
-      <c r="G453" s="5"/>
+      <c r="F453" s="5">
+        <v>876</v>
+      </c>
+      <c r="G453" s="5">
+        <v>12</v>
+      </c>
       <c r="H453" s="6"/>
     </row>
-    <row r="454" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3" t="s">
         <v>542</v>
       </c>
@@ -11693,11 +13133,15 @@
       <c r="E454" s="3">
         <v>1664</v>
       </c>
-      <c r="F454" s="5"/>
-      <c r="G454" s="5"/>
+      <c r="F454" s="5">
+        <v>1673</v>
+      </c>
+      <c r="G454" s="5">
+        <v>9</v>
+      </c>
       <c r="H454" s="6"/>
     </row>
-    <row r="455" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
         <v>542</v>
       </c>
@@ -11713,11 +13157,15 @@
       <c r="E455" s="3">
         <v>32</v>
       </c>
-      <c r="F455" s="5"/>
-      <c r="G455" s="5"/>
+      <c r="F455" s="5">
+        <v>32</v>
+      </c>
+      <c r="G455" s="5">
+        <v>5</v>
+      </c>
       <c r="H455" s="6"/>
     </row>
-    <row r="456" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3" t="s">
         <v>542</v>
       </c>
@@ -11733,11 +13181,15 @@
       <c r="E456" s="3">
         <v>88</v>
       </c>
-      <c r="F456" s="5"/>
-      <c r="G456" s="5"/>
+      <c r="F456" s="5">
+        <v>101</v>
+      </c>
+      <c r="G456" s="5">
+        <v>13</v>
+      </c>
       <c r="H456" s="6"/>
     </row>
-    <row r="457" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
         <v>542</v>
       </c>
@@ -11757,7 +13209,7 @@
       <c r="G457" s="5"/>
       <c r="H457" s="6"/>
     </row>
-    <row r="458" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3" t="s">
         <v>542</v>
       </c>
@@ -11773,11 +13225,15 @@
       <c r="E458" s="3">
         <v>264</v>
       </c>
-      <c r="F458" s="5"/>
-      <c r="G458" s="5"/>
+      <c r="F458" s="5">
+        <v>264</v>
+      </c>
+      <c r="G458" s="5">
+        <v>5</v>
+      </c>
       <c r="H458" s="6"/>
     </row>
-    <row r="459" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
         <v>542</v>
       </c>
@@ -11793,11 +13249,15 @@
       <c r="E459" s="3">
         <v>1404</v>
       </c>
-      <c r="F459" s="5"/>
-      <c r="G459" s="5"/>
+      <c r="F459" s="5">
+        <v>1429</v>
+      </c>
+      <c r="G459" s="5">
+        <v>25</v>
+      </c>
       <c r="H459" s="6"/>
     </row>
-    <row r="460" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3" t="s">
         <v>542</v>
       </c>
@@ -11817,7 +13277,7 @@
       <c r="G460" s="5"/>
       <c r="H460" s="6"/>
     </row>
-    <row r="461" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
         <v>542</v>
       </c>
@@ -11833,11 +13293,15 @@
       <c r="E461" s="3">
         <v>1203</v>
       </c>
-      <c r="F461" s="5"/>
-      <c r="G461" s="5"/>
+      <c r="F461" s="5">
+        <v>1217</v>
+      </c>
+      <c r="G461" s="5">
+        <v>14</v>
+      </c>
       <c r="H461" s="6"/>
     </row>
-    <row r="462" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3" t="s">
         <v>542</v>
       </c>
@@ -11853,11 +13317,15 @@
       <c r="E462" s="3">
         <v>1014</v>
       </c>
-      <c r="F462" s="5"/>
-      <c r="G462" s="5"/>
+      <c r="F462" s="5">
+        <v>1025</v>
+      </c>
+      <c r="G462" s="5">
+        <v>11</v>
+      </c>
       <c r="H462" s="6"/>
     </row>
-    <row r="463" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
         <v>550</v>
       </c>
@@ -11877,7 +13345,7 @@
       <c r="G463" s="5"/>
       <c r="H463" s="6"/>
     </row>
-    <row r="464" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3" t="s">
         <v>550</v>
       </c>
@@ -11893,11 +13361,15 @@
       <c r="E464" s="3">
         <v>1573</v>
       </c>
-      <c r="F464" s="5"/>
-      <c r="G464" s="5"/>
+      <c r="F464" s="5">
+        <v>1585</v>
+      </c>
+      <c r="G464" s="5">
+        <v>12</v>
+      </c>
       <c r="H464" s="6"/>
     </row>
-    <row r="465" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
         <v>550</v>
       </c>
@@ -11913,11 +13385,15 @@
       <c r="E465" s="3">
         <v>497</v>
       </c>
-      <c r="F465" s="5"/>
-      <c r="G465" s="5"/>
+      <c r="F465" s="5">
+        <v>507</v>
+      </c>
+      <c r="G465" s="5">
+        <v>10</v>
+      </c>
       <c r="H465" s="6"/>
     </row>
-    <row r="466" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3" t="s">
         <v>550</v>
       </c>
@@ -11933,11 +13409,15 @@
       <c r="E466" s="3">
         <v>1988</v>
       </c>
-      <c r="F466" s="5"/>
-      <c r="G466" s="5"/>
+      <c r="F466" s="5">
+        <v>1993</v>
+      </c>
+      <c r="G466" s="5">
+        <v>5</v>
+      </c>
       <c r="H466" s="6"/>
     </row>
-    <row r="467" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
         <v>550</v>
       </c>
@@ -11953,11 +13433,15 @@
       <c r="E467" s="3">
         <v>15</v>
       </c>
-      <c r="F467" s="5"/>
-      <c r="G467" s="5"/>
+      <c r="F467" s="5">
+        <v>17</v>
+      </c>
+      <c r="G467" s="5">
+        <v>5</v>
+      </c>
       <c r="H467" s="6"/>
     </row>
-    <row r="468" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3" t="s">
         <v>550</v>
       </c>
@@ -11973,11 +13457,15 @@
       <c r="E468" s="3">
         <v>0</v>
       </c>
-      <c r="F468" s="5"/>
-      <c r="G468" s="5"/>
+      <c r="F468" s="5">
+        <v>0</v>
+      </c>
+      <c r="G468" s="5">
+        <v>5</v>
+      </c>
       <c r="H468" s="6"/>
     </row>
-    <row r="469" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
         <v>550</v>
       </c>
@@ -11993,11 +13481,15 @@
       <c r="E469" s="3">
         <v>1005</v>
       </c>
-      <c r="F469" s="5"/>
-      <c r="G469" s="5"/>
+      <c r="F469" s="5">
+        <v>1020</v>
+      </c>
+      <c r="G469" s="5">
+        <v>15</v>
+      </c>
       <c r="H469" s="6"/>
     </row>
-    <row r="470" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3" t="s">
         <v>550</v>
       </c>
@@ -12013,11 +13505,15 @@
       <c r="E470" s="3">
         <v>453</v>
       </c>
-      <c r="F470" s="5"/>
-      <c r="G470" s="5"/>
+      <c r="F470" s="5">
+        <v>468</v>
+      </c>
+      <c r="G470" s="5">
+        <v>15</v>
+      </c>
       <c r="H470" s="6"/>
     </row>
-    <row r="471" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
         <v>550</v>
       </c>
@@ -12033,11 +13529,15 @@
       <c r="E471" s="3">
         <v>510</v>
       </c>
-      <c r="F471" s="5"/>
-      <c r="G471" s="5"/>
+      <c r="F471" s="5">
+        <v>515</v>
+      </c>
+      <c r="G471" s="5">
+        <v>6</v>
+      </c>
       <c r="H471" s="6"/>
     </row>
-    <row r="472" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3" t="s">
         <v>550</v>
       </c>
@@ -12057,7 +13557,7 @@
       <c r="G472" s="5"/>
       <c r="H472" s="6"/>
     </row>
-    <row r="473" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
         <v>550</v>
       </c>
@@ -12073,11 +13573,15 @@
       <c r="E473" s="3">
         <v>1398</v>
       </c>
-      <c r="F473" s="5"/>
-      <c r="G473" s="5"/>
+      <c r="F473" s="5">
+        <v>1413</v>
+      </c>
+      <c r="G473" s="5">
+        <v>15</v>
+      </c>
       <c r="H473" s="6"/>
     </row>
-    <row r="474" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3" t="s">
         <v>550</v>
       </c>
@@ -12093,11 +13597,15 @@
       <c r="E474" s="3">
         <v>88</v>
       </c>
-      <c r="F474" s="5"/>
-      <c r="G474" s="5"/>
+      <c r="F474" s="5">
+        <v>89</v>
+      </c>
+      <c r="G474" s="5">
+        <v>5</v>
+      </c>
       <c r="H474" s="6"/>
     </row>
-    <row r="475" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
         <v>550</v>
       </c>
@@ -12113,11 +13621,15 @@
       <c r="E475" s="3">
         <v>585</v>
       </c>
-      <c r="F475" s="5"/>
-      <c r="G475" s="5"/>
+      <c r="F475" s="5">
+        <v>587</v>
+      </c>
+      <c r="G475" s="5">
+        <v>5</v>
+      </c>
       <c r="H475" s="6"/>
     </row>
-    <row r="476" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3" t="s">
         <v>550</v>
       </c>
@@ -12133,11 +13645,15 @@
       <c r="E476" s="3">
         <v>1201</v>
       </c>
-      <c r="F476" s="5"/>
-      <c r="G476" s="5"/>
+      <c r="F476" s="5">
+        <v>1213</v>
+      </c>
+      <c r="G476" s="5">
+        <v>12</v>
+      </c>
       <c r="H476" s="6"/>
     </row>
-    <row r="477" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
         <v>550</v>
       </c>
@@ -12153,11 +13669,15 @@
       <c r="E477" s="3">
         <v>1528</v>
       </c>
-      <c r="F477" s="5"/>
-      <c r="G477" s="5"/>
+      <c r="F477" s="5">
+        <v>1532</v>
+      </c>
+      <c r="G477" s="5">
+        <v>6</v>
+      </c>
       <c r="H477" s="6"/>
     </row>
-    <row r="478" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3" t="s">
         <v>550</v>
       </c>
@@ -12173,11 +13693,15 @@
       <c r="E478" s="3">
         <v>1945</v>
       </c>
-      <c r="F478" s="5"/>
-      <c r="G478" s="5"/>
+      <c r="F478" s="5">
+        <v>1945</v>
+      </c>
+      <c r="G478" s="5">
+        <v>5</v>
+      </c>
       <c r="H478" s="6"/>
     </row>
-    <row r="479" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
         <v>550</v>
       </c>
@@ -12193,11 +13717,15 @@
       <c r="E479" s="3">
         <v>2069</v>
       </c>
-      <c r="F479" s="5"/>
-      <c r="G479" s="5"/>
+      <c r="F479" s="5">
+        <v>2102</v>
+      </c>
+      <c r="G479" s="5">
+        <v>33</v>
+      </c>
       <c r="H479" s="6"/>
     </row>
-    <row r="480" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3" t="s">
         <v>550</v>
       </c>
@@ -12213,11 +13741,15 @@
       <c r="E480" s="3">
         <v>295</v>
       </c>
-      <c r="F480" s="5"/>
-      <c r="G480" s="5"/>
+      <c r="F480" s="5">
+        <v>313</v>
+      </c>
+      <c r="G480" s="5">
+        <v>18</v>
+      </c>
       <c r="H480" s="6"/>
     </row>
-    <row r="481" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
         <v>550</v>
       </c>
@@ -12237,7 +13769,7 @@
       <c r="G481" s="5"/>
       <c r="H481" s="6"/>
     </row>
-    <row r="482" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3" t="s">
         <v>569</v>
       </c>
@@ -12253,11 +13785,15 @@
       <c r="E482" s="3">
         <v>519</v>
       </c>
-      <c r="F482" s="5"/>
-      <c r="G482" s="5"/>
+      <c r="F482" s="5">
+        <v>521</v>
+      </c>
+      <c r="G482" s="5">
+        <v>5</v>
+      </c>
       <c r="H482" s="6"/>
     </row>
-    <row r="483" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
         <v>569</v>
       </c>
@@ -12273,11 +13809,15 @@
       <c r="E483" s="3">
         <v>978</v>
       </c>
-      <c r="F483" s="5"/>
-      <c r="G483" s="5"/>
+      <c r="F483" s="5">
+        <v>996</v>
+      </c>
+      <c r="G483" s="5">
+        <v>18</v>
+      </c>
       <c r="H483" s="6"/>
     </row>
-    <row r="484" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3" t="s">
         <v>569</v>
       </c>
@@ -12293,11 +13833,15 @@
       <c r="E484" s="3">
         <v>7714</v>
       </c>
-      <c r="F484" s="5"/>
-      <c r="G484" s="5"/>
+      <c r="F484" s="5">
+        <v>7775</v>
+      </c>
+      <c r="G484" s="5">
+        <v>122</v>
+      </c>
       <c r="H484" s="6"/>
     </row>
-    <row r="485" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>569</v>
       </c>
@@ -12313,11 +13857,15 @@
       <c r="E485" s="3">
         <v>299</v>
       </c>
-      <c r="F485" s="5"/>
-      <c r="G485" s="5"/>
+      <c r="F485" s="5">
+        <v>308</v>
+      </c>
+      <c r="G485" s="5">
+        <v>9</v>
+      </c>
       <c r="H485" s="6"/>
     </row>
-    <row r="486" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
         <v>569</v>
       </c>
@@ -12333,11 +13881,15 @@
       <c r="E486" s="3">
         <v>1087</v>
       </c>
-      <c r="F486" s="5"/>
-      <c r="G486" s="5"/>
+      <c r="F486" s="5">
+        <v>1093</v>
+      </c>
+      <c r="G486" s="5">
+        <v>6</v>
+      </c>
       <c r="H486" s="6"/>
     </row>
-    <row r="487" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
         <v>569</v>
       </c>
@@ -12353,11 +13905,15 @@
       <c r="E487" s="3">
         <v>1229</v>
       </c>
-      <c r="F487" s="5"/>
-      <c r="G487" s="5"/>
+      <c r="F487" s="5">
+        <v>1238</v>
+      </c>
+      <c r="G487" s="5">
+        <v>9</v>
+      </c>
       <c r="H487" s="6"/>
     </row>
-    <row r="488" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3" t="s">
         <v>569</v>
       </c>
@@ -12373,11 +13929,15 @@
       <c r="E488" s="3">
         <v>292</v>
       </c>
-      <c r="F488" s="5"/>
-      <c r="G488" s="5"/>
+      <c r="F488" s="5">
+        <v>299</v>
+      </c>
+      <c r="G488" s="5">
+        <v>7</v>
+      </c>
       <c r="H488" s="6"/>
     </row>
-    <row r="489" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
         <v>569</v>
       </c>
@@ -12393,11 +13953,15 @@
       <c r="E489" s="3">
         <v>466</v>
       </c>
-      <c r="F489" s="5"/>
-      <c r="G489" s="5"/>
+      <c r="F489" s="5">
+        <v>479</v>
+      </c>
+      <c r="G489" s="5">
+        <v>13</v>
+      </c>
       <c r="H489" s="6"/>
     </row>
-    <row r="490" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3" t="s">
         <v>569</v>
       </c>
@@ -12417,7 +13981,7 @@
       <c r="G490" s="5"/>
       <c r="H490" s="6"/>
     </row>
-    <row r="491" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
         <v>569</v>
       </c>
@@ -12437,7 +14001,7 @@
       <c r="G491" s="5"/>
       <c r="H491" s="6"/>
     </row>
-    <row r="492" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3" t="s">
         <v>569</v>
       </c>
@@ -12457,7 +14021,7 @@
       <c r="G492" s="5"/>
       <c r="H492" s="6"/>
     </row>
-    <row r="493" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
         <v>569</v>
       </c>
@@ -12473,11 +14037,15 @@
       <c r="E493" s="3">
         <v>79</v>
       </c>
-      <c r="F493" s="5"/>
-      <c r="G493" s="5"/>
+      <c r="F493" s="5">
+        <v>84</v>
+      </c>
+      <c r="G493" s="5">
+        <v>6</v>
+      </c>
       <c r="H493" s="6"/>
     </row>
-    <row r="494" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3" t="s">
         <v>569</v>
       </c>
@@ -12493,11 +14061,15 @@
       <c r="E494" s="3">
         <v>2</v>
       </c>
-      <c r="F494" s="5"/>
-      <c r="G494" s="5"/>
+      <c r="F494" s="5">
+        <v>2</v>
+      </c>
+      <c r="G494" s="5">
+        <v>5</v>
+      </c>
       <c r="H494" s="6"/>
     </row>
-    <row r="495" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
         <v>569</v>
       </c>
@@ -12513,11 +14085,15 @@
       <c r="E495" s="3">
         <v>57</v>
       </c>
-      <c r="F495" s="5"/>
-      <c r="G495" s="5"/>
+      <c r="F495" s="5">
+        <v>95</v>
+      </c>
+      <c r="G495" s="5">
+        <v>38</v>
+      </c>
       <c r="H495" s="6"/>
     </row>
-    <row r="496" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3" t="s">
         <v>584</v>
       </c>
@@ -12533,11 +14109,15 @@
       <c r="E496" s="3">
         <v>1754</v>
       </c>
-      <c r="F496" s="5"/>
-      <c r="G496" s="5"/>
+      <c r="F496" s="5">
+        <v>1760</v>
+      </c>
+      <c r="G496" s="5">
+        <v>6</v>
+      </c>
       <c r="H496" s="6"/>
     </row>
-    <row r="497" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
         <v>584</v>
       </c>
@@ -12557,7 +14137,7 @@
       <c r="G497" s="5"/>
       <c r="H497" s="6"/>
     </row>
-    <row r="498" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3" t="s">
         <v>584</v>
       </c>
@@ -12573,11 +14153,15 @@
       <c r="E498" s="3">
         <v>33</v>
       </c>
-      <c r="F498" s="5"/>
-      <c r="G498" s="5"/>
+      <c r="F498" s="5">
+        <v>33</v>
+      </c>
+      <c r="G498" s="5">
+        <v>5</v>
+      </c>
       <c r="H498" s="6"/>
     </row>
-    <row r="499" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
         <v>584</v>
       </c>
@@ -12593,11 +14177,15 @@
       <c r="E499" s="3">
         <v>140</v>
       </c>
-      <c r="F499" s="5"/>
-      <c r="G499" s="5"/>
+      <c r="F499" s="5">
+        <v>150</v>
+      </c>
+      <c r="G499" s="5">
+        <v>10</v>
+      </c>
       <c r="H499" s="6"/>
     </row>
-    <row r="500" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3" t="s">
         <v>584</v>
       </c>
@@ -12613,11 +14201,15 @@
       <c r="E500" s="3">
         <v>1575</v>
       </c>
-      <c r="F500" s="5"/>
-      <c r="G500" s="5"/>
+      <c r="F500" s="5">
+        <v>1586</v>
+      </c>
+      <c r="G500" s="5">
+        <v>11</v>
+      </c>
       <c r="H500" s="6"/>
     </row>
-    <row r="501" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
         <v>584</v>
       </c>
@@ -12633,11 +14225,15 @@
       <c r="E501" s="3">
         <v>1142</v>
       </c>
-      <c r="F501" s="5"/>
-      <c r="G501" s="5"/>
+      <c r="F501" s="5">
+        <v>1149</v>
+      </c>
+      <c r="G501" s="5">
+        <v>7</v>
+      </c>
       <c r="H501" s="6"/>
     </row>
-    <row r="502" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3" t="s">
         <v>584</v>
       </c>
@@ -12657,7 +14253,7 @@
       <c r="G502" s="5"/>
       <c r="H502" s="6"/>
     </row>
-    <row r="503" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
         <v>584</v>
       </c>
@@ -12673,11 +14269,15 @@
       <c r="E503" s="3">
         <v>1762</v>
       </c>
-      <c r="F503" s="5"/>
-      <c r="G503" s="5"/>
+      <c r="F503" s="5">
+        <v>1779</v>
+      </c>
+      <c r="G503" s="5">
+        <v>17</v>
+      </c>
       <c r="H503" s="6"/>
     </row>
-    <row r="504" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3" t="s">
         <v>584</v>
       </c>
@@ -12693,11 +14293,15 @@
       <c r="E504" s="3">
         <v>1687</v>
       </c>
-      <c r="F504" s="5"/>
-      <c r="G504" s="5"/>
+      <c r="F504" s="5">
+        <v>1698</v>
+      </c>
+      <c r="G504" s="5">
+        <v>11</v>
+      </c>
       <c r="H504" s="6"/>
     </row>
-    <row r="505" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
         <v>584</v>
       </c>
@@ -12713,11 +14317,15 @@
       <c r="E505" s="3">
         <v>1603</v>
       </c>
-      <c r="F505" s="5"/>
-      <c r="G505" s="5"/>
+      <c r="F505" s="5">
+        <v>1614</v>
+      </c>
+      <c r="G505" s="5">
+        <v>11</v>
+      </c>
       <c r="H505" s="6"/>
     </row>
-    <row r="506" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3" t="s">
         <v>584</v>
       </c>
@@ -12733,11 +14341,15 @@
       <c r="E506" s="3">
         <v>816</v>
       </c>
-      <c r="F506" s="5"/>
-      <c r="G506" s="5"/>
+      <c r="F506" s="5">
+        <v>825</v>
+      </c>
+      <c r="G506" s="5">
+        <v>9</v>
+      </c>
       <c r="H506" s="6"/>
     </row>
-    <row r="507" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
         <v>584</v>
       </c>
@@ -12753,11 +14365,15 @@
       <c r="E507" s="3">
         <v>970</v>
       </c>
-      <c r="F507" s="5"/>
-      <c r="G507" s="5"/>
+      <c r="F507" s="5">
+        <v>255</v>
+      </c>
+      <c r="G507" s="5">
+        <v>5</v>
+      </c>
       <c r="H507" s="6"/>
     </row>
-    <row r="508" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3" t="s">
         <v>584</v>
       </c>
@@ -12773,11 +14389,15 @@
       <c r="E508" s="3">
         <v>125</v>
       </c>
-      <c r="F508" s="5"/>
-      <c r="G508" s="5"/>
+      <c r="F508" s="5">
+        <v>251</v>
+      </c>
+      <c r="G508" s="5">
+        <v>26</v>
+      </c>
       <c r="H508" s="6"/>
     </row>
-    <row r="509" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
         <v>584</v>
       </c>
@@ -12793,11 +14413,15 @@
       <c r="E509" s="3">
         <v>286</v>
       </c>
-      <c r="F509" s="5"/>
-      <c r="G509" s="5"/>
+      <c r="F509" s="5">
+        <v>286</v>
+      </c>
+      <c r="G509" s="5">
+        <v>5</v>
+      </c>
       <c r="H509" s="6"/>
     </row>
-    <row r="510" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3" t="s">
         <v>599</v>
       </c>
@@ -12813,11 +14437,15 @@
       <c r="E510" s="3">
         <v>1954</v>
       </c>
-      <c r="F510" s="5"/>
-      <c r="G510" s="5"/>
+      <c r="F510" s="5">
+        <v>1967</v>
+      </c>
+      <c r="G510" s="5">
+        <v>13</v>
+      </c>
       <c r="H510" s="6"/>
     </row>
-    <row r="511" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
         <v>599</v>
       </c>
@@ -12833,11 +14461,15 @@
       <c r="E511" s="3">
         <v>1</v>
       </c>
-      <c r="F511" s="5"/>
-      <c r="G511" s="5"/>
+      <c r="F511" s="5">
+        <v>1</v>
+      </c>
+      <c r="G511" s="5">
+        <v>5</v>
+      </c>
       <c r="H511" s="6"/>
     </row>
-    <row r="512" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3" t="s">
         <v>599</v>
       </c>
@@ -12853,11 +14485,15 @@
       <c r="E512" s="3">
         <v>423</v>
       </c>
-      <c r="F512" s="5"/>
-      <c r="G512" s="5"/>
+      <c r="F512" s="5">
+        <v>426</v>
+      </c>
+      <c r="G512" s="5">
+        <v>5</v>
+      </c>
       <c r="H512" s="6"/>
     </row>
-    <row r="513" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
         <v>599</v>
       </c>
@@ -12873,11 +14509,15 @@
       <c r="E513" s="3">
         <v>577</v>
       </c>
-      <c r="F513" s="5"/>
-      <c r="G513" s="5"/>
+      <c r="F513" s="5">
+        <v>577</v>
+      </c>
+      <c r="G513" s="5">
+        <v>5</v>
+      </c>
       <c r="H513" s="6"/>
     </row>
-    <row r="514" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3" t="s">
         <v>599</v>
       </c>
@@ -12893,11 +14533,15 @@
       <c r="E514" s="3">
         <v>103</v>
       </c>
-      <c r="F514" s="5"/>
-      <c r="G514" s="5"/>
+      <c r="F514" s="5">
+        <v>107</v>
+      </c>
+      <c r="G514" s="5">
+        <v>5</v>
+      </c>
       <c r="H514" s="6"/>
     </row>
-    <row r="515" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
         <v>599</v>
       </c>
@@ -12913,11 +14557,15 @@
       <c r="E515" s="3">
         <v>930</v>
       </c>
-      <c r="F515" s="5"/>
-      <c r="G515" s="5"/>
+      <c r="F515" s="5">
+        <v>934</v>
+      </c>
+      <c r="G515" s="5">
+        <v>5</v>
+      </c>
       <c r="H515" s="6"/>
     </row>
-    <row r="516" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3" t="s">
         <v>599</v>
       </c>
@@ -12933,11 +14581,15 @@
       <c r="E516" s="3">
         <v>322</v>
       </c>
-      <c r="F516" s="5"/>
-      <c r="G516" s="5"/>
+      <c r="F516" s="5">
+        <v>342</v>
+      </c>
+      <c r="G516" s="5">
+        <v>20</v>
+      </c>
       <c r="H516" s="6"/>
     </row>
-    <row r="517" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
         <v>599</v>
       </c>
@@ -12953,11 +14605,15 @@
       <c r="E517" s="3">
         <v>520</v>
       </c>
-      <c r="F517" s="5"/>
-      <c r="G517" s="5"/>
+      <c r="F517" s="5">
+        <v>528</v>
+      </c>
+      <c r="G517" s="5">
+        <v>8</v>
+      </c>
       <c r="H517" s="6"/>
     </row>
-    <row r="518" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3" t="s">
         <v>599</v>
       </c>
@@ -12977,7 +14633,7 @@
       <c r="G518" s="5"/>
       <c r="H518" s="6"/>
     </row>
-    <row r="519" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
         <v>599</v>
       </c>
@@ -12993,11 +14649,15 @@
       <c r="E519" s="3">
         <v>600</v>
       </c>
-      <c r="F519" s="5"/>
-      <c r="G519" s="5"/>
+      <c r="F519" s="5">
+        <v>609</v>
+      </c>
+      <c r="G519" s="5">
+        <v>9</v>
+      </c>
       <c r="H519" s="6"/>
     </row>
-    <row r="520" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3" t="s">
         <v>599</v>
       </c>
@@ -13013,11 +14673,15 @@
       <c r="E520" s="3">
         <v>686</v>
       </c>
-      <c r="F520" s="5"/>
-      <c r="G520" s="5"/>
+      <c r="F520" s="5">
+        <v>687</v>
+      </c>
+      <c r="G520" s="5">
+        <v>5</v>
+      </c>
       <c r="H520" s="6"/>
     </row>
-    <row r="521" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
         <v>599</v>
       </c>
@@ -13033,11 +14697,15 @@
       <c r="E521" s="3">
         <v>133</v>
       </c>
-      <c r="F521" s="5"/>
-      <c r="G521" s="5"/>
+      <c r="F521" s="5">
+        <v>135</v>
+      </c>
+      <c r="G521" s="5">
+        <v>5</v>
+      </c>
       <c r="H521" s="6"/>
     </row>
-    <row r="522" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3" t="s">
         <v>599</v>
       </c>
@@ -13051,11 +14719,15 @@
         <v>23</v>
       </c>
       <c r="E522" s="3"/>
-      <c r="F522" s="5"/>
-      <c r="G522" s="5"/>
+      <c r="F522" s="5">
+        <v>0</v>
+      </c>
+      <c r="G522" s="5">
+        <v>0</v>
+      </c>
       <c r="H522" s="6"/>
     </row>
-    <row r="523" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3" t="s">
         <v>599</v>
       </c>
@@ -13071,11 +14743,15 @@
       <c r="E523" s="3">
         <v>418</v>
       </c>
-      <c r="F523" s="5"/>
-      <c r="G523" s="5"/>
+      <c r="F523" s="5">
+        <v>424</v>
+      </c>
+      <c r="G523" s="5">
+        <v>6</v>
+      </c>
       <c r="H523" s="6"/>
     </row>
-    <row r="524" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
         <v>612</v>
       </c>
@@ -13091,11 +14767,15 @@
       <c r="E524" s="3">
         <v>165</v>
       </c>
-      <c r="F524" s="5"/>
-      <c r="G524" s="5"/>
+      <c r="F524" s="5">
+        <v>165</v>
+      </c>
+      <c r="G524" s="5">
+        <v>5</v>
+      </c>
       <c r="H524" s="6"/>
     </row>
-    <row r="525" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3" t="s">
         <v>612</v>
       </c>
@@ -13111,11 +14791,15 @@
       <c r="E525" s="3">
         <v>40</v>
       </c>
-      <c r="F525" s="5"/>
-      <c r="G525" s="5"/>
+      <c r="F525" s="5">
+        <v>40</v>
+      </c>
+      <c r="G525" s="5">
+        <v>5</v>
+      </c>
       <c r="H525" s="6"/>
     </row>
-    <row r="526" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
         <v>612</v>
       </c>
@@ -13131,11 +14815,15 @@
       <c r="E526" s="3">
         <v>653</v>
       </c>
-      <c r="F526" s="5"/>
-      <c r="G526" s="5"/>
+      <c r="F526" s="5">
+        <v>658</v>
+      </c>
+      <c r="G526" s="5">
+        <v>5</v>
+      </c>
       <c r="H526" s="6"/>
     </row>
-    <row r="527" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3" t="s">
         <v>612</v>
       </c>
@@ -13151,11 +14839,15 @@
       <c r="E527" s="3">
         <v>97</v>
       </c>
-      <c r="F527" s="5"/>
-      <c r="G527" s="5"/>
+      <c r="F527" s="5">
+        <v>103</v>
+      </c>
+      <c r="G527" s="5">
+        <v>6</v>
+      </c>
       <c r="H527" s="6"/>
     </row>
-    <row r="528" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
         <v>612</v>
       </c>
@@ -13171,11 +14863,15 @@
       <c r="E528" s="3">
         <v>911</v>
       </c>
-      <c r="F528" s="5"/>
-      <c r="G528" s="5"/>
+      <c r="F528" s="5">
+        <v>919</v>
+      </c>
+      <c r="G528" s="5">
+        <v>8</v>
+      </c>
       <c r="H528" s="6"/>
     </row>
-    <row r="529" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3" t="s">
         <v>612</v>
       </c>
@@ -13191,11 +14887,15 @@
       <c r="E529" s="3">
         <v>279</v>
       </c>
-      <c r="F529" s="5"/>
-      <c r="G529" s="5"/>
+      <c r="F529" s="5">
+        <v>283</v>
+      </c>
+      <c r="G529" s="5">
+        <v>5</v>
+      </c>
       <c r="H529" s="6"/>
     </row>
-    <row r="530" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
         <v>619</v>
       </c>
@@ -13211,11 +14911,15 @@
       <c r="E530" s="3">
         <v>891</v>
       </c>
-      <c r="F530" s="5"/>
-      <c r="G530" s="5"/>
+      <c r="F530" s="5">
+        <v>892</v>
+      </c>
+      <c r="G530" s="5">
+        <v>5</v>
+      </c>
       <c r="H530" s="6"/>
     </row>
-    <row r="531" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3" t="s">
         <v>619</v>
       </c>
@@ -13235,7 +14939,7 @@
       <c r="G531" s="5"/>
       <c r="H531" s="6"/>
     </row>
-    <row r="532" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
         <v>619</v>
       </c>
@@ -13251,11 +14955,15 @@
       <c r="E532" s="3">
         <v>88</v>
       </c>
-      <c r="F532" s="5"/>
-      <c r="G532" s="5"/>
+      <c r="F532" s="5">
+        <v>96</v>
+      </c>
+      <c r="G532" s="5">
+        <v>8</v>
+      </c>
       <c r="H532" s="6"/>
     </row>
-    <row r="533" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3" t="s">
         <v>619</v>
       </c>
@@ -13271,11 +14979,15 @@
       <c r="E533" s="3">
         <v>1019</v>
       </c>
-      <c r="F533" s="5"/>
-      <c r="G533" s="5"/>
+      <c r="F533" s="5">
+        <v>1033</v>
+      </c>
+      <c r="G533" s="5">
+        <v>14</v>
+      </c>
       <c r="H533" s="6"/>
     </row>
-    <row r="534" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
         <v>619</v>
       </c>
@@ -13295,7 +15007,7 @@
       <c r="G534" s="5"/>
       <c r="H534" s="6"/>
     </row>
-    <row r="535" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3" t="s">
         <v>619</v>
       </c>
@@ -13315,7 +15027,7 @@
       <c r="G535" s="5"/>
       <c r="H535" s="6"/>
     </row>
-    <row r="536" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
         <v>619</v>
       </c>
@@ -13331,11 +15043,15 @@
       <c r="E536" s="3">
         <v>337</v>
       </c>
-      <c r="F536" s="5"/>
-      <c r="G536" s="5"/>
+      <c r="F536" s="5">
+        <v>346</v>
+      </c>
+      <c r="G536" s="5">
+        <v>9</v>
+      </c>
       <c r="H536" s="6"/>
     </row>
-    <row r="537" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3" t="s">
         <v>619</v>
       </c>
@@ -13351,11 +15067,15 @@
       <c r="E537" s="3">
         <v>374</v>
       </c>
-      <c r="F537" s="5"/>
-      <c r="G537" s="5"/>
+      <c r="F537" s="5">
+        <v>375</v>
+      </c>
+      <c r="G537" s="5">
+        <v>5</v>
+      </c>
       <c r="H537" s="6"/>
     </row>
-    <row r="538" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
         <v>619</v>
       </c>
@@ -13371,11 +15091,15 @@
       <c r="E538" s="3">
         <v>83</v>
       </c>
-      <c r="F538" s="5"/>
-      <c r="G538" s="5"/>
+      <c r="F538" s="5">
+        <v>97</v>
+      </c>
+      <c r="G538" s="5">
+        <v>14</v>
+      </c>
       <c r="H538" s="6"/>
     </row>
-    <row r="539" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3" t="s">
         <v>628</v>
       </c>
@@ -13391,11 +15115,15 @@
       <c r="E539" s="3">
         <v>276</v>
       </c>
-      <c r="F539" s="5"/>
-      <c r="G539" s="5"/>
+      <c r="F539" s="5">
+        <v>280</v>
+      </c>
+      <c r="G539" s="5">
+        <v>5</v>
+      </c>
       <c r="H539" s="6"/>
     </row>
-    <row r="540" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
         <v>628</v>
       </c>
@@ -13411,11 +15139,15 @@
       <c r="E540" s="3">
         <v>849</v>
       </c>
-      <c r="F540" s="5"/>
-      <c r="G540" s="5"/>
+      <c r="F540" s="5">
+        <v>852</v>
+      </c>
+      <c r="G540" s="5">
+        <v>5</v>
+      </c>
       <c r="H540" s="6"/>
     </row>
-    <row r="541" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3" t="s">
         <v>628</v>
       </c>
@@ -13435,7 +15167,7 @@
       <c r="G541" s="5"/>
       <c r="H541" s="6"/>
     </row>
-    <row r="542" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
         <v>628</v>
       </c>
@@ -13451,11 +15183,15 @@
       <c r="E542" s="3">
         <v>1336</v>
       </c>
-      <c r="F542" s="5"/>
-      <c r="G542" s="5"/>
+      <c r="F542" s="5">
+        <v>1362</v>
+      </c>
+      <c r="G542" s="5">
+        <v>26</v>
+      </c>
       <c r="H542" s="6"/>
     </row>
-    <row r="543" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3" t="s">
         <v>628</v>
       </c>
@@ -13475,7 +15211,7 @@
       <c r="G543" s="5"/>
       <c r="H543" s="6"/>
     </row>
-    <row r="544" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
         <v>628</v>
       </c>
@@ -13491,11 +15227,15 @@
       <c r="E544" s="3">
         <v>128</v>
       </c>
-      <c r="F544" s="5"/>
-      <c r="G544" s="5"/>
+      <c r="F544" s="5">
+        <v>134</v>
+      </c>
+      <c r="G544" s="5">
+        <v>6</v>
+      </c>
       <c r="H544" s="6"/>
     </row>
-    <row r="545" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3" t="s">
         <v>628</v>
       </c>
@@ -13511,11 +15251,15 @@
       <c r="E545" s="3">
         <v>365</v>
       </c>
-      <c r="F545" s="5"/>
-      <c r="G545" s="5"/>
+      <c r="F545" s="5">
+        <v>368</v>
+      </c>
+      <c r="G545" s="5">
+        <v>5</v>
+      </c>
       <c r="H545" s="6"/>
     </row>
-    <row r="546" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
         <v>628</v>
       </c>
@@ -13531,11 +15275,15 @@
       <c r="E546" s="3">
         <v>42</v>
       </c>
-      <c r="F546" s="5"/>
-      <c r="G546" s="5"/>
+      <c r="F546" s="5">
+        <v>53</v>
+      </c>
+      <c r="G546" s="5">
+        <v>11</v>
+      </c>
       <c r="H546" s="6"/>
     </row>
-    <row r="547" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3" t="s">
         <v>628</v>
       </c>
@@ -13551,11 +15299,15 @@
       <c r="E547" s="3">
         <v>133</v>
       </c>
-      <c r="F547" s="5"/>
-      <c r="G547" s="5"/>
+      <c r="F547" s="5">
+        <v>137</v>
+      </c>
+      <c r="G547" s="5">
+        <v>5</v>
+      </c>
       <c r="H547" s="6"/>
     </row>
-    <row r="548" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
         <v>628</v>
       </c>
@@ -13571,11 +15323,15 @@
       <c r="E548" s="3">
         <v>995</v>
       </c>
-      <c r="F548" s="5"/>
-      <c r="G548" s="5"/>
+      <c r="F548" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G548" s="5">
+        <v>6</v>
+      </c>
       <c r="H548" s="6"/>
     </row>
-    <row r="549" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3" t="s">
         <v>628</v>
       </c>
@@ -13591,11 +15347,15 @@
       <c r="E549" s="3">
         <v>119</v>
       </c>
-      <c r="F549" s="5"/>
-      <c r="G549" s="5"/>
+      <c r="F549" s="5">
+        <v>122</v>
+      </c>
+      <c r="G549" s="5">
+        <v>5</v>
+      </c>
       <c r="H549" s="6"/>
     </row>
-    <row r="550" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
         <v>628</v>
       </c>
@@ -13611,11 +15371,15 @@
       <c r="E550" s="3">
         <v>261</v>
       </c>
-      <c r="F550" s="5"/>
-      <c r="G550" s="5"/>
+      <c r="F550" s="5">
+        <v>263</v>
+      </c>
+      <c r="G550" s="5">
+        <v>5</v>
+      </c>
       <c r="H550" s="6"/>
     </row>
-    <row r="551" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3" t="s">
         <v>641</v>
       </c>
@@ -13631,11 +15395,15 @@
       <c r="E551" s="3">
         <v>116</v>
       </c>
-      <c r="F551" s="5"/>
-      <c r="G551" s="5"/>
+      <c r="F551" s="5">
+        <v>119</v>
+      </c>
+      <c r="G551" s="5">
+        <v>5</v>
+      </c>
       <c r="H551" s="6"/>
     </row>
-    <row r="552" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
         <v>641</v>
       </c>
@@ -13651,11 +15419,15 @@
       <c r="E552" s="3">
         <v>627</v>
       </c>
-      <c r="F552" s="5"/>
-      <c r="G552" s="5"/>
+      <c r="F552" s="5">
+        <v>633</v>
+      </c>
+      <c r="G552" s="5">
+        <v>6</v>
+      </c>
       <c r="H552" s="6"/>
     </row>
-    <row r="553" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3" t="s">
         <v>641</v>
       </c>
@@ -13671,11 +15443,15 @@
       <c r="E553" s="3">
         <v>916</v>
       </c>
-      <c r="F553" s="5"/>
-      <c r="G553" s="5"/>
+      <c r="F553" s="5">
+        <v>922</v>
+      </c>
+      <c r="G553" s="5">
+        <v>6</v>
+      </c>
       <c r="H553" s="6"/>
     </row>
-    <row r="554" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
         <v>641</v>
       </c>
@@ -13691,11 +15467,15 @@
       <c r="E554" s="3">
         <v>1054</v>
       </c>
-      <c r="F554" s="5"/>
-      <c r="G554" s="5"/>
+      <c r="F554" s="5">
+        <v>1058</v>
+      </c>
+      <c r="G554" s="5">
+        <v>5</v>
+      </c>
       <c r="H554" s="6"/>
     </row>
-    <row r="555" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3" t="s">
         <v>641</v>
       </c>
@@ -13711,11 +15491,15 @@
       <c r="E555" s="3">
         <v>20</v>
       </c>
-      <c r="F555" s="5"/>
-      <c r="G555" s="5"/>
+      <c r="F555" s="5">
+        <v>20</v>
+      </c>
+      <c r="G555" s="5">
+        <v>5</v>
+      </c>
       <c r="H555" s="6"/>
     </row>
-    <row r="556" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
         <v>641</v>
       </c>
@@ -13735,7 +15519,7 @@
       <c r="G556" s="5"/>
       <c r="H556" s="6"/>
     </row>
-    <row r="557" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3" t="s">
         <v>641</v>
       </c>
@@ -13755,7 +15539,7 @@
       <c r="G557" s="5"/>
       <c r="H557" s="6"/>
     </row>
-    <row r="558" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
         <v>641</v>
       </c>
@@ -13775,7 +15559,7 @@
       <c r="G558" s="5"/>
       <c r="H558" s="6"/>
     </row>
-    <row r="559" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3" t="s">
         <v>641</v>
       </c>
@@ -13795,7 +15579,7 @@
       <c r="G559" s="5"/>
       <c r="H559" s="6"/>
     </row>
-    <row r="560" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
         <v>641</v>
       </c>
@@ -13815,7 +15599,7 @@
       <c r="G560" s="5"/>
       <c r="H560" s="6"/>
     </row>
-    <row r="561" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3" t="s">
         <v>641</v>
       </c>
@@ -13835,7 +15619,7 @@
       <c r="G561" s="5"/>
       <c r="H561" s="6"/>
     </row>
-    <row r="562" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
         <v>641</v>
       </c>
@@ -13855,7 +15639,7 @@
       <c r="G562" s="5"/>
       <c r="H562" s="6"/>
     </row>
-    <row r="563" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3" t="s">
         <v>641</v>
       </c>
@@ -13875,7 +15659,7 @@
       <c r="G563" s="5"/>
       <c r="H563" s="6"/>
     </row>
-    <row r="564" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
         <v>641</v>
       </c>
@@ -13895,7 +15679,7 @@
       <c r="G564" s="5"/>
       <c r="H564" s="6"/>
     </row>
-    <row r="565" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3" t="s">
         <v>641</v>
       </c>
@@ -13915,7 +15699,7 @@
       <c r="G565" s="5"/>
       <c r="H565" s="6"/>
     </row>
-    <row r="566" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
         <v>657</v>
       </c>
@@ -13931,11 +15715,15 @@
       <c r="E566" s="3">
         <v>77</v>
       </c>
-      <c r="F566" s="5"/>
-      <c r="G566" s="5"/>
+      <c r="F566" s="5">
+        <v>82</v>
+      </c>
+      <c r="G566" s="5">
+        <v>6</v>
+      </c>
       <c r="H566" s="6"/>
     </row>
-    <row r="567" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3" t="s">
         <v>657</v>
       </c>
@@ -13955,7 +15743,7 @@
       <c r="G567" s="5"/>
       <c r="H567" s="6"/>
     </row>
-    <row r="568" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
         <v>657</v>
       </c>
@@ -13971,11 +15759,15 @@
       <c r="E568" s="3">
         <v>369</v>
       </c>
-      <c r="F568" s="5"/>
-      <c r="G568" s="5"/>
+      <c r="F568" s="5">
+        <v>376</v>
+      </c>
+      <c r="G568" s="5">
+        <v>7</v>
+      </c>
       <c r="H568" s="6"/>
     </row>
-    <row r="569" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3" t="s">
         <v>657</v>
       </c>
@@ -13995,7 +15787,7 @@
       <c r="G569" s="5"/>
       <c r="H569" s="6"/>
     </row>
-    <row r="570" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
         <v>657</v>
       </c>
@@ -14011,11 +15803,15 @@
       <c r="E570" s="3">
         <v>0</v>
       </c>
-      <c r="F570" s="5"/>
-      <c r="G570" s="5"/>
+      <c r="F570" s="5">
+        <v>0</v>
+      </c>
+      <c r="G570" s="5">
+        <v>5</v>
+      </c>
       <c r="H570" s="6"/>
     </row>
-    <row r="571" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3" t="s">
         <v>657</v>
       </c>
@@ -14031,11 +15827,15 @@
       <c r="E571" s="3">
         <v>637</v>
       </c>
-      <c r="F571" s="5"/>
-      <c r="G571" s="5"/>
+      <c r="F571" s="5">
+        <v>642</v>
+      </c>
+      <c r="G571" s="5">
+        <v>6</v>
+      </c>
       <c r="H571" s="6"/>
     </row>
-    <row r="572" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
         <v>657</v>
       </c>
@@ -14051,11 +15851,15 @@
       <c r="E572" s="3">
         <v>305</v>
       </c>
-      <c r="F572" s="5"/>
-      <c r="G572" s="5"/>
+      <c r="F572" s="5">
+        <v>315</v>
+      </c>
+      <c r="G572" s="5">
+        <v>10</v>
+      </c>
       <c r="H572" s="6"/>
     </row>
-    <row r="573" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3" t="s">
         <v>657</v>
       </c>
@@ -14071,11 +15875,15 @@
       <c r="E573" s="3">
         <v>486</v>
       </c>
-      <c r="F573" s="5"/>
-      <c r="G573" s="5"/>
+      <c r="F573" s="5">
+        <v>495</v>
+      </c>
+      <c r="G573" s="5">
+        <v>9</v>
+      </c>
       <c r="H573" s="6"/>
     </row>
-    <row r="574" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
         <v>657</v>
       </c>
@@ -14091,11 +15899,15 @@
       <c r="E574" s="3">
         <v>132</v>
       </c>
-      <c r="F574" s="5"/>
-      <c r="G574" s="5"/>
+      <c r="F574" s="5">
+        <v>132</v>
+      </c>
+      <c r="G574" s="5">
+        <v>5</v>
+      </c>
       <c r="H574" s="6"/>
     </row>
-    <row r="575" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
         <v>657</v>
       </c>
@@ -14115,7 +15927,7 @@
       <c r="G575" s="5"/>
       <c r="H575" s="6"/>
     </row>
-    <row r="576" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>657</v>
       </c>
@@ -14131,11 +15943,15 @@
       <c r="E576" s="3">
         <v>392</v>
       </c>
-      <c r="F576" s="5"/>
-      <c r="G576" s="5"/>
+      <c r="F576" s="5">
+        <v>399</v>
+      </c>
+      <c r="G576" s="5">
+        <v>7</v>
+      </c>
       <c r="H576" s="6"/>
     </row>
-    <row r="577" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="3" t="s">
         <v>657</v>
       </c>
@@ -14151,11 +15967,15 @@
       <c r="E577" s="3">
         <v>727</v>
       </c>
-      <c r="F577" s="5"/>
-      <c r="G577" s="5"/>
+      <c r="F577" s="5">
+        <v>737</v>
+      </c>
+      <c r="G577" s="5">
+        <v>10</v>
+      </c>
       <c r="H577" s="6"/>
     </row>
-    <row r="578" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
         <v>657</v>
       </c>
@@ -14171,11 +15991,15 @@
       <c r="E578" s="3">
         <v>211</v>
       </c>
-      <c r="F578" s="5"/>
-      <c r="G578" s="5"/>
+      <c r="F578" s="5">
+        <v>216</v>
+      </c>
+      <c r="G578" s="5">
+        <v>6</v>
+      </c>
       <c r="H578" s="6"/>
     </row>
-    <row r="579" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="3" t="s">
         <v>657</v>
       </c>
@@ -14191,11 +16015,15 @@
       <c r="E579" s="3">
         <v>676</v>
       </c>
-      <c r="F579" s="5"/>
-      <c r="G579" s="5"/>
+      <c r="F579" s="5">
+        <v>684</v>
+      </c>
+      <c r="G579" s="5">
+        <v>8</v>
+      </c>
       <c r="H579" s="6"/>
     </row>
-    <row r="580" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
         <v>657</v>
       </c>
@@ -14211,11 +16039,15 @@
       <c r="E580" s="3">
         <v>24</v>
       </c>
-      <c r="F580" s="5"/>
-      <c r="G580" s="5"/>
+      <c r="F580" s="5">
+        <v>24</v>
+      </c>
+      <c r="G580" s="5">
+        <v>5</v>
+      </c>
       <c r="H580" s="6"/>
     </row>
-    <row r="581" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="3" t="s">
         <v>657</v>
       </c>
@@ -14231,11 +16063,15 @@
       <c r="E581" s="3">
         <v>213</v>
       </c>
-      <c r="F581" s="5"/>
-      <c r="G581" s="5"/>
+      <c r="F581" s="5">
+        <v>218</v>
+      </c>
+      <c r="G581" s="5">
+        <v>6</v>
+      </c>
       <c r="H581" s="6"/>
     </row>
-    <row r="582" spans="1:8" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
         <v>657</v>
       </c>
@@ -14251,19 +16087,19 @@
       <c r="E582" s="3">
         <v>497</v>
       </c>
-      <c r="F582" s="5"/>
-      <c r="G582" s="5"/>
+      <c r="F582" s="5">
+        <v>503</v>
+      </c>
+      <c r="G582" s="5">
+        <v>6</v>
+      </c>
       <c r="H582" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:H582" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="C"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A7:H582" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="9">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:H5"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="B4:C4"/>
@@ -14271,8 +16107,6 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/1_lecturas/inputs/registro_operario_mes.xlsx
+++ b/1_lecturas/inputs/registro_operario_mes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lecturas" sheetId="1" state="visible" r:id="rId1"/>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,12 +133,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,86 +508,86 @@
   <dimension ref="A1:H582"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="8" customWidth="1" style="8" min="1" max="1"/>
-    <col width="6" customWidth="1" style="8" min="2" max="2"/>
-    <col width="28" customWidth="1" style="8" min="3" max="3"/>
-    <col width="11" customWidth="1" style="8" min="4" max="6"/>
-    <col width="8" customWidth="1" style="8" min="7" max="7"/>
-    <col width="14" customWidth="1" style="8" min="8" max="8"/>
+    <col width="8" customWidth="1" style="9" min="1" max="1"/>
+    <col width="6" customWidth="1" style="9" min="2" max="2"/>
+    <col width="28" customWidth="1" style="9" min="3" max="3"/>
+    <col width="11" customWidth="1" style="9" min="4" max="6"/>
+    <col width="8" customWidth="1" style="9" min="7" max="7"/>
+    <col width="14" customWidth="1" style="9" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="9">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>LEYENDA — códigos válidos en obs_operario</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="8">
+    <row r="2" ht="16" customHeight="1" s="9">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Medidor cambiado</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>MARC_ACT &lt; MARC_ANT → no es retroceso, se acepta</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="8">
+    <row r="3" ht="16" customHeight="1" s="9">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Fuga visible reportada</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Alerta informativa al supervisor</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="8">
+    <row r="4" ht="16" customHeight="1" s="9">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Predio cerrado / inaccesible</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>MARC_ACT vacío → no es SIN_LECTURA, se acepta</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="8">
+    <row r="5" ht="16" customHeight="1" s="9">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>(vacío)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Lectura normal sin observación</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" s="8">
+    <row r="7" ht="22" customHeight="1" s="9">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MZ</t>
@@ -628,7 +629,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="8">
+    <row r="8" ht="16" customHeight="1" s="9">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -660,7 +661,7 @@
       </c>
       <c r="H8" s="6" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1" s="8">
+    <row r="9" ht="16" customHeight="1" s="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -692,7 +693,7 @@
       </c>
       <c r="H9" s="6" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1" s="8">
+    <row r="10" ht="16" customHeight="1" s="9">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -724,7 +725,7 @@
       </c>
       <c r="H10" s="6" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1" s="8">
+    <row r="11" ht="16" customHeight="1" s="9">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -756,7 +757,7 @@
       </c>
       <c r="H11" s="6" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1" s="8">
+    <row r="12" ht="16" customHeight="1" s="9">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -788,7 +789,7 @@
       </c>
       <c r="H12" s="6" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1" s="8">
+    <row r="13" ht="16" customHeight="1" s="9">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -820,7 +821,7 @@
       </c>
       <c r="H13" s="6" t="n"/>
     </row>
-    <row r="14" ht="16" customHeight="1" s="8">
+    <row r="14" ht="16" customHeight="1" s="9">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -846,7 +847,7 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
-    <row r="15" ht="16" customHeight="1" s="8">
+    <row r="15" ht="16" customHeight="1" s="9">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -878,7 +879,7 @@
       </c>
       <c r="H15" s="6" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1" s="8">
+    <row r="16" ht="16" customHeight="1" s="9">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -910,7 +911,7 @@
       </c>
       <c r="H16" s="6" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1" s="8">
+    <row r="17" ht="16" customHeight="1" s="9">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -942,7 +943,7 @@
       </c>
       <c r="H17" s="6" t="n"/>
     </row>
-    <row r="18" ht="16" customHeight="1" s="8">
+    <row r="18" ht="16" customHeight="1" s="9">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -974,7 +975,7 @@
       </c>
       <c r="H18" s="6" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1" s="8">
+    <row r="19" ht="16" customHeight="1" s="9">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -982,7 +983,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1002,7 +1003,7 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1" s="8">
+    <row r="20" ht="16" customHeight="1" s="9">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -1010,7 +1011,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1032,7 +1033,7 @@
       </c>
       <c r="H20" s="6" t="n"/>
     </row>
-    <row r="21" ht="16" customHeight="1" s="8">
+    <row r="21" ht="16" customHeight="1" s="9">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>A</t>
@@ -1064,7 +1065,7 @@
       </c>
       <c r="H21" s="6" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1" s="8">
+    <row r="22" ht="16" customHeight="1" s="9">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1096,7 +1097,7 @@
       </c>
       <c r="H22" s="6" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1" s="8">
+    <row r="23" ht="16" customHeight="1" s="9">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1128,7 +1129,7 @@
       </c>
       <c r="H23" s="6" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1" s="8">
+    <row r="24" ht="16" customHeight="1" s="9">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1160,7 +1161,7 @@
       </c>
       <c r="H24" s="6" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1" s="8">
+    <row r="25" ht="16" customHeight="1" s="9">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1192,7 +1193,7 @@
       </c>
       <c r="H25" s="6" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1" s="8">
+    <row r="26" ht="16" customHeight="1" s="9">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1224,7 +1225,7 @@
       </c>
       <c r="H26" s="6" t="n"/>
     </row>
-    <row r="27" ht="16" customHeight="1" s="8">
+    <row r="27" ht="16" customHeight="1" s="9">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1256,7 +1257,7 @@
       </c>
       <c r="H27" s="6" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1" s="8">
+    <row r="28" ht="16" customHeight="1" s="9">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1288,7 +1289,7 @@
       </c>
       <c r="H28" s="6" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1" s="8">
+    <row r="29" ht="16" customHeight="1" s="9">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1320,7 +1321,7 @@
       </c>
       <c r="H29" s="6" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1" s="8">
+    <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1352,7 +1353,7 @@
       </c>
       <c r="H30" s="6" t="n"/>
     </row>
-    <row r="31" ht="16" customHeight="1" s="8">
+    <row r="31" ht="16" customHeight="1" s="9">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1384,7 +1385,7 @@
       </c>
       <c r="H31" s="6" t="n"/>
     </row>
-    <row r="32" ht="16" customHeight="1" s="8">
+    <row r="32" ht="16" customHeight="1" s="9">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1416,7 +1417,7 @@
       </c>
       <c r="H32" s="6" t="n"/>
     </row>
-    <row r="33" ht="16" customHeight="1" s="8">
+    <row r="33" ht="16" customHeight="1" s="9">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1448,7 +1449,7 @@
       </c>
       <c r="H33" s="6" t="n"/>
     </row>
-    <row r="34" ht="16" customHeight="1" s="8">
+    <row r="34" ht="16" customHeight="1" s="9">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1480,7 +1481,7 @@
       </c>
       <c r="H34" s="6" t="n"/>
     </row>
-    <row r="35" ht="16" customHeight="1" s="8">
+    <row r="35" ht="16" customHeight="1" s="9">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1512,7 +1513,7 @@
       </c>
       <c r="H35" s="6" t="n"/>
     </row>
-    <row r="36" ht="16" customHeight="1" s="8">
+    <row r="36" ht="16" customHeight="1" s="9">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1544,7 +1545,7 @@
       </c>
       <c r="H36" s="6" t="n"/>
     </row>
-    <row r="37" ht="16" customHeight="1" s="8">
+    <row r="37" ht="16" customHeight="1" s="9">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1570,7 +1571,7 @@
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="6" t="n"/>
     </row>
-    <row r="38" ht="16" customHeight="1" s="8">
+    <row r="38" ht="16" customHeight="1" s="9">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1602,7 +1603,7 @@
       </c>
       <c r="H38" s="6" t="n"/>
     </row>
-    <row r="39" ht="16" customHeight="1" s="8">
+    <row r="39" ht="16" customHeight="1" s="9">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1634,7 +1635,7 @@
       </c>
       <c r="H39" s="6" t="n"/>
     </row>
-    <row r="40" ht="16" customHeight="1" s="8">
+    <row r="40" ht="16" customHeight="1" s="9">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1666,7 +1667,7 @@
       </c>
       <c r="H40" s="6" t="n"/>
     </row>
-    <row r="41" ht="16" customHeight="1" s="8">
+    <row r="41" ht="16" customHeight="1" s="9">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1698,7 +1699,7 @@
       </c>
       <c r="H41" s="6" t="n"/>
     </row>
-    <row r="42" ht="16" customHeight="1" s="8">
+    <row r="42" ht="16" customHeight="1" s="9">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -1730,7 +1731,7 @@
       </c>
       <c r="H42" s="6" t="n"/>
     </row>
-    <row r="43" ht="16" customHeight="1" s="8">
+    <row r="43" ht="16" customHeight="1" s="9">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1762,7 +1763,7 @@
       </c>
       <c r="H43" s="6" t="n"/>
     </row>
-    <row r="44" ht="16" customHeight="1" s="8">
+    <row r="44" ht="16" customHeight="1" s="9">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="H44" s="6" t="n"/>
     </row>
-    <row r="45" ht="16" customHeight="1" s="8">
+    <row r="45" ht="16" customHeight="1" s="9">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="H45" s="6" t="n"/>
     </row>
-    <row r="46" ht="16" customHeight="1" s="8">
+    <row r="46" ht="16" customHeight="1" s="9">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1856,7 +1857,7 @@
       </c>
       <c r="H46" s="6" t="n"/>
     </row>
-    <row r="47" ht="16" customHeight="1" s="8">
+    <row r="47" ht="16" customHeight="1" s="9">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1888,7 +1889,7 @@
       </c>
       <c r="H47" s="6" t="n"/>
     </row>
-    <row r="48" ht="16" customHeight="1" s="8">
+    <row r="48" ht="16" customHeight="1" s="9">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1920,7 +1921,7 @@
       </c>
       <c r="H48" s="6" t="n"/>
     </row>
-    <row r="49" ht="16" customHeight="1" s="8">
+    <row r="49" ht="16" customHeight="1" s="9">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1952,7 +1953,7 @@
       </c>
       <c r="H49" s="6" t="n"/>
     </row>
-    <row r="50" ht="16" customHeight="1" s="8">
+    <row r="50" ht="16" customHeight="1" s="9">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -1984,7 +1985,7 @@
       </c>
       <c r="H50" s="6" t="n"/>
     </row>
-    <row r="51" ht="16" customHeight="1" s="8">
+    <row r="51" ht="16" customHeight="1" s="9">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2016,7 +2017,7 @@
       </c>
       <c r="H51" s="6" t="n"/>
     </row>
-    <row r="52" ht="16" customHeight="1" s="8">
+    <row r="52" ht="16" customHeight="1" s="9">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2048,7 +2049,7 @@
       </c>
       <c r="H52" s="6" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1" s="8">
+    <row r="53" ht="16" customHeight="1" s="9">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2080,7 +2081,7 @@
       </c>
       <c r="H53" s="6" t="n"/>
     </row>
-    <row r="54" ht="16" customHeight="1" s="8">
+    <row r="54" ht="16" customHeight="1" s="9">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2112,7 +2113,7 @@
       </c>
       <c r="H54" s="6" t="n"/>
     </row>
-    <row r="55" ht="16" customHeight="1" s="8">
+    <row r="55" ht="16" customHeight="1" s="9">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2142,7 +2143,7 @@
       </c>
       <c r="H55" s="6" t="n"/>
     </row>
-    <row r="56" ht="16" customHeight="1" s="8">
+    <row r="56" ht="16" customHeight="1" s="9">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2174,7 +2175,7 @@
       </c>
       <c r="H56" s="6" t="n"/>
     </row>
-    <row r="57" ht="16" customHeight="1" s="8">
+    <row r="57" ht="16" customHeight="1" s="9">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="H57" s="6" t="n"/>
     </row>
-    <row r="58" ht="16" customHeight="1" s="8">
+    <row r="58" ht="16" customHeight="1" s="9">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2238,7 +2239,7 @@
       </c>
       <c r="H58" s="6" t="n"/>
     </row>
-    <row r="59" ht="16" customHeight="1" s="8">
+    <row r="59" ht="16" customHeight="1" s="9">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2270,7 +2271,7 @@
       </c>
       <c r="H59" s="6" t="n"/>
     </row>
-    <row r="60" ht="16" customHeight="1" s="8">
+    <row r="60" ht="16" customHeight="1" s="9">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2302,7 +2303,7 @@
       </c>
       <c r="H60" s="6" t="n"/>
     </row>
-    <row r="61" ht="16" customHeight="1" s="8">
+    <row r="61" ht="16" customHeight="1" s="9">
       <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2334,7 +2335,7 @@
       </c>
       <c r="H61" s="6" t="n"/>
     </row>
-    <row r="62" ht="16" customHeight="1" s="8">
+    <row r="62" ht="16" customHeight="1" s="9">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="H62" s="6" t="n"/>
     </row>
-    <row r="63" ht="16" customHeight="1" s="8">
+    <row r="63" ht="16" customHeight="1" s="9">
       <c r="A63" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2396,7 +2397,7 @@
       </c>
       <c r="H63" s="6" t="n"/>
     </row>
-    <row r="64" ht="16" customHeight="1" s="8">
+    <row r="64" ht="16" customHeight="1" s="9">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2428,7 +2429,7 @@
       </c>
       <c r="H64" s="6" t="n"/>
     </row>
-    <row r="65" ht="16" customHeight="1" s="8">
+    <row r="65" ht="16" customHeight="1" s="9">
       <c r="A65" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2460,7 +2461,7 @@
       </c>
       <c r="H65" s="6" t="n"/>
     </row>
-    <row r="66" ht="16" customHeight="1" s="8">
+    <row r="66" ht="16" customHeight="1" s="9">
       <c r="A66" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2492,7 +2493,7 @@
       </c>
       <c r="H66" s="6" t="n"/>
     </row>
-    <row r="67" ht="16" customHeight="1" s="8">
+    <row r="67" ht="16" customHeight="1" s="9">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2524,7 +2525,7 @@
       </c>
       <c r="H67" s="6" t="n"/>
     </row>
-    <row r="68" ht="16" customHeight="1" s="8">
+    <row r="68" ht="16" customHeight="1" s="9">
       <c r="A68" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2556,7 +2557,7 @@
       </c>
       <c r="H68" s="6" t="n"/>
     </row>
-    <row r="69" ht="16" customHeight="1" s="8">
+    <row r="69" ht="16" customHeight="1" s="9">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2588,7 +2589,7 @@
       </c>
       <c r="H69" s="6" t="n"/>
     </row>
-    <row r="70" ht="16" customHeight="1" s="8">
+    <row r="70" ht="16" customHeight="1" s="9">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2620,7 +2621,7 @@
       </c>
       <c r="H70" s="6" t="n"/>
     </row>
-    <row r="71" ht="16" customHeight="1" s="8">
+    <row r="71" ht="16" customHeight="1" s="9">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2652,7 +2653,7 @@
       </c>
       <c r="H71" s="6" t="n"/>
     </row>
-    <row r="72" ht="16" customHeight="1" s="8">
+    <row r="72" ht="16" customHeight="1" s="9">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2684,7 +2685,7 @@
       </c>
       <c r="H72" s="6" t="n"/>
     </row>
-    <row r="73" ht="16" customHeight="1" s="8">
+    <row r="73" ht="16" customHeight="1" s="9">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2710,7 +2711,7 @@
       <c r="G73" s="5" t="n"/>
       <c r="H73" s="6" t="n"/>
     </row>
-    <row r="74" ht="16" customHeight="1" s="8">
+    <row r="74" ht="16" customHeight="1" s="9">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2742,7 +2743,7 @@
       </c>
       <c r="H74" s="6" t="n"/>
     </row>
-    <row r="75" ht="16" customHeight="1" s="8">
+    <row r="75" ht="16" customHeight="1" s="9">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2768,7 +2769,7 @@
       <c r="G75" s="5" t="n"/>
       <c r="H75" s="6" t="n"/>
     </row>
-    <row r="76" ht="16" customHeight="1" s="8">
+    <row r="76" ht="16" customHeight="1" s="9">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2794,7 +2795,7 @@
       <c r="G76" s="5" t="n"/>
       <c r="H76" s="6" t="n"/>
     </row>
-    <row r="77" ht="16" customHeight="1" s="8">
+    <row r="77" ht="16" customHeight="1" s="9">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2826,7 +2827,7 @@
       </c>
       <c r="H77" s="6" t="n"/>
     </row>
-    <row r="78" ht="16" customHeight="1" s="8">
+    <row r="78" ht="16" customHeight="1" s="9">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="H78" s="6" t="n"/>
     </row>
-    <row r="79" ht="16" customHeight="1" s="8">
+    <row r="79" ht="16" customHeight="1" s="9">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2890,7 +2891,7 @@
       </c>
       <c r="H79" s="6" t="n"/>
     </row>
-    <row r="80" ht="16" customHeight="1" s="8">
+    <row r="80" ht="16" customHeight="1" s="9">
       <c r="A80" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2922,7 +2923,7 @@
       </c>
       <c r="H80" s="6" t="n"/>
     </row>
-    <row r="81" ht="16" customHeight="1" s="8">
+    <row r="81" ht="16" customHeight="1" s="9">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2954,7 +2955,7 @@
       </c>
       <c r="H81" s="6" t="n"/>
     </row>
-    <row r="82" ht="16" customHeight="1" s="8">
+    <row r="82" ht="16" customHeight="1" s="9">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -2986,7 +2987,7 @@
       </c>
       <c r="H82" s="6" t="n"/>
     </row>
-    <row r="83" ht="16" customHeight="1" s="8">
+    <row r="83" ht="16" customHeight="1" s="9">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="H83" s="6" t="n"/>
     </row>
-    <row r="84" ht="16" customHeight="1" s="8">
+    <row r="84" ht="16" customHeight="1" s="9">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -3044,7 +3045,7 @@
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="6" t="n"/>
     </row>
-    <row r="85" ht="16" customHeight="1" s="8">
+    <row r="85" ht="16" customHeight="1" s="9">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -3076,7 +3077,7 @@
       </c>
       <c r="H85" s="6" t="n"/>
     </row>
-    <row r="86" ht="16" customHeight="1" s="8">
+    <row r="86" ht="16" customHeight="1" s="9">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -3108,7 +3109,7 @@
       </c>
       <c r="H86" s="6" t="n"/>
     </row>
-    <row r="87" ht="16" customHeight="1" s="8">
+    <row r="87" ht="16" customHeight="1" s="9">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>C</t>
@@ -3134,7 +3135,7 @@
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="6" t="n"/>
     </row>
-    <row r="88" ht="16" customHeight="1" s="8">
+    <row r="88" ht="16" customHeight="1" s="9">
       <c r="A88" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3166,7 +3167,7 @@
       </c>
       <c r="H88" s="6" t="n"/>
     </row>
-    <row r="89" ht="16" customHeight="1" s="8">
+    <row r="89" ht="16" customHeight="1" s="9">
       <c r="A89" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3198,7 +3199,7 @@
       </c>
       <c r="H89" s="6" t="n"/>
     </row>
-    <row r="90" ht="16" customHeight="1" s="8">
+    <row r="90" ht="16" customHeight="1" s="9">
       <c r="A90" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3230,7 +3231,7 @@
       </c>
       <c r="H90" s="6" t="n"/>
     </row>
-    <row r="91" ht="16" customHeight="1" s="8">
+    <row r="91" ht="16" customHeight="1" s="9">
       <c r="A91" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3262,7 +3263,7 @@
       </c>
       <c r="H91" s="6" t="n"/>
     </row>
-    <row r="92" ht="16" customHeight="1" s="8">
+    <row r="92" ht="16" customHeight="1" s="9">
       <c r="A92" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3294,7 +3295,7 @@
       </c>
       <c r="H92" s="6" t="n"/>
     </row>
-    <row r="93" ht="16" customHeight="1" s="8">
+    <row r="93" ht="16" customHeight="1" s="9">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3326,7 +3327,7 @@
       </c>
       <c r="H93" s="6" t="n"/>
     </row>
-    <row r="94" ht="16" customHeight="1" s="8">
+    <row r="94" ht="16" customHeight="1" s="9">
       <c r="A94" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3358,7 +3359,7 @@
       </c>
       <c r="H94" s="6" t="n"/>
     </row>
-    <row r="95" ht="16" customHeight="1" s="8">
+    <row r="95" ht="16" customHeight="1" s="9">
       <c r="A95" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3390,7 +3391,7 @@
       </c>
       <c r="H95" s="6" t="n"/>
     </row>
-    <row r="96" ht="16" customHeight="1" s="8">
+    <row r="96" ht="16" customHeight="1" s="9">
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="H96" s="6" t="n"/>
     </row>
-    <row r="97" ht="16" customHeight="1" s="8">
+    <row r="97" ht="16" customHeight="1" s="9">
       <c r="A97" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3454,7 +3455,7 @@
       </c>
       <c r="H97" s="6" t="n"/>
     </row>
-    <row r="98" ht="16" customHeight="1" s="8">
+    <row r="98" ht="16" customHeight="1" s="9">
       <c r="A98" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3486,7 +3487,7 @@
       </c>
       <c r="H98" s="6" t="n"/>
     </row>
-    <row r="99" ht="16" customHeight="1" s="8">
+    <row r="99" ht="16" customHeight="1" s="9">
       <c r="A99" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3518,7 +3519,7 @@
       </c>
       <c r="H99" s="6" t="n"/>
     </row>
-    <row r="100" ht="16" customHeight="1" s="8">
+    <row r="100" ht="16" customHeight="1" s="9">
       <c r="A100" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3550,7 +3551,7 @@
       </c>
       <c r="H100" s="6" t="n"/>
     </row>
-    <row r="101" ht="16" customHeight="1" s="8">
+    <row r="101" ht="16" customHeight="1" s="9">
       <c r="A101" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3576,7 +3577,7 @@
       <c r="G101" s="5" t="n"/>
       <c r="H101" s="6" t="n"/>
     </row>
-    <row r="102" ht="16" customHeight="1" s="8">
+    <row r="102" ht="16" customHeight="1" s="9">
       <c r="A102" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3608,7 +3609,7 @@
       </c>
       <c r="H102" s="6" t="n"/>
     </row>
-    <row r="103" ht="16" customHeight="1" s="8">
+    <row r="103" ht="16" customHeight="1" s="9">
       <c r="A103" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3640,7 +3641,7 @@
       </c>
       <c r="H103" s="6" t="n"/>
     </row>
-    <row r="104" ht="16" customHeight="1" s="8">
+    <row r="104" ht="16" customHeight="1" s="9">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3672,7 +3673,7 @@
       </c>
       <c r="H104" s="6" t="n"/>
     </row>
-    <row r="105" ht="16" customHeight="1" s="8">
+    <row r="105" ht="16" customHeight="1" s="9">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3704,7 +3705,7 @@
       </c>
       <c r="H105" s="6" t="n"/>
     </row>
-    <row r="106" ht="16" customHeight="1" s="8">
+    <row r="106" ht="16" customHeight="1" s="9">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3736,7 +3737,7 @@
       </c>
       <c r="H106" s="6" t="n"/>
     </row>
-    <row r="107" ht="16" customHeight="1" s="8">
+    <row r="107" ht="16" customHeight="1" s="9">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3768,7 +3769,7 @@
       </c>
       <c r="H107" s="6" t="n"/>
     </row>
-    <row r="108" ht="16" customHeight="1" s="8">
+    <row r="108" ht="16" customHeight="1" s="9">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3794,7 +3795,7 @@
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="6" t="n"/>
     </row>
-    <row r="109" ht="16" customHeight="1" s="8">
+    <row r="109" ht="16" customHeight="1" s="9">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3826,7 +3827,7 @@
       </c>
       <c r="H109" s="6" t="n"/>
     </row>
-    <row r="110" ht="16" customHeight="1" s="8">
+    <row r="110" ht="16" customHeight="1" s="9">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3858,7 +3859,7 @@
       </c>
       <c r="H110" s="6" t="n"/>
     </row>
-    <row r="111" ht="16" customHeight="1" s="8">
+    <row r="111" ht="16" customHeight="1" s="9">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3884,7 +3885,7 @@
       <c r="G111" s="5" t="n"/>
       <c r="H111" s="6" t="n"/>
     </row>
-    <row r="112" ht="16" customHeight="1" s="8">
+    <row r="112" ht="16" customHeight="1" s="9">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3916,7 +3917,7 @@
       </c>
       <c r="H112" s="6" t="n"/>
     </row>
-    <row r="113" ht="16" customHeight="1" s="8">
+    <row r="113" ht="16" customHeight="1" s="9">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3948,7 +3949,7 @@
       </c>
       <c r="H113" s="6" t="n"/>
     </row>
-    <row r="114" ht="16" customHeight="1" s="8">
+    <row r="114" ht="16" customHeight="1" s="9">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -3980,7 +3981,7 @@
       </c>
       <c r="H114" s="6" t="n"/>
     </row>
-    <row r="115" ht="16" customHeight="1" s="8">
+    <row r="115" ht="16" customHeight="1" s="9">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4012,7 +4013,7 @@
       </c>
       <c r="H115" s="6" t="n"/>
     </row>
-    <row r="116" ht="16" customHeight="1" s="8">
+    <row r="116" ht="16" customHeight="1" s="9">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4044,7 +4045,7 @@
       </c>
       <c r="H116" s="6" t="n"/>
     </row>
-    <row r="117" ht="16" customHeight="1" s="8">
+    <row r="117" ht="16" customHeight="1" s="9">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4076,7 +4077,7 @@
       </c>
       <c r="H117" s="6" t="n"/>
     </row>
-    <row r="118" ht="16" customHeight="1" s="8">
+    <row r="118" ht="16" customHeight="1" s="9">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4108,7 +4109,7 @@
       </c>
       <c r="H118" s="6" t="n"/>
     </row>
-    <row r="119" ht="16" customHeight="1" s="8">
+    <row r="119" ht="16" customHeight="1" s="9">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4140,7 +4141,7 @@
       </c>
       <c r="H119" s="6" t="n"/>
     </row>
-    <row r="120" ht="16" customHeight="1" s="8">
+    <row r="120" ht="16" customHeight="1" s="9">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4172,7 +4173,7 @@
       </c>
       <c r="H120" s="6" t="n"/>
     </row>
-    <row r="121" ht="16" customHeight="1" s="8">
+    <row r="121" ht="16" customHeight="1" s="9">
       <c r="A121" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4204,7 +4205,7 @@
       </c>
       <c r="H121" s="6" t="n"/>
     </row>
-    <row r="122" ht="16" customHeight="1" s="8">
+    <row r="122" ht="16" customHeight="1" s="9">
       <c r="A122" s="3" t="inlineStr">
         <is>
           <t>E</t>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="H122" s="6" t="n"/>
     </row>
-    <row r="123" ht="16" customHeight="1" s="8">
+    <row r="123" ht="16" customHeight="1" s="9">
       <c r="A123" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4268,7 +4269,7 @@
       </c>
       <c r="H123" s="6" t="n"/>
     </row>
-    <row r="124" ht="16" customHeight="1" s="8">
+    <row r="124" ht="16" customHeight="1" s="9">
       <c r="A124" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4294,7 +4295,7 @@
       <c r="G124" s="5" t="n"/>
       <c r="H124" s="6" t="n"/>
     </row>
-    <row r="125" ht="16" customHeight="1" s="8">
+    <row r="125" ht="16" customHeight="1" s="9">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4326,7 +4327,7 @@
       </c>
       <c r="H125" s="6" t="n"/>
     </row>
-    <row r="126" ht="16" customHeight="1" s="8">
+    <row r="126" ht="16" customHeight="1" s="9">
       <c r="A126" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4358,7 +4359,7 @@
       </c>
       <c r="H126" s="6" t="n"/>
     </row>
-    <row r="127" ht="16" customHeight="1" s="8">
+    <row r="127" ht="16" customHeight="1" s="9">
       <c r="A127" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4390,7 +4391,7 @@
       </c>
       <c r="H127" s="6" t="n"/>
     </row>
-    <row r="128" ht="16" customHeight="1" s="8">
+    <row r="128" ht="16" customHeight="1" s="9">
       <c r="A128" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4422,7 +4423,7 @@
       </c>
       <c r="H128" s="6" t="n"/>
     </row>
-    <row r="129" ht="16" customHeight="1" s="8">
+    <row r="129" ht="16" customHeight="1" s="9">
       <c r="A129" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4454,7 +4455,7 @@
       </c>
       <c r="H129" s="6" t="n"/>
     </row>
-    <row r="130" ht="16" customHeight="1" s="8">
+    <row r="130" ht="16" customHeight="1" s="9">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4486,7 +4487,7 @@
       </c>
       <c r="H130" s="6" t="n"/>
     </row>
-    <row r="131" ht="16" customHeight="1" s="8">
+    <row r="131" ht="16" customHeight="1" s="9">
       <c r="A131" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4518,7 +4519,7 @@
       </c>
       <c r="H131" s="6" t="n"/>
     </row>
-    <row r="132" ht="16" customHeight="1" s="8">
+    <row r="132" ht="16" customHeight="1" s="9">
       <c r="A132" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4550,7 +4551,7 @@
       </c>
       <c r="H132" s="6" t="n"/>
     </row>
-    <row r="133" ht="16" customHeight="1" s="8">
+    <row r="133" ht="16" customHeight="1" s="9">
       <c r="A133" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="H133" s="6" t="n"/>
     </row>
-    <row r="134" ht="16" customHeight="1" s="8">
+    <row r="134" ht="16" customHeight="1" s="9">
       <c r="A134" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4614,7 +4615,7 @@
       </c>
       <c r="H134" s="6" t="n"/>
     </row>
-    <row r="135" ht="16" customHeight="1" s="8">
+    <row r="135" ht="16" customHeight="1" s="9">
       <c r="A135" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4646,7 +4647,7 @@
       </c>
       <c r="H135" s="6" t="n"/>
     </row>
-    <row r="136" ht="16" customHeight="1" s="8">
+    <row r="136" ht="16" customHeight="1" s="9">
       <c r="A136" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4678,7 +4679,7 @@
       </c>
       <c r="H136" s="6" t="n"/>
     </row>
-    <row r="137" ht="16" customHeight="1" s="8">
+    <row r="137" ht="16" customHeight="1" s="9">
       <c r="A137" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -4710,7 +4711,7 @@
       </c>
       <c r="H137" s="6" t="n"/>
     </row>
-    <row r="138" ht="16" customHeight="1" s="8">
+    <row r="138" ht="16" customHeight="1" s="9">
       <c r="A138" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4742,7 +4743,7 @@
       </c>
       <c r="H138" s="6" t="n"/>
     </row>
-    <row r="139" ht="16" customHeight="1" s="8">
+    <row r="139" ht="16" customHeight="1" s="9">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4774,7 +4775,7 @@
       </c>
       <c r="H139" s="6" t="n"/>
     </row>
-    <row r="140" ht="16" customHeight="1" s="8">
+    <row r="140" ht="16" customHeight="1" s="9">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4806,7 +4807,7 @@
       </c>
       <c r="H140" s="6" t="n"/>
     </row>
-    <row r="141" ht="16" customHeight="1" s="8">
+    <row r="141" ht="16" customHeight="1" s="9">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4838,7 +4839,7 @@
       </c>
       <c r="H141" s="6" t="n"/>
     </row>
-    <row r="142" ht="16" customHeight="1" s="8">
+    <row r="142" ht="16" customHeight="1" s="9">
       <c r="A142" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4870,7 +4871,7 @@
       </c>
       <c r="H142" s="6" t="n"/>
     </row>
-    <row r="143" ht="16" customHeight="1" s="8">
+    <row r="143" ht="16" customHeight="1" s="9">
       <c r="A143" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4902,7 +4903,7 @@
       </c>
       <c r="H143" s="6" t="n"/>
     </row>
-    <row r="144" ht="16" customHeight="1" s="8">
+    <row r="144" ht="16" customHeight="1" s="9">
       <c r="A144" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4934,7 +4935,7 @@
       </c>
       <c r="H144" s="6" t="n"/>
     </row>
-    <row r="145" ht="16" customHeight="1" s="8">
+    <row r="145" ht="16" customHeight="1" s="9">
       <c r="A145" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4966,7 +4967,7 @@
       </c>
       <c r="H145" s="6" t="n"/>
     </row>
-    <row r="146" ht="16" customHeight="1" s="8">
+    <row r="146" ht="16" customHeight="1" s="9">
       <c r="A146" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -4998,7 +4999,7 @@
       </c>
       <c r="H146" s="6" t="n"/>
     </row>
-    <row r="147" ht="16" customHeight="1" s="8">
+    <row r="147" ht="16" customHeight="1" s="9">
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5024,7 +5025,7 @@
       <c r="G147" s="5" t="n"/>
       <c r="H147" s="6" t="n"/>
     </row>
-    <row r="148" ht="16" customHeight="1" s="8">
+    <row r="148" ht="16" customHeight="1" s="9">
       <c r="A148" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5056,7 +5057,7 @@
       </c>
       <c r="H148" s="6" t="n"/>
     </row>
-    <row r="149" ht="16" customHeight="1" s="8">
+    <row r="149" ht="16" customHeight="1" s="9">
       <c r="A149" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5088,7 +5089,7 @@
       </c>
       <c r="H149" s="6" t="n"/>
     </row>
-    <row r="150" ht="16" customHeight="1" s="8">
+    <row r="150" ht="16" customHeight="1" s="9">
       <c r="A150" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5120,7 +5121,7 @@
       </c>
       <c r="H150" s="6" t="n"/>
     </row>
-    <row r="151" ht="16" customHeight="1" s="8">
+    <row r="151" ht="16" customHeight="1" s="9">
       <c r="A151" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5152,7 +5153,7 @@
       </c>
       <c r="H151" s="6" t="n"/>
     </row>
-    <row r="152" ht="16" customHeight="1" s="8">
+    <row r="152" ht="16" customHeight="1" s="9">
       <c r="A152" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5184,7 +5185,7 @@
       </c>
       <c r="H152" s="6" t="n"/>
     </row>
-    <row r="153" ht="16" customHeight="1" s="8">
+    <row r="153" ht="16" customHeight="1" s="9">
       <c r="A153" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5216,7 +5217,7 @@
       </c>
       <c r="H153" s="6" t="n"/>
     </row>
-    <row r="154" ht="16" customHeight="1" s="8">
+    <row r="154" ht="16" customHeight="1" s="9">
       <c r="A154" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5248,7 +5249,7 @@
       </c>
       <c r="H154" s="6" t="n"/>
     </row>
-    <row r="155" ht="16" customHeight="1" s="8">
+    <row r="155" ht="16" customHeight="1" s="9">
       <c r="A155" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5272,13 +5273,9 @@
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="5" t="n"/>
       <c r="G155" s="5" t="n"/>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>no existe este lote</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16" customHeight="1" s="8">
+      <c r="H155" s="6" t="n"/>
+    </row>
+    <row r="156" ht="16" customHeight="1" s="9">
       <c r="A156" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5308,7 +5305,7 @@
       </c>
       <c r="H156" s="6" t="n"/>
     </row>
-    <row r="157" ht="16" customHeight="1" s="8">
+    <row r="157" ht="16" customHeight="1" s="9">
       <c r="A157" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5334,13 +5331,9 @@
       </c>
       <c r="F157" s="5" t="n"/>
       <c r="G157" s="5" t="n"/>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>cambiar nombre usuario</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1" s="8">
+      <c r="H157" s="6" t="n"/>
+    </row>
+    <row r="158" ht="16" customHeight="1" s="9">
       <c r="A158" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5372,7 +5365,7 @@
       </c>
       <c r="H158" s="6" t="n"/>
     </row>
-    <row r="159" ht="16" customHeight="1" s="8">
+    <row r="159" ht="16" customHeight="1" s="9">
       <c r="A159" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5404,7 +5397,7 @@
       </c>
       <c r="H159" s="6" t="n"/>
     </row>
-    <row r="160" ht="16" customHeight="1" s="8">
+    <row r="160" ht="16" customHeight="1" s="9">
       <c r="A160" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5436,7 +5429,7 @@
       </c>
       <c r="H160" s="6" t="n"/>
     </row>
-    <row r="161" ht="16" customHeight="1" s="8">
+    <row r="161" ht="16" customHeight="1" s="9">
       <c r="A161" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5468,7 +5461,7 @@
       </c>
       <c r="H161" s="6" t="n"/>
     </row>
-    <row r="162" ht="16" customHeight="1" s="8">
+    <row r="162" ht="16" customHeight="1" s="9">
       <c r="A162" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5500,7 +5493,7 @@
       </c>
       <c r="H162" s="6" t="n"/>
     </row>
-    <row r="163" ht="16" customHeight="1" s="8">
+    <row r="163" ht="16" customHeight="1" s="9">
       <c r="A163" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5532,7 +5525,7 @@
       </c>
       <c r="H163" s="6" t="n"/>
     </row>
-    <row r="164" ht="16" customHeight="1" s="8">
+    <row r="164" ht="16" customHeight="1" s="9">
       <c r="A164" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5564,7 +5557,7 @@
       </c>
       <c r="H164" s="6" t="n"/>
     </row>
-    <row r="165" ht="16" customHeight="1" s="8">
+    <row r="165" ht="16" customHeight="1" s="9">
       <c r="A165" s="3" t="inlineStr">
         <is>
           <t>G</t>
@@ -5596,7 +5589,7 @@
       </c>
       <c r="H165" s="6" t="n"/>
     </row>
-    <row r="166" ht="16" customHeight="1" s="8">
+    <row r="166" ht="16" customHeight="1" s="9">
       <c r="A166" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5628,7 +5621,7 @@
       </c>
       <c r="H166" s="6" t="n"/>
     </row>
-    <row r="167" ht="16" customHeight="1" s="8">
+    <row r="167" ht="16" customHeight="1" s="9">
       <c r="A167" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5660,7 +5653,7 @@
       </c>
       <c r="H167" s="6" t="n"/>
     </row>
-    <row r="168" ht="16" customHeight="1" s="8">
+    <row r="168" ht="16" customHeight="1" s="9">
       <c r="A168" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5692,7 +5685,7 @@
       </c>
       <c r="H168" s="6" t="n"/>
     </row>
-    <row r="169" ht="16" customHeight="1" s="8">
+    <row r="169" ht="16" customHeight="1" s="9">
       <c r="A169" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5724,7 +5717,7 @@
       </c>
       <c r="H169" s="6" t="n"/>
     </row>
-    <row r="170" ht="16" customHeight="1" s="8">
+    <row r="170" ht="16" customHeight="1" s="9">
       <c r="A170" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5756,7 +5749,7 @@
       </c>
       <c r="H170" s="6" t="n"/>
     </row>
-    <row r="171" ht="16" customHeight="1" s="8">
+    <row r="171" ht="16" customHeight="1" s="9">
       <c r="A171" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5782,7 +5775,7 @@
       <c r="G171" s="5" t="n"/>
       <c r="H171" s="6" t="n"/>
     </row>
-    <row r="172" ht="16" customHeight="1" s="8">
+    <row r="172" ht="16" customHeight="1" s="9">
       <c r="A172" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5814,7 +5807,7 @@
       </c>
       <c r="H172" s="6" t="n"/>
     </row>
-    <row r="173" ht="16" customHeight="1" s="8">
+    <row r="173" ht="16" customHeight="1" s="9">
       <c r="A173" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5846,7 +5839,7 @@
       </c>
       <c r="H173" s="6" t="n"/>
     </row>
-    <row r="174" ht="16" customHeight="1" s="8">
+    <row r="174" ht="16" customHeight="1" s="9">
       <c r="A174" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5878,7 +5871,7 @@
       </c>
       <c r="H174" s="6" t="n"/>
     </row>
-    <row r="175" ht="16" customHeight="1" s="8">
+    <row r="175" ht="16" customHeight="1" s="9">
       <c r="A175" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5910,7 +5903,7 @@
       </c>
       <c r="H175" s="6" t="n"/>
     </row>
-    <row r="176" ht="16" customHeight="1" s="8">
+    <row r="176" ht="16" customHeight="1" s="9">
       <c r="A176" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5942,7 +5935,7 @@
       </c>
       <c r="H176" s="6" t="n"/>
     </row>
-    <row r="177" ht="16" customHeight="1" s="8">
+    <row r="177" ht="16" customHeight="1" s="9">
       <c r="A177" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -5974,7 +5967,7 @@
       </c>
       <c r="H177" s="6" t="n"/>
     </row>
-    <row r="178" ht="16" customHeight="1" s="8">
+    <row r="178" ht="16" customHeight="1" s="9">
       <c r="A178" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6006,7 +5999,7 @@
       </c>
       <c r="H178" s="6" t="n"/>
     </row>
-    <row r="179" ht="16" customHeight="1" s="8">
+    <row r="179" ht="16" customHeight="1" s="9">
       <c r="A179" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6038,7 +6031,7 @@
       </c>
       <c r="H179" s="6" t="n"/>
     </row>
-    <row r="180" ht="16" customHeight="1" s="8">
+    <row r="180" ht="16" customHeight="1" s="9">
       <c r="A180" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6070,7 +6063,7 @@
       </c>
       <c r="H180" s="6" t="n"/>
     </row>
-    <row r="181" ht="16" customHeight="1" s="8">
+    <row r="181" ht="16" customHeight="1" s="9">
       <c r="A181" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6102,7 +6095,7 @@
       </c>
       <c r="H181" s="6" t="n"/>
     </row>
-    <row r="182" ht="16" customHeight="1" s="8">
+    <row r="182" ht="16" customHeight="1" s="9">
       <c r="A182" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6134,7 +6127,7 @@
       </c>
       <c r="H182" s="6" t="n"/>
     </row>
-    <row r="183" ht="16" customHeight="1" s="8">
+    <row r="183" ht="16" customHeight="1" s="9">
       <c r="A183" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6166,7 +6159,7 @@
       </c>
       <c r="H183" s="6" t="n"/>
     </row>
-    <row r="184" ht="16" customHeight="1" s="8">
+    <row r="184" ht="16" customHeight="1" s="9">
       <c r="A184" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6198,7 +6191,7 @@
       </c>
       <c r="H184" s="6" t="n"/>
     </row>
-    <row r="185" ht="16" customHeight="1" s="8">
+    <row r="185" ht="16" customHeight="1" s="9">
       <c r="A185" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6230,7 +6223,7 @@
       </c>
       <c r="H185" s="6" t="n"/>
     </row>
-    <row r="186" ht="16" customHeight="1" s="8">
+    <row r="186" ht="16" customHeight="1" s="9">
       <c r="A186" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6262,7 +6255,7 @@
       </c>
       <c r="H186" s="6" t="n"/>
     </row>
-    <row r="187" ht="16" customHeight="1" s="8">
+    <row r="187" ht="16" customHeight="1" s="9">
       <c r="A187" s="3" t="inlineStr">
         <is>
           <t>H</t>
@@ -6294,7 +6287,7 @@
       </c>
       <c r="H187" s="6" t="n"/>
     </row>
-    <row r="188" ht="16" customHeight="1" s="8">
+    <row r="188" ht="16" customHeight="1" s="9">
       <c r="A188" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6326,7 +6319,7 @@
       </c>
       <c r="H188" s="6" t="n"/>
     </row>
-    <row r="189" ht="16" customHeight="1" s="8">
+    <row r="189" ht="16" customHeight="1" s="9">
       <c r="A189" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6358,7 +6351,7 @@
       </c>
       <c r="H189" s="6" t="n"/>
     </row>
-    <row r="190" ht="16" customHeight="1" s="8">
+    <row r="190" ht="16" customHeight="1" s="9">
       <c r="A190" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6390,7 +6383,7 @@
       </c>
       <c r="H190" s="6" t="n"/>
     </row>
-    <row r="191" ht="16" customHeight="1" s="8">
+    <row r="191" ht="16" customHeight="1" s="9">
       <c r="A191" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6422,7 +6415,7 @@
       </c>
       <c r="H191" s="6" t="n"/>
     </row>
-    <row r="192" ht="16" customHeight="1" s="8">
+    <row r="192" ht="16" customHeight="1" s="9">
       <c r="A192" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6454,7 +6447,7 @@
       </c>
       <c r="H192" s="6" t="n"/>
     </row>
-    <row r="193" ht="16" customHeight="1" s="8">
+    <row r="193" ht="16" customHeight="1" s="9">
       <c r="A193" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6486,7 +6479,7 @@
       </c>
       <c r="H193" s="6" t="n"/>
     </row>
-    <row r="194" ht="16" customHeight="1" s="8">
+    <row r="194" ht="16" customHeight="1" s="9">
       <c r="A194" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6518,7 +6511,7 @@
       </c>
       <c r="H194" s="6" t="n"/>
     </row>
-    <row r="195" ht="16" customHeight="1" s="8">
+    <row r="195" ht="16" customHeight="1" s="9">
       <c r="A195" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6550,7 +6543,7 @@
       </c>
       <c r="H195" s="6" t="n"/>
     </row>
-    <row r="196" ht="16" customHeight="1" s="8">
+    <row r="196" ht="16" customHeight="1" s="9">
       <c r="A196" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6582,7 +6575,7 @@
       </c>
       <c r="H196" s="6" t="n"/>
     </row>
-    <row r="197" ht="16" customHeight="1" s="8">
+    <row r="197" ht="16" customHeight="1" s="9">
       <c r="A197" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6614,7 +6607,7 @@
       </c>
       <c r="H197" s="6" t="n"/>
     </row>
-    <row r="198" ht="16" customHeight="1" s="8">
+    <row r="198" ht="16" customHeight="1" s="9">
       <c r="A198" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6646,7 +6639,7 @@
       </c>
       <c r="H198" s="6" t="n"/>
     </row>
-    <row r="199" ht="16" customHeight="1" s="8">
+    <row r="199" ht="16" customHeight="1" s="9">
       <c r="A199" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6678,7 +6671,7 @@
       </c>
       <c r="H199" s="6" t="n"/>
     </row>
-    <row r="200" ht="16" customHeight="1" s="8">
+    <row r="200" ht="16" customHeight="1" s="9">
       <c r="A200" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6710,7 +6703,7 @@
       </c>
       <c r="H200" s="6" t="n"/>
     </row>
-    <row r="201" ht="16" customHeight="1" s="8">
+    <row r="201" ht="16" customHeight="1" s="9">
       <c r="A201" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6742,7 +6735,7 @@
       </c>
       <c r="H201" s="6" t="n"/>
     </row>
-    <row r="202" ht="16" customHeight="1" s="8">
+    <row r="202" ht="16" customHeight="1" s="9">
       <c r="A202" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6774,7 +6767,7 @@
       </c>
       <c r="H202" s="6" t="n"/>
     </row>
-    <row r="203" ht="16" customHeight="1" s="8">
+    <row r="203" ht="16" customHeight="1" s="9">
       <c r="A203" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6806,7 +6799,7 @@
       </c>
       <c r="H203" s="6" t="n"/>
     </row>
-    <row r="204" ht="16" customHeight="1" s="8">
+    <row r="204" ht="16" customHeight="1" s="9">
       <c r="A204" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6838,7 +6831,7 @@
       </c>
       <c r="H204" s="6" t="n"/>
     </row>
-    <row r="205" ht="16" customHeight="1" s="8">
+    <row r="205" ht="16" customHeight="1" s="9">
       <c r="A205" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6870,7 +6863,7 @@
       </c>
       <c r="H205" s="6" t="n"/>
     </row>
-    <row r="206" ht="16" customHeight="1" s="8">
+    <row r="206" ht="16" customHeight="1" s="9">
       <c r="A206" s="3" t="inlineStr">
         <is>
           <t>I</t>
@@ -6902,7 +6895,7 @@
       </c>
       <c r="H206" s="6" t="n"/>
     </row>
-    <row r="207" ht="16" customHeight="1" s="8">
+    <row r="207" ht="16" customHeight="1" s="9">
       <c r="A207" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -6934,7 +6927,7 @@
       </c>
       <c r="H207" s="6" t="n"/>
     </row>
-    <row r="208" ht="16" customHeight="1" s="8">
+    <row r="208" ht="16" customHeight="1" s="9">
       <c r="A208" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -6966,7 +6959,7 @@
       </c>
       <c r="H208" s="6" t="n"/>
     </row>
-    <row r="209" ht="16" customHeight="1" s="8">
+    <row r="209" ht="16" customHeight="1" s="9">
       <c r="A209" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -6998,7 +6991,7 @@
       </c>
       <c r="H209" s="6" t="n"/>
     </row>
-    <row r="210" ht="16" customHeight="1" s="8">
+    <row r="210" ht="16" customHeight="1" s="9">
       <c r="A210" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7030,7 +7023,7 @@
       </c>
       <c r="H210" s="6" t="n"/>
     </row>
-    <row r="211" ht="16" customHeight="1" s="8">
+    <row r="211" ht="16" customHeight="1" s="9">
       <c r="A211" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7062,7 +7055,7 @@
       </c>
       <c r="H211" s="6" t="n"/>
     </row>
-    <row r="212" ht="16" customHeight="1" s="8">
+    <row r="212" ht="16" customHeight="1" s="9">
       <c r="A212" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7092,7 +7085,7 @@
       </c>
       <c r="H212" s="6" t="n"/>
     </row>
-    <row r="213" ht="16" customHeight="1" s="8">
+    <row r="213" ht="16" customHeight="1" s="9">
       <c r="A213" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7124,7 +7117,7 @@
       </c>
       <c r="H213" s="6" t="n"/>
     </row>
-    <row r="214" ht="16" customHeight="1" s="8">
+    <row r="214" ht="16" customHeight="1" s="9">
       <c r="A214" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7156,7 +7149,7 @@
       </c>
       <c r="H214" s="6" t="n"/>
     </row>
-    <row r="215" ht="16" customHeight="1" s="8">
+    <row r="215" ht="16" customHeight="1" s="9">
       <c r="A215" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7188,7 +7181,7 @@
       </c>
       <c r="H215" s="6" t="n"/>
     </row>
-    <row r="216" ht="16" customHeight="1" s="8">
+    <row r="216" ht="16" customHeight="1" s="9">
       <c r="A216" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7220,7 +7213,7 @@
       </c>
       <c r="H216" s="6" t="n"/>
     </row>
-    <row r="217" ht="16" customHeight="1" s="8">
+    <row r="217" ht="16" customHeight="1" s="9">
       <c r="A217" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7252,7 +7245,7 @@
       </c>
       <c r="H217" s="6" t="n"/>
     </row>
-    <row r="218" ht="16" customHeight="1" s="8">
+    <row r="218" ht="16" customHeight="1" s="9">
       <c r="A218" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7278,7 +7271,7 @@
       <c r="G218" s="5" t="n"/>
       <c r="H218" s="6" t="n"/>
     </row>
-    <row r="219" ht="16" customHeight="1" s="8">
+    <row r="219" ht="16" customHeight="1" s="9">
       <c r="A219" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7310,7 +7303,7 @@
       </c>
       <c r="H219" s="6" t="n"/>
     </row>
-    <row r="220" ht="16" customHeight="1" s="8">
+    <row r="220" ht="16" customHeight="1" s="9">
       <c r="A220" s="3" t="inlineStr">
         <is>
           <t>J</t>
@@ -7342,7 +7335,7 @@
       </c>
       <c r="H220" s="6" t="n"/>
     </row>
-    <row r="221" ht="16" customHeight="1" s="8">
+    <row r="221" ht="16" customHeight="1" s="9">
       <c r="A221" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7374,7 +7367,7 @@
       </c>
       <c r="H221" s="6" t="n"/>
     </row>
-    <row r="222" ht="16" customHeight="1" s="8">
+    <row r="222" ht="16" customHeight="1" s="9">
       <c r="A222" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7406,7 +7399,7 @@
       </c>
       <c r="H222" s="6" t="n"/>
     </row>
-    <row r="223" ht="16" customHeight="1" s="8">
+    <row r="223" ht="16" customHeight="1" s="9">
       <c r="A223" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7438,7 +7431,7 @@
       </c>
       <c r="H223" s="6" t="n"/>
     </row>
-    <row r="224" ht="16" customHeight="1" s="8">
+    <row r="224" ht="16" customHeight="1" s="9">
       <c r="A224" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7470,7 +7463,7 @@
       </c>
       <c r="H224" s="6" t="n"/>
     </row>
-    <row r="225" ht="16" customHeight="1" s="8">
+    <row r="225" ht="16" customHeight="1" s="9">
       <c r="A225" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7496,7 +7489,7 @@
       <c r="G225" s="5" t="n"/>
       <c r="H225" s="6" t="n"/>
     </row>
-    <row r="226" ht="16" customHeight="1" s="8">
+    <row r="226" ht="16" customHeight="1" s="9">
       <c r="A226" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7528,7 +7521,7 @@
       </c>
       <c r="H226" s="6" t="n"/>
     </row>
-    <row r="227" ht="16" customHeight="1" s="8">
+    <row r="227" ht="16" customHeight="1" s="9">
       <c r="A227" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7560,7 +7553,7 @@
       </c>
       <c r="H227" s="6" t="n"/>
     </row>
-    <row r="228" ht="16" customHeight="1" s="8">
+    <row r="228" ht="16" customHeight="1" s="9">
       <c r="A228" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7592,7 +7585,7 @@
       </c>
       <c r="H228" s="6" t="n"/>
     </row>
-    <row r="229" ht="16" customHeight="1" s="8">
+    <row r="229" ht="16" customHeight="1" s="9">
       <c r="A229" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7624,7 +7617,7 @@
       </c>
       <c r="H229" s="6" t="n"/>
     </row>
-    <row r="230" ht="16" customHeight="1" s="8">
+    <row r="230" ht="16" customHeight="1" s="9">
       <c r="A230" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7656,7 +7649,7 @@
       </c>
       <c r="H230" s="6" t="n"/>
     </row>
-    <row r="231" ht="16" customHeight="1" s="8">
+    <row r="231" ht="16" customHeight="1" s="9">
       <c r="A231" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7688,7 +7681,7 @@
       </c>
       <c r="H231" s="6" t="n"/>
     </row>
-    <row r="232" ht="16" customHeight="1" s="8">
+    <row r="232" ht="16" customHeight="1" s="9">
       <c r="A232" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7720,7 +7713,7 @@
       </c>
       <c r="H232" s="6" t="n"/>
     </row>
-    <row r="233" ht="16" customHeight="1" s="8">
+    <row r="233" ht="16" customHeight="1" s="9">
       <c r="A233" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7752,7 +7745,7 @@
       </c>
       <c r="H233" s="6" t="n"/>
     </row>
-    <row r="234" ht="16" customHeight="1" s="8">
+    <row r="234" ht="16" customHeight="1" s="9">
       <c r="A234" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7784,7 +7777,7 @@
       </c>
       <c r="H234" s="6" t="n"/>
     </row>
-    <row r="235" ht="16" customHeight="1" s="8">
+    <row r="235" ht="16" customHeight="1" s="9">
       <c r="A235" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7816,7 +7809,7 @@
       </c>
       <c r="H235" s="6" t="n"/>
     </row>
-    <row r="236" ht="16" customHeight="1" s="8">
+    <row r="236" ht="16" customHeight="1" s="9">
       <c r="A236" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7842,7 +7835,7 @@
       <c r="G236" s="5" t="n"/>
       <c r="H236" s="6" t="n"/>
     </row>
-    <row r="237" ht="16" customHeight="1" s="8">
+    <row r="237" ht="16" customHeight="1" s="9">
       <c r="A237" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7874,7 +7867,7 @@
       </c>
       <c r="H237" s="6" t="n"/>
     </row>
-    <row r="238" ht="16" customHeight="1" s="8">
+    <row r="238" ht="16" customHeight="1" s="9">
       <c r="A238" s="3" t="inlineStr">
         <is>
           <t>K</t>
@@ -7900,7 +7893,7 @@
       <c r="G238" s="5" t="n"/>
       <c r="H238" s="6" t="n"/>
     </row>
-    <row r="239" ht="16" customHeight="1" s="8">
+    <row r="239" ht="16" customHeight="1" s="9">
       <c r="A239" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -7932,7 +7925,7 @@
       </c>
       <c r="H239" s="6" t="n"/>
     </row>
-    <row r="240" ht="16" customHeight="1" s="8">
+    <row r="240" ht="16" customHeight="1" s="9">
       <c r="A240" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -7964,7 +7957,7 @@
       </c>
       <c r="H240" s="6" t="n"/>
     </row>
-    <row r="241" ht="16" customHeight="1" s="8">
+    <row r="241" ht="16" customHeight="1" s="9">
       <c r="A241" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -7996,7 +7989,7 @@
       </c>
       <c r="H241" s="6" t="n"/>
     </row>
-    <row r="242" ht="16" customHeight="1" s="8">
+    <row r="242" ht="16" customHeight="1" s="9">
       <c r="A242" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8028,7 +8021,7 @@
       </c>
       <c r="H242" s="6" t="n"/>
     </row>
-    <row r="243" ht="16" customHeight="1" s="8">
+    <row r="243" ht="16" customHeight="1" s="9">
       <c r="A243" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8060,7 +8053,7 @@
       </c>
       <c r="H243" s="6" t="n"/>
     </row>
-    <row r="244" ht="16" customHeight="1" s="8">
+    <row r="244" ht="16" customHeight="1" s="9">
       <c r="A244" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8092,7 +8085,7 @@
       </c>
       <c r="H244" s="6" t="n"/>
     </row>
-    <row r="245" ht="16" customHeight="1" s="8">
+    <row r="245" ht="16" customHeight="1" s="9">
       <c r="A245" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8124,7 +8117,7 @@
       </c>
       <c r="H245" s="6" t="n"/>
     </row>
-    <row r="246" ht="16" customHeight="1" s="8">
+    <row r="246" ht="16" customHeight="1" s="9">
       <c r="A246" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8156,7 +8149,7 @@
       </c>
       <c r="H246" s="6" t="n"/>
     </row>
-    <row r="247" ht="16" customHeight="1" s="8">
+    <row r="247" ht="16" customHeight="1" s="9">
       <c r="A247" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8182,7 +8175,7 @@
       <c r="G247" s="5" t="n"/>
       <c r="H247" s="6" t="n"/>
     </row>
-    <row r="248" ht="16" customHeight="1" s="8">
+    <row r="248" ht="16" customHeight="1" s="9">
       <c r="A248" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8214,7 +8207,7 @@
       </c>
       <c r="H248" s="6" t="n"/>
     </row>
-    <row r="249" ht="16" customHeight="1" s="8">
+    <row r="249" ht="16" customHeight="1" s="9">
       <c r="A249" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8246,7 +8239,7 @@
       </c>
       <c r="H249" s="6" t="n"/>
     </row>
-    <row r="250" ht="16" customHeight="1" s="8">
+    <row r="250" ht="16" customHeight="1" s="9">
       <c r="A250" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8278,7 +8271,7 @@
       </c>
       <c r="H250" s="6" t="n"/>
     </row>
-    <row r="251" ht="16" customHeight="1" s="8">
+    <row r="251" ht="16" customHeight="1" s="9">
       <c r="A251" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8310,7 +8303,7 @@
       </c>
       <c r="H251" s="6" t="n"/>
     </row>
-    <row r="252" ht="16" customHeight="1" s="8">
+    <row r="252" ht="16" customHeight="1" s="9">
       <c r="A252" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8342,7 +8335,7 @@
       </c>
       <c r="H252" s="6" t="n"/>
     </row>
-    <row r="253" ht="16" customHeight="1" s="8">
+    <row r="253" ht="16" customHeight="1" s="9">
       <c r="A253" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8374,7 +8367,7 @@
       </c>
       <c r="H253" s="6" t="n"/>
     </row>
-    <row r="254" ht="16" customHeight="1" s="8">
+    <row r="254" ht="16" customHeight="1" s="9">
       <c r="A254" s="3" t="inlineStr">
         <is>
           <t>L</t>
@@ -8400,7 +8393,7 @@
       <c r="G254" s="5" t="n"/>
       <c r="H254" s="6" t="n"/>
     </row>
-    <row r="255" ht="16" customHeight="1" s="8">
+    <row r="255" ht="16" customHeight="1" s="9">
       <c r="A255" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8432,7 +8425,7 @@
       </c>
       <c r="H255" s="6" t="n"/>
     </row>
-    <row r="256" ht="16" customHeight="1" s="8">
+    <row r="256" ht="16" customHeight="1" s="9">
       <c r="A256" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8464,7 +8457,7 @@
       </c>
       <c r="H256" s="6" t="n"/>
     </row>
-    <row r="257" ht="16" customHeight="1" s="8">
+    <row r="257" ht="16" customHeight="1" s="9">
       <c r="A257" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8496,7 +8489,7 @@
       </c>
       <c r="H257" s="6" t="n"/>
     </row>
-    <row r="258" ht="16" customHeight="1" s="8">
+    <row r="258" ht="16" customHeight="1" s="9">
       <c r="A258" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8528,7 +8521,7 @@
       </c>
       <c r="H258" s="6" t="n"/>
     </row>
-    <row r="259" ht="16" customHeight="1" s="8">
+    <row r="259" ht="16" customHeight="1" s="9">
       <c r="A259" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8560,7 +8553,7 @@
       </c>
       <c r="H259" s="6" t="n"/>
     </row>
-    <row r="260" ht="16" customHeight="1" s="8">
+    <row r="260" ht="16" customHeight="1" s="9">
       <c r="A260" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8592,7 +8585,7 @@
       </c>
       <c r="H260" s="6" t="n"/>
     </row>
-    <row r="261" ht="16" customHeight="1" s="8">
+    <row r="261" ht="16" customHeight="1" s="9">
       <c r="A261" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8624,7 +8617,7 @@
       </c>
       <c r="H261" s="6" t="n"/>
     </row>
-    <row r="262" ht="16" customHeight="1" s="8">
+    <row r="262" ht="16" customHeight="1" s="9">
       <c r="A262" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8656,7 +8649,7 @@
       </c>
       <c r="H262" s="6" t="n"/>
     </row>
-    <row r="263" ht="16" customHeight="1" s="8">
+    <row r="263" ht="16" customHeight="1" s="9">
       <c r="A263" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8688,7 +8681,7 @@
       </c>
       <c r="H263" s="6" t="n"/>
     </row>
-    <row r="264" ht="16" customHeight="1" s="8">
+    <row r="264" ht="16" customHeight="1" s="9">
       <c r="A264" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8720,7 +8713,7 @@
       </c>
       <c r="H264" s="6" t="n"/>
     </row>
-    <row r="265" ht="16" customHeight="1" s="8">
+    <row r="265" ht="16" customHeight="1" s="9">
       <c r="A265" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8752,7 +8745,7 @@
       </c>
       <c r="H265" s="6" t="n"/>
     </row>
-    <row r="266" ht="16" customHeight="1" s="8">
+    <row r="266" ht="16" customHeight="1" s="9">
       <c r="A266" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8782,7 +8775,7 @@
       </c>
       <c r="H266" s="6" t="n"/>
     </row>
-    <row r="267" ht="16" customHeight="1" s="8">
+    <row r="267" ht="16" customHeight="1" s="9">
       <c r="A267" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8814,7 +8807,7 @@
       </c>
       <c r="H267" s="6" t="n"/>
     </row>
-    <row r="268" ht="16" customHeight="1" s="8">
+    <row r="268" ht="16" customHeight="1" s="9">
       <c r="A268" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8846,7 +8839,7 @@
       </c>
       <c r="H268" s="6" t="n"/>
     </row>
-    <row r="269" ht="16" customHeight="1" s="8">
+    <row r="269" ht="16" customHeight="1" s="9">
       <c r="A269" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8878,7 +8871,7 @@
       </c>
       <c r="H269" s="6" t="n"/>
     </row>
-    <row r="270" ht="16" customHeight="1" s="8">
+    <row r="270" ht="16" customHeight="1" s="9">
       <c r="A270" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8910,7 +8903,7 @@
       </c>
       <c r="H270" s="6" t="n"/>
     </row>
-    <row r="271" ht="16" customHeight="1" s="8">
+    <row r="271" ht="16" customHeight="1" s="9">
       <c r="A271" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8942,7 +8935,7 @@
       </c>
       <c r="H271" s="6" t="n"/>
     </row>
-    <row r="272" ht="16" customHeight="1" s="8">
+    <row r="272" ht="16" customHeight="1" s="9">
       <c r="A272" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -8974,7 +8967,7 @@
       </c>
       <c r="H272" s="6" t="n"/>
     </row>
-    <row r="273" ht="16" customHeight="1" s="8">
+    <row r="273" ht="16" customHeight="1" s="9">
       <c r="A273" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -9006,7 +8999,7 @@
       </c>
       <c r="H273" s="6" t="n"/>
     </row>
-    <row r="274" ht="16" customHeight="1" s="8">
+    <row r="274" ht="16" customHeight="1" s="9">
       <c r="A274" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -9038,7 +9031,7 @@
       </c>
       <c r="H274" s="6" t="n"/>
     </row>
-    <row r="275" ht="16" customHeight="1" s="8">
+    <row r="275" ht="16" customHeight="1" s="9">
       <c r="A275" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -9070,7 +9063,7 @@
       </c>
       <c r="H275" s="6" t="n"/>
     </row>
-    <row r="276" ht="16" customHeight="1" s="8">
+    <row r="276" ht="16" customHeight="1" s="9">
       <c r="A276" s="3" t="inlineStr">
         <is>
           <t>M</t>
@@ -9102,7 +9095,7 @@
       </c>
       <c r="H276" s="6" t="n"/>
     </row>
-    <row r="277" ht="16" customHeight="1" s="8">
+    <row r="277" ht="16" customHeight="1" s="9">
       <c r="A277" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9134,7 +9127,7 @@
       </c>
       <c r="H277" s="6" t="n"/>
     </row>
-    <row r="278" ht="16" customHeight="1" s="8">
+    <row r="278" ht="16" customHeight="1" s="9">
       <c r="A278" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9166,7 +9159,7 @@
       </c>
       <c r="H278" s="6" t="n"/>
     </row>
-    <row r="279" ht="16" customHeight="1" s="8">
+    <row r="279" ht="16" customHeight="1" s="9">
       <c r="A279" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9198,7 +9191,7 @@
       </c>
       <c r="H279" s="6" t="n"/>
     </row>
-    <row r="280" ht="16" customHeight="1" s="8">
+    <row r="280" ht="16" customHeight="1" s="9">
       <c r="A280" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9230,7 +9223,7 @@
       </c>
       <c r="H280" s="6" t="n"/>
     </row>
-    <row r="281" ht="16" customHeight="1" s="8">
+    <row r="281" ht="16" customHeight="1" s="9">
       <c r="A281" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9256,7 +9249,7 @@
       <c r="G281" s="5" t="n"/>
       <c r="H281" s="6" t="n"/>
     </row>
-    <row r="282" ht="16" customHeight="1" s="8">
+    <row r="282" ht="16" customHeight="1" s="9">
       <c r="A282" s="3" t="inlineStr">
         <is>
           <t>N</t>
@@ -9288,7 +9281,7 @@
       </c>
       <c r="H282" s="6" t="n"/>
     </row>
-    <row r="283" ht="16" customHeight="1" s="8">
+    <row r="283" ht="16" customHeight="1" s="9">
       <c r="A283" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9320,7 +9313,7 @@
       </c>
       <c r="H283" s="6" t="n"/>
     </row>
-    <row r="284" ht="16" customHeight="1" s="8">
+    <row r="284" ht="16" customHeight="1" s="9">
       <c r="A284" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9352,7 +9345,7 @@
       </c>
       <c r="H284" s="6" t="n"/>
     </row>
-    <row r="285" ht="16" customHeight="1" s="8">
+    <row r="285" ht="16" customHeight="1" s="9">
       <c r="A285" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9384,7 +9377,7 @@
       </c>
       <c r="H285" s="6" t="n"/>
     </row>
-    <row r="286" ht="16" customHeight="1" s="8">
+    <row r="286" ht="16" customHeight="1" s="9">
       <c r="A286" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9416,7 +9409,7 @@
       </c>
       <c r="H286" s="6" t="n"/>
     </row>
-    <row r="287" ht="16" customHeight="1" s="8">
+    <row r="287" ht="16" customHeight="1" s="9">
       <c r="A287" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9448,7 +9441,7 @@
       </c>
       <c r="H287" s="6" t="n"/>
     </row>
-    <row r="288" ht="16" customHeight="1" s="8">
+    <row r="288" ht="16" customHeight="1" s="9">
       <c r="A288" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9480,7 +9473,7 @@
       </c>
       <c r="H288" s="6" t="n"/>
     </row>
-    <row r="289" ht="16" customHeight="1" s="8">
+    <row r="289" ht="16" customHeight="1" s="9">
       <c r="A289" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9512,7 +9505,7 @@
       </c>
       <c r="H289" s="6" t="n"/>
     </row>
-    <row r="290" ht="16" customHeight="1" s="8">
+    <row r="290" ht="16" customHeight="1" s="9">
       <c r="A290" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9544,7 +9537,7 @@
       </c>
       <c r="H290" s="6" t="n"/>
     </row>
-    <row r="291" ht="16" customHeight="1" s="8">
+    <row r="291" ht="16" customHeight="1" s="9">
       <c r="A291" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9576,7 +9569,7 @@
       </c>
       <c r="H291" s="6" t="n"/>
     </row>
-    <row r="292" ht="16" customHeight="1" s="8">
+    <row r="292" ht="16" customHeight="1" s="9">
       <c r="A292" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9608,7 +9601,7 @@
       </c>
       <c r="H292" s="6" t="n"/>
     </row>
-    <row r="293" ht="16" customHeight="1" s="8">
+    <row r="293" ht="16" customHeight="1" s="9">
       <c r="A293" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9640,7 +9633,7 @@
       </c>
       <c r="H293" s="6" t="n"/>
     </row>
-    <row r="294" ht="16" customHeight="1" s="8">
+    <row r="294" ht="16" customHeight="1" s="9">
       <c r="A294" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9672,7 +9665,7 @@
       </c>
       <c r="H294" s="6" t="n"/>
     </row>
-    <row r="295" ht="16" customHeight="1" s="8">
+    <row r="295" ht="16" customHeight="1" s="9">
       <c r="A295" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9704,7 +9697,7 @@
       </c>
       <c r="H295" s="6" t="n"/>
     </row>
-    <row r="296" ht="16" customHeight="1" s="8">
+    <row r="296" ht="16" customHeight="1" s="9">
       <c r="A296" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9736,7 +9729,7 @@
       </c>
       <c r="H296" s="6" t="n"/>
     </row>
-    <row r="297" ht="16" customHeight="1" s="8">
+    <row r="297" ht="16" customHeight="1" s="9">
       <c r="A297" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9768,7 +9761,7 @@
       </c>
       <c r="H297" s="6" t="n"/>
     </row>
-    <row r="298" ht="16" customHeight="1" s="8">
+    <row r="298" ht="16" customHeight="1" s="9">
       <c r="A298" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9800,7 +9793,7 @@
       </c>
       <c r="H298" s="6" t="n"/>
     </row>
-    <row r="299" ht="16" customHeight="1" s="8">
+    <row r="299" ht="16" customHeight="1" s="9">
       <c r="A299" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9832,7 +9825,7 @@
       </c>
       <c r="H299" s="6" t="n"/>
     </row>
-    <row r="300" ht="16" customHeight="1" s="8">
+    <row r="300" ht="16" customHeight="1" s="9">
       <c r="A300" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9864,7 +9857,7 @@
       </c>
       <c r="H300" s="6" t="n"/>
     </row>
-    <row r="301" ht="16" customHeight="1" s="8">
+    <row r="301" ht="16" customHeight="1" s="9">
       <c r="A301" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9896,7 +9889,7 @@
       </c>
       <c r="H301" s="6" t="n"/>
     </row>
-    <row r="302" ht="16" customHeight="1" s="8">
+    <row r="302" ht="16" customHeight="1" s="9">
       <c r="A302" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9928,7 +9921,7 @@
       </c>
       <c r="H302" s="6" t="n"/>
     </row>
-    <row r="303" ht="16" customHeight="1" s="8">
+    <row r="303" ht="16" customHeight="1" s="9">
       <c r="A303" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9960,7 +9953,7 @@
       </c>
       <c r="H303" s="6" t="n"/>
     </row>
-    <row r="304" ht="16" customHeight="1" s="8">
+    <row r="304" ht="16" customHeight="1" s="9">
       <c r="A304" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -9992,7 +9985,7 @@
       </c>
       <c r="H304" s="6" t="n"/>
     </row>
-    <row r="305" ht="16" customHeight="1" s="8">
+    <row r="305" ht="16" customHeight="1" s="9">
       <c r="A305" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10024,7 +10017,7 @@
       </c>
       <c r="H305" s="6" t="n"/>
     </row>
-    <row r="306" ht="16" customHeight="1" s="8">
+    <row r="306" ht="16" customHeight="1" s="9">
       <c r="A306" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10056,7 +10049,7 @@
       </c>
       <c r="H306" s="6" t="n"/>
     </row>
-    <row r="307" ht="16" customHeight="1" s="8">
+    <row r="307" ht="16" customHeight="1" s="9">
       <c r="A307" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10088,7 +10081,7 @@
       </c>
       <c r="H307" s="6" t="n"/>
     </row>
-    <row r="308" ht="16" customHeight="1" s="8">
+    <row r="308" ht="16" customHeight="1" s="9">
       <c r="A308" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10120,7 +10113,7 @@
       </c>
       <c r="H308" s="6" t="n"/>
     </row>
-    <row r="309" ht="16" customHeight="1" s="8">
+    <row r="309" ht="16" customHeight="1" s="9">
       <c r="A309" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10152,7 +10145,7 @@
       </c>
       <c r="H309" s="6" t="n"/>
     </row>
-    <row r="310" ht="16" customHeight="1" s="8">
+    <row r="310" ht="16" customHeight="1" s="9">
       <c r="A310" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10184,7 +10177,7 @@
       </c>
       <c r="H310" s="6" t="n"/>
     </row>
-    <row r="311" ht="16" customHeight="1" s="8">
+    <row r="311" ht="16" customHeight="1" s="9">
       <c r="A311" s="3" t="inlineStr">
         <is>
           <t>O</t>
@@ -10216,7 +10209,7 @@
       </c>
       <c r="H311" s="6" t="n"/>
     </row>
-    <row r="312" ht="16" customHeight="1" s="8">
+    <row r="312" ht="16" customHeight="1" s="9">
       <c r="A312" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10248,7 +10241,7 @@
       </c>
       <c r="H312" s="6" t="n"/>
     </row>
-    <row r="313" ht="16" customHeight="1" s="8">
+    <row r="313" ht="16" customHeight="1" s="9">
       <c r="A313" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10280,7 +10273,7 @@
       </c>
       <c r="H313" s="6" t="n"/>
     </row>
-    <row r="314" ht="16" customHeight="1" s="8">
+    <row r="314" ht="16" customHeight="1" s="9">
       <c r="A314" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10312,7 +10305,7 @@
       </c>
       <c r="H314" s="6" t="n"/>
     </row>
-    <row r="315" ht="16" customHeight="1" s="8">
+    <row r="315" ht="16" customHeight="1" s="9">
       <c r="A315" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10344,7 +10337,7 @@
       </c>
       <c r="H315" s="6" t="n"/>
     </row>
-    <row r="316" ht="16" customHeight="1" s="8">
+    <row r="316" ht="16" customHeight="1" s="9">
       <c r="A316" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10376,7 +10369,7 @@
       </c>
       <c r="H316" s="6" t="n"/>
     </row>
-    <row r="317" ht="16" customHeight="1" s="8">
+    <row r="317" ht="16" customHeight="1" s="9">
       <c r="A317" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10408,7 +10401,7 @@
       </c>
       <c r="H317" s="6" t="n"/>
     </row>
-    <row r="318" ht="16" customHeight="1" s="8">
+    <row r="318" ht="16" customHeight="1" s="9">
       <c r="A318" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10440,7 +10433,7 @@
       </c>
       <c r="H318" s="6" t="n"/>
     </row>
-    <row r="319" ht="16" customHeight="1" s="8">
+    <row r="319" ht="16" customHeight="1" s="9">
       <c r="A319" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10472,7 +10465,7 @@
       </c>
       <c r="H319" s="6" t="n"/>
     </row>
-    <row r="320" ht="16" customHeight="1" s="8">
+    <row r="320" ht="16" customHeight="1" s="9">
       <c r="A320" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10504,7 +10497,7 @@
       </c>
       <c r="H320" s="6" t="n"/>
     </row>
-    <row r="321" ht="16" customHeight="1" s="8">
+    <row r="321" ht="16" customHeight="1" s="9">
       <c r="A321" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10536,7 +10529,7 @@
       </c>
       <c r="H321" s="6" t="n"/>
     </row>
-    <row r="322" ht="16" customHeight="1" s="8">
+    <row r="322" ht="16" customHeight="1" s="9">
       <c r="A322" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10568,7 +10561,7 @@
       </c>
       <c r="H322" s="6" t="n"/>
     </row>
-    <row r="323" ht="16" customHeight="1" s="8">
+    <row r="323" ht="16" customHeight="1" s="9">
       <c r="A323" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10600,7 +10593,7 @@
       </c>
       <c r="H323" s="6" t="n"/>
     </row>
-    <row r="324" ht="16" customHeight="1" s="8">
+    <row r="324" ht="16" customHeight="1" s="9">
       <c r="A324" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10626,7 +10619,7 @@
       <c r="G324" s="5" t="n"/>
       <c r="H324" s="6" t="n"/>
     </row>
-    <row r="325" ht="16" customHeight="1" s="8">
+    <row r="325" ht="16" customHeight="1" s="9">
       <c r="A325" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10658,7 +10651,7 @@
       </c>
       <c r="H325" s="6" t="n"/>
     </row>
-    <row r="326" ht="16" customHeight="1" s="8">
+    <row r="326" ht="16" customHeight="1" s="9">
       <c r="A326" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10690,7 +10683,7 @@
       </c>
       <c r="H326" s="6" t="n"/>
     </row>
-    <row r="327" ht="16" customHeight="1" s="8">
+    <row r="327" ht="16" customHeight="1" s="9">
       <c r="A327" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10722,7 +10715,7 @@
       </c>
       <c r="H327" s="6" t="n"/>
     </row>
-    <row r="328" ht="16" customHeight="1" s="8">
+    <row r="328" ht="16" customHeight="1" s="9">
       <c r="A328" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10754,7 +10747,7 @@
       </c>
       <c r="H328" s="6" t="n"/>
     </row>
-    <row r="329" ht="16" customHeight="1" s="8">
+    <row r="329" ht="16" customHeight="1" s="9">
       <c r="A329" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10780,7 +10773,7 @@
       <c r="G329" s="5" t="n"/>
       <c r="H329" s="6" t="n"/>
     </row>
-    <row r="330" ht="16" customHeight="1" s="8">
+    <row r="330" ht="16" customHeight="1" s="9">
       <c r="A330" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10812,7 +10805,7 @@
       </c>
       <c r="H330" s="6" t="n"/>
     </row>
-    <row r="331" ht="16" customHeight="1" s="8">
+    <row r="331" ht="16" customHeight="1" s="9">
       <c r="A331" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10844,7 +10837,7 @@
       </c>
       <c r="H331" s="6" t="n"/>
     </row>
-    <row r="332" ht="16" customHeight="1" s="8">
+    <row r="332" ht="16" customHeight="1" s="9">
       <c r="A332" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10876,7 +10869,7 @@
       </c>
       <c r="H332" s="6" t="n"/>
     </row>
-    <row r="333" ht="16" customHeight="1" s="8">
+    <row r="333" ht="16" customHeight="1" s="9">
       <c r="A333" s="3" t="inlineStr">
         <is>
           <t>P</t>
@@ -10902,7 +10895,7 @@
       <c r="G333" s="5" t="n"/>
       <c r="H333" s="6" t="n"/>
     </row>
-    <row r="334" ht="16" customHeight="1" s="8">
+    <row r="334" ht="16" customHeight="1" s="9">
       <c r="A334" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -10934,7 +10927,7 @@
       </c>
       <c r="H334" s="6" t="n"/>
     </row>
-    <row r="335" ht="16" customHeight="1" s="8">
+    <row r="335" ht="16" customHeight="1" s="9">
       <c r="A335" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -10966,7 +10959,7 @@
       </c>
       <c r="H335" s="6" t="n"/>
     </row>
-    <row r="336" ht="16" customHeight="1" s="8">
+    <row r="336" ht="16" customHeight="1" s="9">
       <c r="A336" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -10998,7 +10991,7 @@
       </c>
       <c r="H336" s="6" t="n"/>
     </row>
-    <row r="337" ht="16" customHeight="1" s="8">
+    <row r="337" ht="16" customHeight="1" s="9">
       <c r="A337" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11024,7 +11017,7 @@
       <c r="G337" s="5" t="n"/>
       <c r="H337" s="6" t="n"/>
     </row>
-    <row r="338" ht="16" customHeight="1" s="8">
+    <row r="338" ht="16" customHeight="1" s="9">
       <c r="A338" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11056,7 +11049,7 @@
       </c>
       <c r="H338" s="6" t="n"/>
     </row>
-    <row r="339" ht="16" customHeight="1" s="8">
+    <row r="339" ht="16" customHeight="1" s="9">
       <c r="A339" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11088,7 +11081,7 @@
       </c>
       <c r="H339" s="6" t="n"/>
     </row>
-    <row r="340" ht="16" customHeight="1" s="8">
+    <row r="340" ht="16" customHeight="1" s="9">
       <c r="A340" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11120,7 +11113,7 @@
       </c>
       <c r="H340" s="6" t="n"/>
     </row>
-    <row r="341" ht="16" customHeight="1" s="8">
+    <row r="341" ht="16" customHeight="1" s="9">
       <c r="A341" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11152,7 +11145,7 @@
       </c>
       <c r="H341" s="6" t="n"/>
     </row>
-    <row r="342" ht="16" customHeight="1" s="8">
+    <row r="342" ht="16" customHeight="1" s="9">
       <c r="A342" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11184,7 +11177,7 @@
       </c>
       <c r="H342" s="6" t="n"/>
     </row>
-    <row r="343" ht="16" customHeight="1" s="8">
+    <row r="343" ht="16" customHeight="1" s="9">
       <c r="A343" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11210,7 +11203,7 @@
       <c r="G343" s="5" t="n"/>
       <c r="H343" s="6" t="n"/>
     </row>
-    <row r="344" ht="16" customHeight="1" s="8">
+    <row r="344" ht="16" customHeight="1" s="9">
       <c r="A344" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11242,7 +11235,7 @@
       </c>
       <c r="H344" s="6" t="n"/>
     </row>
-    <row r="345" ht="16" customHeight="1" s="8">
+    <row r="345" ht="16" customHeight="1" s="9">
       <c r="A345" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11274,7 +11267,7 @@
       </c>
       <c r="H345" s="6" t="n"/>
     </row>
-    <row r="346" ht="16" customHeight="1" s="8">
+    <row r="346" ht="16" customHeight="1" s="9">
       <c r="A346" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11300,7 +11293,7 @@
       <c r="G346" s="5" t="n"/>
       <c r="H346" s="6" t="n"/>
     </row>
-    <row r="347" ht="16" customHeight="1" s="8">
+    <row r="347" ht="16" customHeight="1" s="9">
       <c r="A347" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11332,7 +11325,7 @@
       </c>
       <c r="H347" s="6" t="n"/>
     </row>
-    <row r="348" ht="16" customHeight="1" s="8">
+    <row r="348" ht="16" customHeight="1" s="9">
       <c r="A348" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11364,7 +11357,7 @@
       </c>
       <c r="H348" s="6" t="n"/>
     </row>
-    <row r="349" ht="16" customHeight="1" s="8">
+    <row r="349" ht="16" customHeight="1" s="9">
       <c r="A349" s="3" t="inlineStr">
         <is>
           <t>Q</t>
@@ -11396,7 +11389,7 @@
       </c>
       <c r="H349" s="6" t="n"/>
     </row>
-    <row r="350" ht="16" customHeight="1" s="8">
+    <row r="350" ht="16" customHeight="1" s="9">
       <c r="A350" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11428,7 +11421,7 @@
       </c>
       <c r="H350" s="6" t="n"/>
     </row>
-    <row r="351" ht="16" customHeight="1" s="8">
+    <row r="351" ht="16" customHeight="1" s="9">
       <c r="A351" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11460,7 +11453,7 @@
       </c>
       <c r="H351" s="6" t="n"/>
     </row>
-    <row r="352" ht="16" customHeight="1" s="8">
+    <row r="352" ht="16" customHeight="1" s="9">
       <c r="A352" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11492,7 +11485,7 @@
       </c>
       <c r="H352" s="6" t="n"/>
     </row>
-    <row r="353" ht="16" customHeight="1" s="8">
+    <row r="353" ht="16" customHeight="1" s="9">
       <c r="A353" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11524,7 +11517,7 @@
       </c>
       <c r="H353" s="6" t="n"/>
     </row>
-    <row r="354" ht="16" customHeight="1" s="8">
+    <row r="354" ht="16" customHeight="1" s="9">
       <c r="A354" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11556,7 +11549,7 @@
       </c>
       <c r="H354" s="6" t="n"/>
     </row>
-    <row r="355" ht="16" customHeight="1" s="8">
+    <row r="355" ht="16" customHeight="1" s="9">
       <c r="A355" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11588,7 +11581,7 @@
       </c>
       <c r="H355" s="6" t="n"/>
     </row>
-    <row r="356" ht="16" customHeight="1" s="8">
+    <row r="356" ht="16" customHeight="1" s="9">
       <c r="A356" s="3" t="inlineStr">
         <is>
           <t>R</t>
@@ -11620,7 +11613,7 @@
       </c>
       <c r="H356" s="6" t="n"/>
     </row>
-    <row r="357" ht="16" customHeight="1" s="8">
+    <row r="357" ht="16" customHeight="1" s="9">
       <c r="A357" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11652,7 +11645,7 @@
       </c>
       <c r="H357" s="6" t="n"/>
     </row>
-    <row r="358" ht="16" customHeight="1" s="8">
+    <row r="358" ht="16" customHeight="1" s="9">
       <c r="A358" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11684,7 +11677,7 @@
       </c>
       <c r="H358" s="6" t="n"/>
     </row>
-    <row r="359" ht="16" customHeight="1" s="8">
+    <row r="359" ht="16" customHeight="1" s="9">
       <c r="A359" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11716,7 +11709,7 @@
       </c>
       <c r="H359" s="6" t="n"/>
     </row>
-    <row r="360" ht="16" customHeight="1" s="8">
+    <row r="360" ht="16" customHeight="1" s="9">
       <c r="A360" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11748,7 +11741,7 @@
       </c>
       <c r="H360" s="6" t="n"/>
     </row>
-    <row r="361" ht="16" customHeight="1" s="8">
+    <row r="361" ht="16" customHeight="1" s="9">
       <c r="A361" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11780,7 +11773,7 @@
       </c>
       <c r="H361" s="6" t="n"/>
     </row>
-    <row r="362" ht="16" customHeight="1" s="8">
+    <row r="362" ht="16" customHeight="1" s="9">
       <c r="A362" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11806,7 +11799,7 @@
       <c r="G362" s="5" t="n"/>
       <c r="H362" s="6" t="n"/>
     </row>
-    <row r="363" ht="16" customHeight="1" s="8">
+    <row r="363" ht="16" customHeight="1" s="9">
       <c r="A363" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11838,7 +11831,7 @@
       </c>
       <c r="H363" s="6" t="n"/>
     </row>
-    <row r="364" ht="16" customHeight="1" s="8">
+    <row r="364" ht="16" customHeight="1" s="9">
       <c r="A364" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11870,7 +11863,7 @@
       </c>
       <c r="H364" s="6" t="n"/>
     </row>
-    <row r="365" ht="16" customHeight="1" s="8">
+    <row r="365" ht="16" customHeight="1" s="9">
       <c r="A365" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11902,7 +11895,7 @@
       </c>
       <c r="H365" s="6" t="n"/>
     </row>
-    <row r="366" ht="16" customHeight="1" s="8">
+    <row r="366" ht="16" customHeight="1" s="9">
       <c r="A366" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11934,7 +11927,7 @@
       </c>
       <c r="H366" s="6" t="n"/>
     </row>
-    <row r="367" ht="16" customHeight="1" s="8">
+    <row r="367" ht="16" customHeight="1" s="9">
       <c r="A367" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11966,7 +11959,7 @@
       </c>
       <c r="H367" s="6" t="n"/>
     </row>
-    <row r="368" ht="16" customHeight="1" s="8">
+    <row r="368" ht="16" customHeight="1" s="9">
       <c r="A368" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -11998,7 +11991,7 @@
       </c>
       <c r="H368" s="6" t="n"/>
     </row>
-    <row r="369" ht="16" customHeight="1" s="8">
+    <row r="369" ht="16" customHeight="1" s="9">
       <c r="A369" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -12030,7 +12023,7 @@
       </c>
       <c r="H369" s="6" t="n"/>
     </row>
-    <row r="370" ht="16" customHeight="1" s="8">
+    <row r="370" ht="16" customHeight="1" s="9">
       <c r="A370" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -12056,7 +12049,7 @@
       <c r="G370" s="5" t="n"/>
       <c r="H370" s="6" t="n"/>
     </row>
-    <row r="371" ht="16" customHeight="1" s="8">
+    <row r="371" ht="16" customHeight="1" s="9">
       <c r="A371" s="3" t="inlineStr">
         <is>
           <t>S</t>
@@ -12088,7 +12081,7 @@
       </c>
       <c r="H371" s="6" t="n"/>
     </row>
-    <row r="372" ht="16" customHeight="1" s="8">
+    <row r="372" ht="16" customHeight="1" s="9">
       <c r="A372" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12120,7 +12113,7 @@
       </c>
       <c r="H372" s="6" t="n"/>
     </row>
-    <row r="373" ht="16" customHeight="1" s="8">
+    <row r="373" ht="16" customHeight="1" s="9">
       <c r="A373" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12146,7 +12139,7 @@
       <c r="G373" s="5" t="n"/>
       <c r="H373" s="6" t="n"/>
     </row>
-    <row r="374" ht="16" customHeight="1" s="8">
+    <row r="374" ht="16" customHeight="1" s="9">
       <c r="A374" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12178,7 +12171,7 @@
       </c>
       <c r="H374" s="6" t="n"/>
     </row>
-    <row r="375" ht="16" customHeight="1" s="8">
+    <row r="375" ht="16" customHeight="1" s="9">
       <c r="A375" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12210,7 +12203,7 @@
       </c>
       <c r="H375" s="6" t="n"/>
     </row>
-    <row r="376" ht="16" customHeight="1" s="8">
+    <row r="376" ht="16" customHeight="1" s="9">
       <c r="A376" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12242,7 +12235,7 @@
       </c>
       <c r="H376" s="6" t="n"/>
     </row>
-    <row r="377" ht="16" customHeight="1" s="8">
+    <row r="377" ht="16" customHeight="1" s="9">
       <c r="A377" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12274,7 +12267,7 @@
       </c>
       <c r="H377" s="6" t="n"/>
     </row>
-    <row r="378" ht="16" customHeight="1" s="8">
+    <row r="378" ht="16" customHeight="1" s="9">
       <c r="A378" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12306,7 +12299,7 @@
       </c>
       <c r="H378" s="6" t="n"/>
     </row>
-    <row r="379" ht="16" customHeight="1" s="8">
+    <row r="379" ht="16" customHeight="1" s="9">
       <c r="A379" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12338,7 +12331,7 @@
       </c>
       <c r="H379" s="6" t="n"/>
     </row>
-    <row r="380" ht="16" customHeight="1" s="8">
+    <row r="380" ht="16" customHeight="1" s="9">
       <c r="A380" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12370,7 +12363,7 @@
       </c>
       <c r="H380" s="6" t="n"/>
     </row>
-    <row r="381" ht="16" customHeight="1" s="8">
+    <row r="381" ht="16" customHeight="1" s="9">
       <c r="A381" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12402,7 +12395,7 @@
       </c>
       <c r="H381" s="6" t="n"/>
     </row>
-    <row r="382" ht="16" customHeight="1" s="8">
+    <row r="382" ht="16" customHeight="1" s="9">
       <c r="A382" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12434,7 +12427,7 @@
       </c>
       <c r="H382" s="6" t="n"/>
     </row>
-    <row r="383" ht="16" customHeight="1" s="8">
+    <row r="383" ht="16" customHeight="1" s="9">
       <c r="A383" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12460,7 +12453,7 @@
       <c r="G383" s="5" t="n"/>
       <c r="H383" s="6" t="n"/>
     </row>
-    <row r="384" ht="16" customHeight="1" s="8">
+    <row r="384" ht="16" customHeight="1" s="9">
       <c r="A384" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12492,7 +12485,7 @@
       </c>
       <c r="H384" s="6" t="n"/>
     </row>
-    <row r="385" ht="16" customHeight="1" s="8">
+    <row r="385" ht="16" customHeight="1" s="9">
       <c r="A385" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12524,7 +12517,7 @@
       </c>
       <c r="H385" s="6" t="n"/>
     </row>
-    <row r="386" ht="16" customHeight="1" s="8">
+    <row r="386" ht="16" customHeight="1" s="9">
       <c r="A386" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12556,7 +12549,7 @@
       </c>
       <c r="H386" s="6" t="n"/>
     </row>
-    <row r="387" ht="16" customHeight="1" s="8">
+    <row r="387" ht="16" customHeight="1" s="9">
       <c r="A387" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12588,7 +12581,7 @@
       </c>
       <c r="H387" s="6" t="n"/>
     </row>
-    <row r="388" ht="16" customHeight="1" s="8">
+    <row r="388" ht="16" customHeight="1" s="9">
       <c r="A388" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12620,7 +12613,7 @@
       </c>
       <c r="H388" s="6" t="n"/>
     </row>
-    <row r="389" ht="16" customHeight="1" s="8">
+    <row r="389" ht="16" customHeight="1" s="9">
       <c r="A389" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12652,7 +12645,7 @@
       </c>
       <c r="H389" s="6" t="n"/>
     </row>
-    <row r="390" ht="16" customHeight="1" s="8">
+    <row r="390" ht="16" customHeight="1" s="9">
       <c r="A390" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12684,7 +12677,7 @@
       </c>
       <c r="H390" s="6" t="n"/>
     </row>
-    <row r="391" ht="16" customHeight="1" s="8">
+    <row r="391" ht="16" customHeight="1" s="9">
       <c r="A391" s="3" t="inlineStr">
         <is>
           <t>T</t>
@@ -12716,7 +12709,7 @@
       </c>
       <c r="H391" s="6" t="n"/>
     </row>
-    <row r="392" ht="16" customHeight="1" s="8">
+    <row r="392" ht="16" customHeight="1" s="9">
       <c r="A392" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12748,7 +12741,7 @@
       </c>
       <c r="H392" s="6" t="n"/>
     </row>
-    <row r="393" ht="16" customHeight="1" s="8">
+    <row r="393" ht="16" customHeight="1" s="9">
       <c r="A393" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12780,7 +12773,7 @@
       </c>
       <c r="H393" s="6" t="n"/>
     </row>
-    <row r="394" ht="16" customHeight="1" s="8">
+    <row r="394" ht="16" customHeight="1" s="9">
       <c r="A394" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12812,7 +12805,7 @@
       </c>
       <c r="H394" s="6" t="n"/>
     </row>
-    <row r="395" ht="16" customHeight="1" s="8">
+    <row r="395" ht="16" customHeight="1" s="9">
       <c r="A395" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12844,7 +12837,7 @@
       </c>
       <c r="H395" s="6" t="n"/>
     </row>
-    <row r="396" ht="16" customHeight="1" s="8">
+    <row r="396" ht="16" customHeight="1" s="9">
       <c r="A396" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12876,7 +12869,7 @@
       </c>
       <c r="H396" s="6" t="n"/>
     </row>
-    <row r="397" ht="16" customHeight="1" s="8">
+    <row r="397" ht="16" customHeight="1" s="9">
       <c r="A397" s="3" t="inlineStr">
         <is>
           <t>U</t>
@@ -12908,7 +12901,7 @@
       </c>
       <c r="H397" s="6" t="n"/>
     </row>
-    <row r="398" ht="16" customHeight="1" s="8">
+    <row r="398" ht="16" customHeight="1" s="9">
       <c r="A398" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -12940,7 +12933,7 @@
       </c>
       <c r="H398" s="6" t="n"/>
     </row>
-    <row r="399" ht="16" customHeight="1" s="8">
+    <row r="399" ht="16" customHeight="1" s="9">
       <c r="A399" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -12972,7 +12965,7 @@
       </c>
       <c r="H399" s="6" t="n"/>
     </row>
-    <row r="400" ht="16" customHeight="1" s="8">
+    <row r="400" ht="16" customHeight="1" s="9">
       <c r="A400" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13004,7 +12997,7 @@
       </c>
       <c r="H400" s="6" t="n"/>
     </row>
-    <row r="401" ht="16" customHeight="1" s="8">
+    <row r="401" ht="16" customHeight="1" s="9">
       <c r="A401" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13036,7 +13029,7 @@
       </c>
       <c r="H401" s="6" t="n"/>
     </row>
-    <row r="402" ht="16" customHeight="1" s="8">
+    <row r="402" ht="16" customHeight="1" s="9">
       <c r="A402" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13068,7 +13061,7 @@
       </c>
       <c r="H402" s="6" t="n"/>
     </row>
-    <row r="403" ht="16" customHeight="1" s="8">
+    <row r="403" ht="16" customHeight="1" s="9">
       <c r="A403" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13100,7 +13093,7 @@
       </c>
       <c r="H403" s="6" t="n"/>
     </row>
-    <row r="404" ht="16" customHeight="1" s="8">
+    <row r="404" ht="16" customHeight="1" s="9">
       <c r="A404" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13132,7 +13125,7 @@
       </c>
       <c r="H404" s="6" t="n"/>
     </row>
-    <row r="405" ht="16" customHeight="1" s="8">
+    <row r="405" ht="16" customHeight="1" s="9">
       <c r="A405" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13164,7 +13157,7 @@
       </c>
       <c r="H405" s="6" t="n"/>
     </row>
-    <row r="406" ht="16" customHeight="1" s="8">
+    <row r="406" ht="16" customHeight="1" s="9">
       <c r="A406" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13196,7 +13189,7 @@
       </c>
       <c r="H406" s="6" t="n"/>
     </row>
-    <row r="407" ht="16" customHeight="1" s="8">
+    <row r="407" ht="16" customHeight="1" s="9">
       <c r="A407" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13228,7 +13221,7 @@
       </c>
       <c r="H407" s="6" t="n"/>
     </row>
-    <row r="408" ht="16" customHeight="1" s="8">
+    <row r="408" ht="16" customHeight="1" s="9">
       <c r="A408" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13260,7 +13253,7 @@
       </c>
       <c r="H408" s="6" t="n"/>
     </row>
-    <row r="409" ht="16" customHeight="1" s="8">
+    <row r="409" ht="16" customHeight="1" s="9">
       <c r="A409" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13292,7 +13285,7 @@
       </c>
       <c r="H409" s="6" t="n"/>
     </row>
-    <row r="410" ht="16" customHeight="1" s="8">
+    <row r="410" ht="16" customHeight="1" s="9">
       <c r="A410" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13324,7 +13317,7 @@
       </c>
       <c r="H410" s="6" t="n"/>
     </row>
-    <row r="411" ht="16" customHeight="1" s="8">
+    <row r="411" ht="16" customHeight="1" s="9">
       <c r="A411" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13356,7 +13349,7 @@
       </c>
       <c r="H411" s="6" t="n"/>
     </row>
-    <row r="412" ht="16" customHeight="1" s="8">
+    <row r="412" ht="16" customHeight="1" s="9">
       <c r="A412" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13388,7 +13381,7 @@
       </c>
       <c r="H412" s="6" t="n"/>
     </row>
-    <row r="413" ht="16" customHeight="1" s="8">
+    <row r="413" ht="16" customHeight="1" s="9">
       <c r="A413" s="3" t="inlineStr">
         <is>
           <t>V</t>
@@ -13420,7 +13413,7 @@
       </c>
       <c r="H413" s="6" t="n"/>
     </row>
-    <row r="414" ht="16" customHeight="1" s="8">
+    <row r="414" ht="16" customHeight="1" s="9">
       <c r="A414" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13452,7 +13445,7 @@
       </c>
       <c r="H414" s="6" t="n"/>
     </row>
-    <row r="415" ht="16" customHeight="1" s="8">
+    <row r="415" ht="16" customHeight="1" s="9">
       <c r="A415" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13484,7 +13477,7 @@
       </c>
       <c r="H415" s="6" t="n"/>
     </row>
-    <row r="416" ht="16" customHeight="1" s="8">
+    <row r="416" ht="16" customHeight="1" s="9">
       <c r="A416" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13516,7 +13509,7 @@
       </c>
       <c r="H416" s="6" t="n"/>
     </row>
-    <row r="417" ht="16" customHeight="1" s="8">
+    <row r="417" ht="16" customHeight="1" s="9">
       <c r="A417" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13548,7 +13541,7 @@
       </c>
       <c r="H417" s="6" t="n"/>
     </row>
-    <row r="418" ht="16" customHeight="1" s="8">
+    <row r="418" ht="16" customHeight="1" s="9">
       <c r="A418" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13580,7 +13573,7 @@
       </c>
       <c r="H418" s="6" t="n"/>
     </row>
-    <row r="419" ht="16" customHeight="1" s="8">
+    <row r="419" ht="16" customHeight="1" s="9">
       <c r="A419" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13612,7 +13605,7 @@
       </c>
       <c r="H419" s="6" t="n"/>
     </row>
-    <row r="420" ht="16" customHeight="1" s="8">
+    <row r="420" ht="16" customHeight="1" s="9">
       <c r="A420" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13644,7 +13637,7 @@
       </c>
       <c r="H420" s="6" t="n"/>
     </row>
-    <row r="421" ht="16" customHeight="1" s="8">
+    <row r="421" ht="16" customHeight="1" s="9">
       <c r="A421" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13670,7 +13663,7 @@
       <c r="G421" s="5" t="n"/>
       <c r="H421" s="6" t="n"/>
     </row>
-    <row r="422" ht="16" customHeight="1" s="8">
+    <row r="422" ht="16" customHeight="1" s="9">
       <c r="A422" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13702,7 +13695,7 @@
       </c>
       <c r="H422" s="6" t="n"/>
     </row>
-    <row r="423" ht="16" customHeight="1" s="8">
+    <row r="423" ht="16" customHeight="1" s="9">
       <c r="A423" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13728,7 +13721,7 @@
       <c r="G423" s="5" t="n"/>
       <c r="H423" s="6" t="n"/>
     </row>
-    <row r="424" ht="16" customHeight="1" s="8">
+    <row r="424" ht="16" customHeight="1" s="9">
       <c r="A424" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13754,7 +13747,7 @@
       <c r="G424" s="5" t="n"/>
       <c r="H424" s="6" t="n"/>
     </row>
-    <row r="425" ht="16" customHeight="1" s="8">
+    <row r="425" ht="16" customHeight="1" s="9">
       <c r="A425" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13786,7 +13779,7 @@
       </c>
       <c r="H425" s="6" t="n"/>
     </row>
-    <row r="426" ht="16" customHeight="1" s="8">
+    <row r="426" ht="16" customHeight="1" s="9">
       <c r="A426" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13818,7 +13811,7 @@
       </c>
       <c r="H426" s="6" t="n"/>
     </row>
-    <row r="427" ht="16" customHeight="1" s="8">
+    <row r="427" ht="16" customHeight="1" s="9">
       <c r="A427" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13844,7 +13837,7 @@
       <c r="G427" s="5" t="n"/>
       <c r="H427" s="6" t="n"/>
     </row>
-    <row r="428" ht="16" customHeight="1" s="8">
+    <row r="428" ht="16" customHeight="1" s="9">
       <c r="A428" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13876,7 +13869,7 @@
       </c>
       <c r="H428" s="6" t="n"/>
     </row>
-    <row r="429" ht="16" customHeight="1" s="8">
+    <row r="429" ht="16" customHeight="1" s="9">
       <c r="A429" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13908,7 +13901,7 @@
       </c>
       <c r="H429" s="6" t="n"/>
     </row>
-    <row r="430" ht="16" customHeight="1" s="8">
+    <row r="430" ht="16" customHeight="1" s="9">
       <c r="A430" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13934,7 +13927,7 @@
       <c r="G430" s="5" t="n"/>
       <c r="H430" s="6" t="n"/>
     </row>
-    <row r="431" ht="16" customHeight="1" s="8">
+    <row r="431" ht="16" customHeight="1" s="9">
       <c r="A431" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13966,7 +13959,7 @@
       </c>
       <c r="H431" s="6" t="n"/>
     </row>
-    <row r="432" ht="16" customHeight="1" s="8">
+    <row r="432" ht="16" customHeight="1" s="9">
       <c r="A432" s="3" t="inlineStr">
         <is>
           <t>W</t>
@@ -13998,7 +13991,7 @@
       </c>
       <c r="H432" s="6" t="n"/>
     </row>
-    <row r="433" ht="16" customHeight="1" s="8">
+    <row r="433" ht="16" customHeight="1" s="9">
       <c r="A433" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14030,7 +14023,7 @@
       </c>
       <c r="H433" s="6" t="n"/>
     </row>
-    <row r="434" ht="16" customHeight="1" s="8">
+    <row r="434" ht="16" customHeight="1" s="9">
       <c r="A434" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14062,7 +14055,7 @@
       </c>
       <c r="H434" s="6" t="n"/>
     </row>
-    <row r="435" ht="16" customHeight="1" s="8">
+    <row r="435" ht="16" customHeight="1" s="9">
       <c r="A435" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14094,7 +14087,7 @@
       </c>
       <c r="H435" s="6" t="n"/>
     </row>
-    <row r="436" ht="16" customHeight="1" s="8">
+    <row r="436" ht="16" customHeight="1" s="9">
       <c r="A436" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14126,7 +14119,7 @@
       </c>
       <c r="H436" s="6" t="n"/>
     </row>
-    <row r="437" ht="16" customHeight="1" s="8">
+    <row r="437" ht="16" customHeight="1" s="9">
       <c r="A437" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14152,7 +14145,7 @@
       <c r="G437" s="5" t="n"/>
       <c r="H437" s="6" t="n"/>
     </row>
-    <row r="438" ht="16" customHeight="1" s="8">
+    <row r="438" ht="16" customHeight="1" s="9">
       <c r="A438" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14184,7 +14177,7 @@
       </c>
       <c r="H438" s="6" t="n"/>
     </row>
-    <row r="439" ht="16" customHeight="1" s="8">
+    <row r="439" ht="16" customHeight="1" s="9">
       <c r="A439" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14216,7 +14209,7 @@
       </c>
       <c r="H439" s="6" t="n"/>
     </row>
-    <row r="440" ht="16" customHeight="1" s="8">
+    <row r="440" ht="16" customHeight="1" s="9">
       <c r="A440" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14242,7 +14235,7 @@
       <c r="G440" s="5" t="n"/>
       <c r="H440" s="6" t="n"/>
     </row>
-    <row r="441" ht="16" customHeight="1" s="8">
+    <row r="441" ht="16" customHeight="1" s="9">
       <c r="A441" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14274,7 +14267,7 @@
       </c>
       <c r="H441" s="6" t="n"/>
     </row>
-    <row r="442" ht="16" customHeight="1" s="8">
+    <row r="442" ht="16" customHeight="1" s="9">
       <c r="A442" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14306,7 +14299,7 @@
       </c>
       <c r="H442" s="6" t="n"/>
     </row>
-    <row r="443" ht="16" customHeight="1" s="8">
+    <row r="443" ht="16" customHeight="1" s="9">
       <c r="A443" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14338,7 +14331,7 @@
       </c>
       <c r="H443" s="6" t="n"/>
     </row>
-    <row r="444" ht="16" customHeight="1" s="8">
+    <row r="444" ht="16" customHeight="1" s="9">
       <c r="A444" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14370,7 +14363,7 @@
       </c>
       <c r="H444" s="6" t="n"/>
     </row>
-    <row r="445" ht="16" customHeight="1" s="8">
+    <row r="445" ht="16" customHeight="1" s="9">
       <c r="A445" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14402,7 +14395,7 @@
       </c>
       <c r="H445" s="6" t="n"/>
     </row>
-    <row r="446" ht="16" customHeight="1" s="8">
+    <row r="446" ht="16" customHeight="1" s="9">
       <c r="A446" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14434,7 +14427,7 @@
       </c>
       <c r="H446" s="6" t="n"/>
     </row>
-    <row r="447" ht="16" customHeight="1" s="8">
+    <row r="447" ht="16" customHeight="1" s="9">
       <c r="A447" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14460,7 +14453,7 @@
       <c r="G447" s="5" t="n"/>
       <c r="H447" s="6" t="n"/>
     </row>
-    <row r="448" ht="16" customHeight="1" s="8">
+    <row r="448" ht="16" customHeight="1" s="9">
       <c r="A448" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14486,7 +14479,7 @@
       <c r="G448" s="5" t="n"/>
       <c r="H448" s="6" t="n"/>
     </row>
-    <row r="449" ht="16" customHeight="1" s="8">
+    <row r="449" ht="16" customHeight="1" s="9">
       <c r="A449" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14518,7 +14511,7 @@
       </c>
       <c r="H449" s="6" t="n"/>
     </row>
-    <row r="450" ht="16" customHeight="1" s="8">
+    <row r="450" ht="16" customHeight="1" s="9">
       <c r="A450" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14550,7 +14543,7 @@
       </c>
       <c r="H450" s="6" t="n"/>
     </row>
-    <row r="451" ht="16" customHeight="1" s="8">
+    <row r="451" ht="16" customHeight="1" s="9">
       <c r="A451" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14582,7 +14575,7 @@
       </c>
       <c r="H451" s="6" t="n"/>
     </row>
-    <row r="452" ht="16" customHeight="1" s="8">
+    <row r="452" ht="16" customHeight="1" s="9">
       <c r="A452" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14614,7 +14607,7 @@
       </c>
       <c r="H452" s="6" t="n"/>
     </row>
-    <row r="453" ht="16" customHeight="1" s="8">
+    <row r="453" ht="16" customHeight="1" s="9">
       <c r="A453" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -14646,7 +14639,7 @@
       </c>
       <c r="H453" s="6" t="n"/>
     </row>
-    <row r="454" ht="16" customHeight="1" s="8">
+    <row r="454" ht="16" customHeight="1" s="9">
       <c r="A454" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14678,7 +14671,7 @@
       </c>
       <c r="H454" s="6" t="n"/>
     </row>
-    <row r="455" ht="16" customHeight="1" s="8">
+    <row r="455" ht="16" customHeight="1" s="9">
       <c r="A455" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14710,7 +14703,7 @@
       </c>
       <c r="H455" s="6" t="n"/>
     </row>
-    <row r="456" ht="16" customHeight="1" s="8">
+    <row r="456" ht="16" customHeight="1" s="9">
       <c r="A456" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14742,7 +14735,7 @@
       </c>
       <c r="H456" s="6" t="n"/>
     </row>
-    <row r="457" ht="16" customHeight="1" s="8">
+    <row r="457" ht="16" customHeight="1" s="9">
       <c r="A457" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14768,7 +14761,7 @@
       <c r="G457" s="5" t="n"/>
       <c r="H457" s="6" t="n"/>
     </row>
-    <row r="458" ht="16" customHeight="1" s="8">
+    <row r="458" ht="16" customHeight="1" s="9">
       <c r="A458" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14798,7 +14791,7 @@
       <c r="G458" s="5" t="n"/>
       <c r="H458" s="6" t="n"/>
     </row>
-    <row r="459" ht="16" customHeight="1" s="8">
+    <row r="459" ht="16" customHeight="1" s="9">
       <c r="A459" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14830,7 +14823,7 @@
       </c>
       <c r="H459" s="6" t="n"/>
     </row>
-    <row r="460" ht="16" customHeight="1" s="8">
+    <row r="460" ht="16" customHeight="1" s="9">
       <c r="A460" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14856,7 +14849,7 @@
       <c r="G460" s="5" t="n"/>
       <c r="H460" s="6" t="n"/>
     </row>
-    <row r="461" ht="16" customHeight="1" s="8">
+    <row r="461" ht="16" customHeight="1" s="9">
       <c r="A461" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14888,7 +14881,7 @@
       </c>
       <c r="H461" s="6" t="n"/>
     </row>
-    <row r="462" ht="16" customHeight="1" s="8">
+    <row r="462" ht="16" customHeight="1" s="9">
       <c r="A462" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14920,7 +14913,7 @@
       </c>
       <c r="H462" s="6" t="n"/>
     </row>
-    <row r="463" ht="16" customHeight="1" s="8">
+    <row r="463" ht="16" customHeight="1" s="9">
       <c r="A463" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -14946,7 +14939,7 @@
       <c r="G463" s="5" t="n"/>
       <c r="H463" s="6" t="n"/>
     </row>
-    <row r="464" ht="16" customHeight="1" s="8">
+    <row r="464" ht="16" customHeight="1" s="9">
       <c r="A464" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -14978,7 +14971,7 @@
       </c>
       <c r="H464" s="6" t="n"/>
     </row>
-    <row r="465" ht="16" customHeight="1" s="8">
+    <row r="465" ht="16" customHeight="1" s="9">
       <c r="A465" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15010,7 +15003,7 @@
       </c>
       <c r="H465" s="6" t="n"/>
     </row>
-    <row r="466" ht="16" customHeight="1" s="8">
+    <row r="466" ht="16" customHeight="1" s="9">
       <c r="A466" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15042,7 +15035,7 @@
       </c>
       <c r="H466" s="6" t="n"/>
     </row>
-    <row r="467" ht="16" customHeight="1" s="8">
+    <row r="467" ht="16" customHeight="1" s="9">
       <c r="A467" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15074,7 +15067,7 @@
       </c>
       <c r="H467" s="6" t="n"/>
     </row>
-    <row r="468" ht="16" customHeight="1" s="8">
+    <row r="468" ht="16" customHeight="1" s="9">
       <c r="A468" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15106,7 +15099,7 @@
       </c>
       <c r="H468" s="6" t="n"/>
     </row>
-    <row r="469" ht="16" customHeight="1" s="8">
+    <row r="469" ht="16" customHeight="1" s="9">
       <c r="A469" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15138,7 +15131,7 @@
       </c>
       <c r="H469" s="6" t="n"/>
     </row>
-    <row r="470" ht="16" customHeight="1" s="8">
+    <row r="470" ht="16" customHeight="1" s="9">
       <c r="A470" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15170,7 +15163,7 @@
       </c>
       <c r="H470" s="6" t="n"/>
     </row>
-    <row r="471" ht="16" customHeight="1" s="8">
+    <row r="471" ht="16" customHeight="1" s="9">
       <c r="A471" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15202,7 +15195,7 @@
       </c>
       <c r="H471" s="6" t="n"/>
     </row>
-    <row r="472" ht="16" customHeight="1" s="8">
+    <row r="472" ht="16" customHeight="1" s="9">
       <c r="A472" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15228,7 +15221,7 @@
       <c r="G472" s="5" t="n"/>
       <c r="H472" s="6" t="n"/>
     </row>
-    <row r="473" ht="16" customHeight="1" s="8">
+    <row r="473" ht="16" customHeight="1" s="9">
       <c r="A473" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15260,7 +15253,7 @@
       </c>
       <c r="H473" s="6" t="n"/>
     </row>
-    <row r="474" ht="16" customHeight="1" s="8">
+    <row r="474" ht="16" customHeight="1" s="9">
       <c r="A474" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15292,7 +15285,7 @@
       </c>
       <c r="H474" s="6" t="n"/>
     </row>
-    <row r="475" ht="16" customHeight="1" s="8">
+    <row r="475" ht="16" customHeight="1" s="9">
       <c r="A475" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15324,7 +15317,7 @@
       </c>
       <c r="H475" s="6" t="n"/>
     </row>
-    <row r="476" ht="16" customHeight="1" s="8">
+    <row r="476" ht="16" customHeight="1" s="9">
       <c r="A476" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15356,7 +15349,7 @@
       </c>
       <c r="H476" s="6" t="n"/>
     </row>
-    <row r="477" ht="16" customHeight="1" s="8">
+    <row r="477" ht="16" customHeight="1" s="9">
       <c r="A477" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15388,7 +15381,7 @@
       </c>
       <c r="H477" s="6" t="n"/>
     </row>
-    <row r="478" ht="16" customHeight="1" s="8">
+    <row r="478" ht="16" customHeight="1" s="9">
       <c r="A478" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15420,7 +15413,7 @@
       </c>
       <c r="H478" s="6" t="n"/>
     </row>
-    <row r="479" ht="16" customHeight="1" s="8">
+    <row r="479" ht="16" customHeight="1" s="9">
       <c r="A479" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15452,7 +15445,7 @@
       </c>
       <c r="H479" s="6" t="n"/>
     </row>
-    <row r="480" ht="16" customHeight="1" s="8">
+    <row r="480" ht="16" customHeight="1" s="9">
       <c r="A480" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15484,7 +15477,7 @@
       </c>
       <c r="H480" s="6" t="n"/>
     </row>
-    <row r="481" ht="16" customHeight="1" s="8">
+    <row r="481" ht="16" customHeight="1" s="9">
       <c r="A481" s="3" t="inlineStr">
         <is>
           <t>Z</t>
@@ -15514,7 +15507,7 @@
       </c>
       <c r="H481" s="6" t="n"/>
     </row>
-    <row r="482" ht="16" customHeight="1" s="8">
+    <row r="482" ht="16" customHeight="1" s="9">
       <c r="A482" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15546,7 +15539,7 @@
       </c>
       <c r="H482" s="6" t="n"/>
     </row>
-    <row r="483" ht="16" customHeight="1" s="8">
+    <row r="483" ht="16" customHeight="1" s="9">
       <c r="A483" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15578,7 +15571,7 @@
       </c>
       <c r="H483" s="6" t="n"/>
     </row>
-    <row r="484" ht="16" customHeight="1" s="8">
+    <row r="484" ht="16" customHeight="1" s="9">
       <c r="A484" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15610,7 +15603,7 @@
       </c>
       <c r="H484" s="6" t="n"/>
     </row>
-    <row r="485" ht="16" customHeight="1" s="8">
+    <row r="485" ht="16" customHeight="1" s="9">
       <c r="A485" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15642,7 +15635,7 @@
       </c>
       <c r="H485" s="6" t="n"/>
     </row>
-    <row r="486" ht="16" customHeight="1" s="8">
+    <row r="486" ht="16" customHeight="1" s="9">
       <c r="A486" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15674,7 +15667,7 @@
       </c>
       <c r="H486" s="6" t="n"/>
     </row>
-    <row r="487" ht="16" customHeight="1" s="8">
+    <row r="487" ht="16" customHeight="1" s="9">
       <c r="A487" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15706,7 +15699,7 @@
       </c>
       <c r="H487" s="6" t="n"/>
     </row>
-    <row r="488" ht="16" customHeight="1" s="8">
+    <row r="488" ht="16" customHeight="1" s="9">
       <c r="A488" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15738,7 +15731,7 @@
       </c>
       <c r="H488" s="6" t="n"/>
     </row>
-    <row r="489" ht="16" customHeight="1" s="8">
+    <row r="489" ht="16" customHeight="1" s="9">
       <c r="A489" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15770,7 +15763,7 @@
       </c>
       <c r="H489" s="6" t="n"/>
     </row>
-    <row r="490" ht="16" customHeight="1" s="8">
+    <row r="490" ht="16" customHeight="1" s="9">
       <c r="A490" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15796,7 +15789,7 @@
       <c r="G490" s="5" t="n"/>
       <c r="H490" s="6" t="n"/>
     </row>
-    <row r="491" ht="16" customHeight="1" s="8">
+    <row r="491" ht="16" customHeight="1" s="9">
       <c r="A491" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15822,7 +15815,7 @@
       <c r="G491" s="5" t="n"/>
       <c r="H491" s="6" t="n"/>
     </row>
-    <row r="492" ht="16" customHeight="1" s="8">
+    <row r="492" ht="16" customHeight="1" s="9">
       <c r="A492" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15848,7 +15841,7 @@
       <c r="G492" s="5" t="n"/>
       <c r="H492" s="6" t="n"/>
     </row>
-    <row r="493" ht="16" customHeight="1" s="8">
+    <row r="493" ht="16" customHeight="1" s="9">
       <c r="A493" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15880,7 +15873,7 @@
       </c>
       <c r="H493" s="6" t="n"/>
     </row>
-    <row r="494" ht="16" customHeight="1" s="8">
+    <row r="494" ht="16" customHeight="1" s="9">
       <c r="A494" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15912,7 +15905,7 @@
       </c>
       <c r="H494" s="6" t="n"/>
     </row>
-    <row r="495" ht="16" customHeight="1" s="8">
+    <row r="495" ht="16" customHeight="1" s="9">
       <c r="A495" s="3" t="inlineStr">
         <is>
           <t>A1</t>
@@ -15944,7 +15937,7 @@
       </c>
       <c r="H495" s="6" t="n"/>
     </row>
-    <row r="496" ht="16" customHeight="1" s="8">
+    <row r="496" ht="16" customHeight="1" s="9">
       <c r="A496" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15976,7 +15969,7 @@
       </c>
       <c r="H496" s="6" t="n"/>
     </row>
-    <row r="497" ht="16" customHeight="1" s="8">
+    <row r="497" ht="16" customHeight="1" s="9">
       <c r="A497" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16002,7 +15995,7 @@
       <c r="G497" s="5" t="n"/>
       <c r="H497" s="6" t="n"/>
     </row>
-    <row r="498" ht="16" customHeight="1" s="8">
+    <row r="498" ht="16" customHeight="1" s="9">
       <c r="A498" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16034,7 +16027,7 @@
       </c>
       <c r="H498" s="6" t="n"/>
     </row>
-    <row r="499" ht="16" customHeight="1" s="8">
+    <row r="499" ht="16" customHeight="1" s="9">
       <c r="A499" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16066,7 +16059,7 @@
       </c>
       <c r="H499" s="6" t="n"/>
     </row>
-    <row r="500" ht="16" customHeight="1" s="8">
+    <row r="500" ht="16" customHeight="1" s="9">
       <c r="A500" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16098,7 +16091,7 @@
       </c>
       <c r="H500" s="6" t="n"/>
     </row>
-    <row r="501" ht="16" customHeight="1" s="8">
+    <row r="501" ht="16" customHeight="1" s="9">
       <c r="A501" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16130,7 +16123,7 @@
       </c>
       <c r="H501" s="6" t="n"/>
     </row>
-    <row r="502" ht="16" customHeight="1" s="8">
+    <row r="502" ht="16" customHeight="1" s="9">
       <c r="A502" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16156,7 +16149,7 @@
       <c r="G502" s="5" t="n"/>
       <c r="H502" s="6" t="n"/>
     </row>
-    <row r="503" ht="16" customHeight="1" s="8">
+    <row r="503" ht="16" customHeight="1" s="9">
       <c r="A503" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16188,7 +16181,7 @@
       </c>
       <c r="H503" s="6" t="n"/>
     </row>
-    <row r="504" ht="16" customHeight="1" s="8">
+    <row r="504" ht="16" customHeight="1" s="9">
       <c r="A504" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16220,7 +16213,7 @@
       </c>
       <c r="H504" s="6" t="n"/>
     </row>
-    <row r="505" ht="16" customHeight="1" s="8">
+    <row r="505" ht="16" customHeight="1" s="9">
       <c r="A505" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16252,7 +16245,7 @@
       </c>
       <c r="H505" s="6" t="n"/>
     </row>
-    <row r="506" ht="16" customHeight="1" s="8">
+    <row r="506" ht="16" customHeight="1" s="9">
       <c r="A506" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16284,7 +16277,7 @@
       </c>
       <c r="H506" s="6" t="n"/>
     </row>
-    <row r="507" ht="16" customHeight="1" s="8">
+    <row r="507" ht="16" customHeight="1" s="9">
       <c r="A507" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16316,7 +16309,7 @@
       </c>
       <c r="H507" s="6" t="n"/>
     </row>
-    <row r="508" ht="16" customHeight="1" s="8">
+    <row r="508" ht="16" customHeight="1" s="9">
       <c r="A508" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16348,7 +16341,7 @@
       </c>
       <c r="H508" s="6" t="n"/>
     </row>
-    <row r="509" ht="16" customHeight="1" s="8">
+    <row r="509" ht="16" customHeight="1" s="9">
       <c r="A509" s="3" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16380,7 +16373,7 @@
       </c>
       <c r="H509" s="6" t="n"/>
     </row>
-    <row r="510" ht="16" customHeight="1" s="8">
+    <row r="510" ht="16" customHeight="1" s="9">
       <c r="A510" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16412,7 +16405,7 @@
       </c>
       <c r="H510" s="6" t="n"/>
     </row>
-    <row r="511" ht="16" customHeight="1" s="8">
+    <row r="511" ht="16" customHeight="1" s="9">
       <c r="A511" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16444,7 +16437,7 @@
       </c>
       <c r="H511" s="6" t="n"/>
     </row>
-    <row r="512" ht="16" customHeight="1" s="8">
+    <row r="512" ht="16" customHeight="1" s="9">
       <c r="A512" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16476,7 +16469,7 @@
       </c>
       <c r="H512" s="6" t="n"/>
     </row>
-    <row r="513" ht="16" customHeight="1" s="8">
+    <row r="513" ht="16" customHeight="1" s="9">
       <c r="A513" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16508,7 +16501,7 @@
       </c>
       <c r="H513" s="6" t="n"/>
     </row>
-    <row r="514" ht="16" customHeight="1" s="8">
+    <row r="514" ht="16" customHeight="1" s="9">
       <c r="A514" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16540,7 +16533,7 @@
       </c>
       <c r="H514" s="6" t="n"/>
     </row>
-    <row r="515" ht="16" customHeight="1" s="8">
+    <row r="515" ht="16" customHeight="1" s="9">
       <c r="A515" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16572,7 +16565,7 @@
       </c>
       <c r="H515" s="6" t="n"/>
     </row>
-    <row r="516" ht="16" customHeight="1" s="8">
+    <row r="516" ht="16" customHeight="1" s="9">
       <c r="A516" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16604,7 +16597,7 @@
       </c>
       <c r="H516" s="6" t="n"/>
     </row>
-    <row r="517" ht="16" customHeight="1" s="8">
+    <row r="517" ht="16" customHeight="1" s="9">
       <c r="A517" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16636,7 +16629,7 @@
       </c>
       <c r="H517" s="6" t="n"/>
     </row>
-    <row r="518" ht="16" customHeight="1" s="8">
+    <row r="518" ht="16" customHeight="1" s="9">
       <c r="A518" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16666,7 +16659,7 @@
       </c>
       <c r="H518" s="6" t="n"/>
     </row>
-    <row r="519" ht="16" customHeight="1" s="8">
+    <row r="519" ht="16" customHeight="1" s="9">
       <c r="A519" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16698,7 +16691,7 @@
       </c>
       <c r="H519" s="6" t="n"/>
     </row>
-    <row r="520" ht="16" customHeight="1" s="8">
+    <row r="520" ht="16" customHeight="1" s="9">
       <c r="A520" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16730,7 +16723,7 @@
       </c>
       <c r="H520" s="6" t="n"/>
     </row>
-    <row r="521" ht="16" customHeight="1" s="8">
+    <row r="521" ht="16" customHeight="1" s="9">
       <c r="A521" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16762,7 +16755,7 @@
       </c>
       <c r="H521" s="6" t="n"/>
     </row>
-    <row r="522" ht="16" customHeight="1" s="8">
+    <row r="522" ht="16" customHeight="1" s="9">
       <c r="A522" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16794,7 +16787,7 @@
       </c>
       <c r="H522" s="6" t="n"/>
     </row>
-    <row r="523" ht="16" customHeight="1" s="8">
+    <row r="523" ht="16" customHeight="1" s="9">
       <c r="A523" s="3" t="inlineStr">
         <is>
           <t>C1</t>
@@ -16820,13 +16813,9 @@
       </c>
       <c r="F523" s="5" t="n"/>
       <c r="G523" s="5" t="n"/>
-      <c r="H523" s="6" t="inlineStr">
-        <is>
-          <t>no existe este lote</t>
-        </is>
-      </c>
-    </row>
-    <row r="524" ht="16" customHeight="1" s="8">
+      <c r="H523" s="6" t="n"/>
+    </row>
+    <row r="524" ht="16" customHeight="1" s="9">
       <c r="A524" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16858,7 +16847,7 @@
       </c>
       <c r="H524" s="6" t="n"/>
     </row>
-    <row r="525" ht="16" customHeight="1" s="8">
+    <row r="525" ht="16" customHeight="1" s="9">
       <c r="A525" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16890,7 +16879,7 @@
       </c>
       <c r="H525" s="6" t="n"/>
     </row>
-    <row r="526" ht="16" customHeight="1" s="8">
+    <row r="526" ht="16" customHeight="1" s="9">
       <c r="A526" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16922,7 +16911,7 @@
       </c>
       <c r="H526" s="6" t="n"/>
     </row>
-    <row r="527" ht="16" customHeight="1" s="8">
+    <row r="527" ht="16" customHeight="1" s="9">
       <c r="A527" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16954,7 +16943,7 @@
       </c>
       <c r="H527" s="6" t="n"/>
     </row>
-    <row r="528" ht="16" customHeight="1" s="8">
+    <row r="528" ht="16" customHeight="1" s="9">
       <c r="A528" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16986,7 +16975,7 @@
       </c>
       <c r="H528" s="6" t="n"/>
     </row>
-    <row r="529" ht="16" customHeight="1" s="8">
+    <row r="529" ht="16" customHeight="1" s="9">
       <c r="A529" s="3" t="inlineStr">
         <is>
           <t>D1</t>
@@ -17018,7 +17007,7 @@
       </c>
       <c r="H529" s="6" t="n"/>
     </row>
-    <row r="530" ht="16" customHeight="1" s="8">
+    <row r="530" ht="16" customHeight="1" s="9">
       <c r="A530" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17050,7 +17039,7 @@
       </c>
       <c r="H530" s="6" t="n"/>
     </row>
-    <row r="531" ht="16" customHeight="1" s="8">
+    <row r="531" ht="16" customHeight="1" s="9">
       <c r="A531" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17076,7 +17065,7 @@
       <c r="G531" s="5" t="n"/>
       <c r="H531" s="6" t="n"/>
     </row>
-    <row r="532" ht="16" customHeight="1" s="8">
+    <row r="532" ht="16" customHeight="1" s="9">
       <c r="A532" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17108,7 +17097,7 @@
       </c>
       <c r="H532" s="6" t="n"/>
     </row>
-    <row r="533" ht="16" customHeight="1" s="8">
+    <row r="533" ht="16" customHeight="1" s="9">
       <c r="A533" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17140,7 +17129,7 @@
       </c>
       <c r="H533" s="6" t="n"/>
     </row>
-    <row r="534" ht="16" customHeight="1" s="8">
+    <row r="534" ht="16" customHeight="1" s="9">
       <c r="A534" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17166,7 +17155,7 @@
       <c r="G534" s="5" t="n"/>
       <c r="H534" s="6" t="n"/>
     </row>
-    <row r="535" ht="16" customHeight="1" s="8">
+    <row r="535" ht="16" customHeight="1" s="9">
       <c r="A535" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17196,7 +17185,7 @@
       </c>
       <c r="H535" s="6" t="n"/>
     </row>
-    <row r="536" ht="16" customHeight="1" s="8">
+    <row r="536" ht="16" customHeight="1" s="9">
       <c r="A536" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17228,7 +17217,7 @@
       </c>
       <c r="H536" s="6" t="n"/>
     </row>
-    <row r="537" ht="16" customHeight="1" s="8">
+    <row r="537" ht="16" customHeight="1" s="9">
       <c r="A537" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17260,7 +17249,7 @@
       </c>
       <c r="H537" s="6" t="n"/>
     </row>
-    <row r="538" ht="16" customHeight="1" s="8">
+    <row r="538" ht="16" customHeight="1" s="9">
       <c r="A538" s="3" t="inlineStr">
         <is>
           <t>E1</t>
@@ -17292,7 +17281,7 @@
       </c>
       <c r="H538" s="6" t="n"/>
     </row>
-    <row r="539" ht="16" customHeight="1" s="8">
+    <row r="539" ht="16" customHeight="1" s="9">
       <c r="A539" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17324,7 +17313,7 @@
       </c>
       <c r="H539" s="6" t="n"/>
     </row>
-    <row r="540" ht="16" customHeight="1" s="8">
+    <row r="540" ht="16" customHeight="1" s="9">
       <c r="A540" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17356,7 +17345,7 @@
       </c>
       <c r="H540" s="6" t="n"/>
     </row>
-    <row r="541" ht="16" customHeight="1" s="8">
+    <row r="541" ht="16" customHeight="1" s="9">
       <c r="A541" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17382,7 +17371,7 @@
       <c r="G541" s="5" t="n"/>
       <c r="H541" s="6" t="n"/>
     </row>
-    <row r="542" ht="16" customHeight="1" s="8">
+    <row r="542" ht="16" customHeight="1" s="9">
       <c r="A542" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17414,7 +17403,7 @@
       </c>
       <c r="H542" s="6" t="n"/>
     </row>
-    <row r="543" ht="16" customHeight="1" s="8">
+    <row r="543" ht="16" customHeight="1" s="9">
       <c r="A543" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17440,7 +17429,7 @@
       <c r="G543" s="5" t="n"/>
       <c r="H543" s="6" t="n"/>
     </row>
-    <row r="544" ht="16" customHeight="1" s="8">
+    <row r="544" ht="16" customHeight="1" s="9">
       <c r="A544" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17470,13 +17459,9 @@
       <c r="G544" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H544" s="6" t="inlineStr">
-        <is>
-          <t>por que nombre recucido</t>
-        </is>
-      </c>
-    </row>
-    <row r="545" ht="16" customHeight="1" s="8">
+      <c r="H544" s="6" t="n"/>
+    </row>
+    <row r="545" ht="16" customHeight="1" s="9">
       <c r="A545" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17506,13 +17491,9 @@
       <c r="G545" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H545" s="6" t="inlineStr">
-        <is>
-          <t>por que nombre recucido</t>
-        </is>
-      </c>
-    </row>
-    <row r="546" ht="16" customHeight="1" s="8">
+      <c r="H545" s="6" t="n"/>
+    </row>
+    <row r="546" ht="16" customHeight="1" s="9">
       <c r="A546" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17544,7 +17525,7 @@
       </c>
       <c r="H546" s="6" t="n"/>
     </row>
-    <row r="547" ht="16" customHeight="1" s="8">
+    <row r="547" ht="16" customHeight="1" s="9">
       <c r="A547" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17576,7 +17557,7 @@
       </c>
       <c r="H547" s="6" t="n"/>
     </row>
-    <row r="548" ht="16" customHeight="1" s="8">
+    <row r="548" ht="16" customHeight="1" s="9">
       <c r="A548" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17608,7 +17589,7 @@
       </c>
       <c r="H548" s="6" t="n"/>
     </row>
-    <row r="549" ht="16" customHeight="1" s="8">
+    <row r="549" ht="16" customHeight="1" s="9">
       <c r="A549" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17640,7 +17621,7 @@
       </c>
       <c r="H549" s="6" t="n"/>
     </row>
-    <row r="550" ht="16" customHeight="1" s="8">
+    <row r="550" ht="16" customHeight="1" s="9">
       <c r="A550" s="3" t="inlineStr">
         <is>
           <t>F1</t>
@@ -17672,7 +17653,7 @@
       </c>
       <c r="H550" s="6" t="n"/>
     </row>
-    <row r="551" ht="16" customHeight="1" s="8">
+    <row r="551" ht="16" customHeight="1" s="9">
       <c r="A551" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17704,7 +17685,7 @@
       </c>
       <c r="H551" s="6" t="n"/>
     </row>
-    <row r="552" ht="16" customHeight="1" s="8">
+    <row r="552" ht="16" customHeight="1" s="9">
       <c r="A552" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17736,7 +17717,7 @@
       </c>
       <c r="H552" s="6" t="n"/>
     </row>
-    <row r="553" ht="16" customHeight="1" s="8">
+    <row r="553" ht="16" customHeight="1" s="9">
       <c r="A553" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17768,7 +17749,7 @@
       </c>
       <c r="H553" s="6" t="n"/>
     </row>
-    <row r="554" ht="16" customHeight="1" s="8">
+    <row r="554" ht="16" customHeight="1" s="9">
       <c r="A554" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17800,7 +17781,7 @@
       </c>
       <c r="H554" s="6" t="n"/>
     </row>
-    <row r="555" ht="16" customHeight="1" s="8">
+    <row r="555" ht="16" customHeight="1" s="9">
       <c r="A555" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17832,7 +17813,7 @@
       </c>
       <c r="H555" s="6" t="n"/>
     </row>
-    <row r="556" ht="16" customHeight="1" s="8">
+    <row r="556" ht="16" customHeight="1" s="9">
       <c r="A556" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17858,7 +17839,7 @@
       <c r="G556" s="5" t="n"/>
       <c r="H556" s="6" t="n"/>
     </row>
-    <row r="557" ht="16" customHeight="1" s="8">
+    <row r="557" ht="16" customHeight="1" s="9">
       <c r="A557" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17884,7 +17865,7 @@
       <c r="G557" s="5" t="n"/>
       <c r="H557" s="6" t="n"/>
     </row>
-    <row r="558" ht="16" customHeight="1" s="8">
+    <row r="558" ht="16" customHeight="1" s="9">
       <c r="A558" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17910,7 +17891,7 @@
       <c r="G558" s="5" t="n"/>
       <c r="H558" s="6" t="n"/>
     </row>
-    <row r="559" ht="16" customHeight="1" s="8">
+    <row r="559" ht="16" customHeight="1" s="9">
       <c r="A559" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17936,7 +17917,7 @@
       <c r="G559" s="5" t="n"/>
       <c r="H559" s="6" t="n"/>
     </row>
-    <row r="560" ht="16" customHeight="1" s="8">
+    <row r="560" ht="16" customHeight="1" s="9">
       <c r="A560" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17962,7 +17943,7 @@
       <c r="G560" s="5" t="n"/>
       <c r="H560" s="6" t="n"/>
     </row>
-    <row r="561" ht="16" customHeight="1" s="8">
+    <row r="561" ht="16" customHeight="1" s="9">
       <c r="A561" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -17988,7 +17969,7 @@
       <c r="G561" s="5" t="n"/>
       <c r="H561" s="6" t="n"/>
     </row>
-    <row r="562" ht="16" customHeight="1" s="8">
+    <row r="562" ht="16" customHeight="1" s="9">
       <c r="A562" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -18014,7 +17995,7 @@
       <c r="G562" s="5" t="n"/>
       <c r="H562" s="6" t="n"/>
     </row>
-    <row r="563" ht="16" customHeight="1" s="8">
+    <row r="563" ht="16" customHeight="1" s="9">
       <c r="A563" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -18040,7 +18021,7 @@
       <c r="G563" s="5" t="n"/>
       <c r="H563" s="6" t="n"/>
     </row>
-    <row r="564" ht="16" customHeight="1" s="8">
+    <row r="564" ht="16" customHeight="1" s="9">
       <c r="A564" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -18066,7 +18047,7 @@
       <c r="G564" s="5" t="n"/>
       <c r="H564" s="6" t="n"/>
     </row>
-    <row r="565" ht="16" customHeight="1" s="8">
+    <row r="565" ht="16" customHeight="1" s="9">
       <c r="A565" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -18092,7 +18073,7 @@
       <c r="G565" s="5" t="n"/>
       <c r="H565" s="6" t="n"/>
     </row>
-    <row r="566" ht="16" customHeight="1" s="8">
+    <row r="566" ht="16" customHeight="1" s="9">
       <c r="A566" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18124,7 +18105,7 @@
       </c>
       <c r="H566" s="6" t="n"/>
     </row>
-    <row r="567" ht="16" customHeight="1" s="8">
+    <row r="567" ht="16" customHeight="1" s="9">
       <c r="A567" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18154,7 +18135,7 @@
       </c>
       <c r="H567" s="6" t="n"/>
     </row>
-    <row r="568" ht="16" customHeight="1" s="8">
+    <row r="568" ht="16" customHeight="1" s="9">
       <c r="A568" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18186,7 +18167,7 @@
       </c>
       <c r="H568" s="6" t="n"/>
     </row>
-    <row r="569" ht="16" customHeight="1" s="8">
+    <row r="569" ht="16" customHeight="1" s="9">
       <c r="A569" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18212,7 +18193,7 @@
       <c r="G569" s="5" t="n"/>
       <c r="H569" s="6" t="n"/>
     </row>
-    <row r="570" ht="16" customHeight="1" s="8">
+    <row r="570" ht="16" customHeight="1" s="9">
       <c r="A570" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18244,7 +18225,7 @@
       </c>
       <c r="H570" s="6" t="n"/>
     </row>
-    <row r="571" ht="16" customHeight="1" s="8">
+    <row r="571" ht="16" customHeight="1" s="9">
       <c r="A571" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18276,7 +18257,7 @@
       </c>
       <c r="H571" s="6" t="n"/>
     </row>
-    <row r="572" ht="16" customHeight="1" s="8">
+    <row r="572" ht="16" customHeight="1" s="9">
       <c r="A572" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18308,7 +18289,7 @@
       </c>
       <c r="H572" s="6" t="n"/>
     </row>
-    <row r="573" ht="16" customHeight="1" s="8">
+    <row r="573" ht="16" customHeight="1" s="9">
       <c r="A573" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18340,7 +18321,7 @@
       </c>
       <c r="H573" s="6" t="n"/>
     </row>
-    <row r="574" ht="16" customHeight="1" s="8">
+    <row r="574" ht="16" customHeight="1" s="9">
       <c r="A574" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18372,7 +18353,7 @@
       </c>
       <c r="H574" s="6" t="n"/>
     </row>
-    <row r="575" ht="16" customHeight="1" s="8">
+    <row r="575" ht="16" customHeight="1" s="9">
       <c r="A575" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18398,7 +18379,7 @@
       <c r="G575" s="5" t="n"/>
       <c r="H575" s="6" t="n"/>
     </row>
-    <row r="576" ht="16" customHeight="1" s="8">
+    <row r="576" ht="16" customHeight="1" s="9">
       <c r="A576" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18430,7 +18411,7 @@
       </c>
       <c r="H576" s="6" t="n"/>
     </row>
-    <row r="577" ht="16" customHeight="1" s="8">
+    <row r="577" ht="16" customHeight="1" s="9">
       <c r="A577" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18462,7 +18443,7 @@
       </c>
       <c r="H577" s="6" t="n"/>
     </row>
-    <row r="578" ht="16" customHeight="1" s="8">
+    <row r="578" ht="16" customHeight="1" s="9">
       <c r="A578" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18492,7 +18473,7 @@
       <c r="G578" s="5" t="n"/>
       <c r="H578" s="6" t="n"/>
     </row>
-    <row r="579" ht="16" customHeight="1" s="8">
+    <row r="579" ht="16" customHeight="1" s="9">
       <c r="A579" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18522,7 +18503,7 @@
       <c r="G579" s="5" t="n"/>
       <c r="H579" s="6" t="n"/>
     </row>
-    <row r="580" ht="16" customHeight="1" s="8">
+    <row r="580" ht="16" customHeight="1" s="9">
       <c r="A580" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18554,7 +18535,7 @@
       </c>
       <c r="H580" s="6" t="n"/>
     </row>
-    <row r="581" ht="16" customHeight="1" s="8">
+    <row r="581" ht="16" customHeight="1" s="9">
       <c r="A581" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18586,7 +18567,7 @@
       </c>
       <c r="H581" s="6" t="n"/>
     </row>
-    <row r="582" ht="16" customHeight="1" s="8">
+    <row r="582" ht="16" customHeight="1" s="9">
       <c r="A582" s="3" t="inlineStr">
         <is>
           <t>H1</t>
@@ -18622,8 +18603,8 @@
   <mergeCells count="9">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D4:H4"/>
